--- a/vokabeln.xlsx
+++ b/vokabeln.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S02887\vokabeltrainer_web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82DABE78-7E5F-4211-813E-730236D147E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8531E1-F2BB-416D-90C7-E1CB47F471FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6210" yWindow="1320" windowWidth="26625" windowHeight="18105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25215" yWindow="660" windowWidth="12870" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5674" uniqueCount="2161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5691" uniqueCount="2177">
   <si>
     <t>Deutsch</t>
   </si>
@@ -6516,6 +6516,54 @@
   </si>
   <si>
     <t>Volatilität</t>
+  </si>
+  <si>
+    <t>drohen</t>
+  </si>
+  <si>
+    <t>threaten</t>
+  </si>
+  <si>
+    <t>Gruppe 14</t>
+  </si>
+  <si>
+    <t>Vergeltung</t>
+  </si>
+  <si>
+    <t>retaliation</t>
+  </si>
+  <si>
+    <t>vermeiden</t>
+  </si>
+  <si>
+    <t>avoid</t>
+  </si>
+  <si>
+    <t>Untergrundvorräte</t>
+  </si>
+  <si>
+    <t>underground inventories</t>
+  </si>
+  <si>
+    <t>Kältewelle</t>
+  </si>
+  <si>
+    <t>cold spell</t>
+  </si>
+  <si>
+    <t>Bestimmung</t>
+  </si>
+  <si>
+    <t>Provision</t>
+  </si>
+  <si>
+    <t>Preisanpassung</t>
+  </si>
+  <si>
+    <t>price revision</t>
+  </si>
+  <si>
+    <t>Überarbeitung/Anpassung</t>
   </si>
 </sst>
 </file>
@@ -6584,7 +6632,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -6593,11 +6641,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -6909,13 +6954,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K631"/>
+  <dimension ref="A1:K639"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.85546875" customWidth="1"/>
     <col min="2" max="2" width="35.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="43.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.140625" style="6"/>
+    <col min="4" max="5" width="9.140625" style="5"/>
     <col min="6" max="6" width="72.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="65.7109375" bestFit="1" customWidth="1"/>
   </cols>
@@ -6930,10 +6975,10 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -7095,38 +7140,38 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="6">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6">
-        <v>1</v>
-      </c>
-      <c r="F6" s="6" t="s">
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -7140,10 +7185,10 @@
       <c r="C7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="6">
-        <v>1</v>
-      </c>
-      <c r="E7" s="6">
+      <c r="D7" s="5">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5">
         <v>1</v>
       </c>
       <c r="F7" t="s">
@@ -7175,10 +7220,10 @@
       <c r="C8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="6">
-        <v>1</v>
-      </c>
-      <c r="E8" s="6">
+      <c r="D8" s="5">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5">
         <v>1</v>
       </c>
       <c r="F8" t="s">
@@ -7210,10 +7255,10 @@
       <c r="C9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="6">
-        <v>1</v>
-      </c>
-      <c r="E9" s="6">
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5">
         <v>1</v>
       </c>
       <c r="F9" t="s">
@@ -7245,10 +7290,10 @@
       <c r="C10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="6">
-        <v>1</v>
-      </c>
-      <c r="E10" s="6">
+      <c r="D10" s="5">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5">
         <v>1</v>
       </c>
       <c r="F10" t="s">
@@ -7280,10 +7325,10 @@
       <c r="C11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="6">
-        <v>1</v>
-      </c>
-      <c r="E11" s="6">
+      <c r="D11" s="5">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5">
         <v>1</v>
       </c>
       <c r="F11" t="s">
@@ -7315,10 +7360,10 @@
       <c r="C12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="6">
-        <v>1</v>
-      </c>
-      <c r="E12" s="6">
+      <c r="D12" s="5">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5">
         <v>1</v>
       </c>
       <c r="F12" t="s">
@@ -7350,10 +7395,10 @@
       <c r="C13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="6">
-        <v>1</v>
-      </c>
-      <c r="E13" s="6">
+      <c r="D13" s="5">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5">
         <v>1</v>
       </c>
       <c r="F13" t="s">
@@ -7385,10 +7430,10 @@
       <c r="C14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="6">
-        <v>1</v>
-      </c>
-      <c r="E14" s="6">
+      <c r="D14" s="5">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5">
         <v>1</v>
       </c>
       <c r="F14" t="s">
@@ -7420,10 +7465,10 @@
       <c r="C15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="6">
-        <v>1</v>
-      </c>
-      <c r="E15" s="6">
+      <c r="D15" s="5">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5">
         <v>1</v>
       </c>
       <c r="F15" t="s">
@@ -7455,10 +7500,10 @@
       <c r="C16" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="6">
-        <v>1</v>
-      </c>
-      <c r="E16" s="6">
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5">
         <v>1</v>
       </c>
       <c r="F16" t="s">
@@ -7490,10 +7535,10 @@
       <c r="C17" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="6">
-        <v>1</v>
-      </c>
-      <c r="E17" s="6">
+      <c r="D17" s="5">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5">
         <v>1</v>
       </c>
       <c r="F17" t="s">
@@ -7525,10 +7570,10 @@
       <c r="C18" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="6">
-        <v>1</v>
-      </c>
-      <c r="E18" s="6">
+      <c r="D18" s="5">
+        <v>1</v>
+      </c>
+      <c r="E18" s="5">
         <v>1</v>
       </c>
       <c r="F18" t="s">
@@ -7560,10 +7605,10 @@
       <c r="C19" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="6">
-        <v>1</v>
-      </c>
-      <c r="E19" s="6">
+      <c r="D19" s="5">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5">
         <v>1</v>
       </c>
       <c r="F19" t="s">
@@ -7595,10 +7640,10 @@
       <c r="C20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="6">
-        <v>1</v>
-      </c>
-      <c r="E20" s="6">
+      <c r="D20" s="5">
+        <v>1</v>
+      </c>
+      <c r="E20" s="5">
         <v>1</v>
       </c>
       <c r="F20" t="s">
@@ -7630,10 +7675,10 @@
       <c r="C21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="6">
-        <v>1</v>
-      </c>
-      <c r="E21" s="6">
+      <c r="D21" s="5">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5">
         <v>1</v>
       </c>
       <c r="F21" t="s">
@@ -7665,10 +7710,10 @@
       <c r="C22" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="6">
-        <v>1</v>
-      </c>
-      <c r="E22" s="6">
+      <c r="D22" s="5">
+        <v>1</v>
+      </c>
+      <c r="E22" s="5">
         <v>1</v>
       </c>
       <c r="F22" t="s">
@@ -7700,10 +7745,10 @@
       <c r="C23" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="6">
-        <v>1</v>
-      </c>
-      <c r="E23" s="6">
+      <c r="D23" s="5">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5">
         <v>1</v>
       </c>
       <c r="F23" t="s">
@@ -7735,10 +7780,10 @@
       <c r="C24" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D24" s="6">
-        <v>1</v>
-      </c>
-      <c r="E24" s="6">
+      <c r="D24" s="5">
+        <v>1</v>
+      </c>
+      <c r="E24" s="5">
         <v>1</v>
       </c>
       <c r="F24" t="s">
@@ -7770,10 +7815,10 @@
       <c r="C25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="6">
-        <v>1</v>
-      </c>
-      <c r="E25" s="6">
+      <c r="D25" s="5">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5">
         <v>1</v>
       </c>
       <c r="F25" t="s">
@@ -7805,10 +7850,10 @@
       <c r="C26" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="6">
-        <v>1</v>
-      </c>
-      <c r="E26" s="6">
+      <c r="D26" s="5">
+        <v>1</v>
+      </c>
+      <c r="E26" s="5">
         <v>1</v>
       </c>
       <c r="F26" t="s">
@@ -7840,10 +7885,10 @@
       <c r="C27" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D27" s="6">
-        <v>1</v>
-      </c>
-      <c r="E27" s="6">
+      <c r="D27" s="5">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5">
         <v>1</v>
       </c>
       <c r="F27" t="s">
@@ -7875,10 +7920,10 @@
       <c r="C28" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="6">
-        <v>1</v>
-      </c>
-      <c r="E28" s="6">
+      <c r="D28" s="5">
+        <v>1</v>
+      </c>
+      <c r="E28" s="5">
         <v>1</v>
       </c>
       <c r="F28" t="s">
@@ -7910,10 +7955,10 @@
       <c r="C29" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="6">
-        <v>1</v>
-      </c>
-      <c r="E29" s="6">
+      <c r="D29" s="5">
+        <v>1</v>
+      </c>
+      <c r="E29" s="5">
         <v>1</v>
       </c>
       <c r="F29" t="s">
@@ -7945,10 +7990,10 @@
       <c r="C30" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="6">
-        <v>1</v>
-      </c>
-      <c r="E30" s="6">
+      <c r="D30" s="5">
+        <v>1</v>
+      </c>
+      <c r="E30" s="5">
         <v>1</v>
       </c>
       <c r="F30" t="s">
@@ -7980,10 +8025,10 @@
       <c r="C31" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="6">
-        <v>1</v>
-      </c>
-      <c r="E31" s="6">
+      <c r="D31" s="5">
+        <v>1</v>
+      </c>
+      <c r="E31" s="5">
         <v>1</v>
       </c>
       <c r="F31" t="s">
@@ -8015,10 +8060,10 @@
       <c r="C32" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="6">
-        <v>1</v>
-      </c>
-      <c r="E32" s="6">
+      <c r="D32" s="5">
+        <v>1</v>
+      </c>
+      <c r="E32" s="5">
         <v>1</v>
       </c>
       <c r="F32" t="s">
@@ -8050,10 +8095,10 @@
       <c r="C33" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="6">
-        <v>1</v>
-      </c>
-      <c r="E33" s="6">
+      <c r="D33" s="5">
+        <v>1</v>
+      </c>
+      <c r="E33" s="5">
         <v>1</v>
       </c>
       <c r="F33" t="s">
@@ -8085,10 +8130,10 @@
       <c r="C34" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="6">
-        <v>1</v>
-      </c>
-      <c r="E34" s="6">
+      <c r="D34" s="5">
+        <v>1</v>
+      </c>
+      <c r="E34" s="5">
         <v>1</v>
       </c>
       <c r="F34" t="s">
@@ -8120,10 +8165,10 @@
       <c r="C35" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D35" s="6">
-        <v>1</v>
-      </c>
-      <c r="E35" s="6">
+      <c r="D35" s="5">
+        <v>1</v>
+      </c>
+      <c r="E35" s="5">
         <v>1</v>
       </c>
       <c r="F35" t="s">
@@ -8155,10 +8200,10 @@
       <c r="C36" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="6">
-        <v>1</v>
-      </c>
-      <c r="E36" s="6">
+      <c r="D36" s="5">
+        <v>1</v>
+      </c>
+      <c r="E36" s="5">
         <v>1</v>
       </c>
       <c r="F36" t="s">
@@ -8190,10 +8235,10 @@
       <c r="C37" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D37" s="6">
-        <v>1</v>
-      </c>
-      <c r="E37" s="6">
+      <c r="D37" s="5">
+        <v>1</v>
+      </c>
+      <c r="E37" s="5">
         <v>1</v>
       </c>
       <c r="F37" t="s">
@@ -8225,10 +8270,10 @@
       <c r="C38" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D38" s="6">
-        <v>1</v>
-      </c>
-      <c r="E38" s="6">
+      <c r="D38" s="5">
+        <v>1</v>
+      </c>
+      <c r="E38" s="5">
         <v>1</v>
       </c>
       <c r="F38" t="s">
@@ -8260,10 +8305,10 @@
       <c r="C39" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="6">
-        <v>1</v>
-      </c>
-      <c r="E39" s="6">
+      <c r="D39" s="5">
+        <v>1</v>
+      </c>
+      <c r="E39" s="5">
         <v>1</v>
       </c>
       <c r="F39" t="s">
@@ -8295,10 +8340,10 @@
       <c r="C40" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D40" s="6">
-        <v>1</v>
-      </c>
-      <c r="E40" s="6">
+      <c r="D40" s="5">
+        <v>1</v>
+      </c>
+      <c r="E40" s="5">
         <v>1</v>
       </c>
       <c r="F40" t="s">
@@ -8330,10 +8375,10 @@
       <c r="C41" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D41" s="6">
-        <v>1</v>
-      </c>
-      <c r="E41" s="6">
+      <c r="D41" s="5">
+        <v>1</v>
+      </c>
+      <c r="E41" s="5">
         <v>1</v>
       </c>
       <c r="F41" t="s">
@@ -8365,10 +8410,10 @@
       <c r="C42" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D42" s="6">
-        <v>1</v>
-      </c>
-      <c r="E42" s="6">
+      <c r="D42" s="5">
+        <v>1</v>
+      </c>
+      <c r="E42" s="5">
         <v>1</v>
       </c>
       <c r="F42" t="s">
@@ -8400,10 +8445,10 @@
       <c r="C43" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D43" s="6">
-        <v>1</v>
-      </c>
-      <c r="E43" s="6">
+      <c r="D43" s="5">
+        <v>1</v>
+      </c>
+      <c r="E43" s="5">
         <v>1</v>
       </c>
       <c r="F43" t="s">
@@ -8435,10 +8480,10 @@
       <c r="C44" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D44" s="6">
-        <v>1</v>
-      </c>
-      <c r="E44" s="6">
+      <c r="D44" s="5">
+        <v>1</v>
+      </c>
+      <c r="E44" s="5">
         <v>1</v>
       </c>
       <c r="F44" t="s">
@@ -8470,10 +8515,10 @@
       <c r="C45" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D45" s="6">
-        <v>1</v>
-      </c>
-      <c r="E45" s="6">
+      <c r="D45" s="5">
+        <v>1</v>
+      </c>
+      <c r="E45" s="5">
         <v>1</v>
       </c>
       <c r="F45" t="s">
@@ -8505,10 +8550,10 @@
       <c r="C46" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D46" s="6">
-        <v>1</v>
-      </c>
-      <c r="E46" s="6">
+      <c r="D46" s="5">
+        <v>1</v>
+      </c>
+      <c r="E46" s="5">
         <v>1</v>
       </c>
       <c r="F46" t="s">
@@ -8540,10 +8585,10 @@
       <c r="C47" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D47" s="6">
-        <v>1</v>
-      </c>
-      <c r="E47" s="6">
+      <c r="D47" s="5">
+        <v>1</v>
+      </c>
+      <c r="E47" s="5">
         <v>1</v>
       </c>
       <c r="F47" t="s">
@@ -8575,10 +8620,10 @@
       <c r="C48" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D48" s="6">
-        <v>1</v>
-      </c>
-      <c r="E48" s="6">
+      <c r="D48" s="5">
+        <v>1</v>
+      </c>
+      <c r="E48" s="5">
         <v>1</v>
       </c>
       <c r="F48" t="s">
@@ -8610,10 +8655,10 @@
       <c r="C49" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D49" s="6">
-        <v>1</v>
-      </c>
-      <c r="E49" s="6">
+      <c r="D49" s="5">
+        <v>1</v>
+      </c>
+      <c r="E49" s="5">
         <v>1</v>
       </c>
       <c r="F49" t="s">
@@ -8645,10 +8690,10 @@
       <c r="C50" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D50" s="6">
-        <v>1</v>
-      </c>
-      <c r="E50" s="6">
+      <c r="D50" s="5">
+        <v>1</v>
+      </c>
+      <c r="E50" s="5">
         <v>1</v>
       </c>
       <c r="F50" t="s">
@@ -8680,10 +8725,10 @@
       <c r="C51" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D51" s="6">
-        <v>1</v>
-      </c>
-      <c r="E51" s="6">
+      <c r="D51" s="5">
+        <v>1</v>
+      </c>
+      <c r="E51" s="5">
         <v>1</v>
       </c>
       <c r="F51" t="s">
@@ -8715,10 +8760,10 @@
       <c r="C52" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D52" s="6">
-        <v>1</v>
-      </c>
-      <c r="E52" s="6">
+      <c r="D52" s="5">
+        <v>1</v>
+      </c>
+      <c r="E52" s="5">
         <v>1</v>
       </c>
       <c r="F52" t="s">
@@ -8750,10 +8795,10 @@
       <c r="C53" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D53" s="6">
-        <v>1</v>
-      </c>
-      <c r="E53" s="6">
+      <c r="D53" s="5">
+        <v>1</v>
+      </c>
+      <c r="E53" s="5">
         <v>1</v>
       </c>
       <c r="F53" t="s">
@@ -8785,10 +8830,10 @@
       <c r="C54" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D54" s="6">
-        <v>1</v>
-      </c>
-      <c r="E54" s="6">
+      <c r="D54" s="5">
+        <v>1</v>
+      </c>
+      <c r="E54" s="5">
         <v>1</v>
       </c>
       <c r="F54" t="s">
@@ -8820,10 +8865,10 @@
       <c r="C55" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D55" s="6">
-        <v>1</v>
-      </c>
-      <c r="E55" s="6">
+      <c r="D55" s="5">
+        <v>1</v>
+      </c>
+      <c r="E55" s="5">
         <v>1</v>
       </c>
       <c r="F55" t="s">
@@ -8855,10 +8900,10 @@
       <c r="C56" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D56" s="6">
-        <v>1</v>
-      </c>
-      <c r="E56" s="6">
+      <c r="D56" s="5">
+        <v>1</v>
+      </c>
+      <c r="E56" s="5">
         <v>1</v>
       </c>
       <c r="F56" t="s">
@@ -8890,10 +8935,10 @@
       <c r="C57" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D57" s="6">
-        <v>1</v>
-      </c>
-      <c r="E57" s="6">
+      <c r="D57" s="5">
+        <v>1</v>
+      </c>
+      <c r="E57" s="5">
         <v>1</v>
       </c>
       <c r="F57" t="s">
@@ -8925,10 +8970,10 @@
       <c r="C58" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D58" s="6">
-        <v>1</v>
-      </c>
-      <c r="E58" s="6">
+      <c r="D58" s="5">
+        <v>1</v>
+      </c>
+      <c r="E58" s="5">
         <v>1</v>
       </c>
       <c r="F58" t="s">
@@ -8960,10 +9005,10 @@
       <c r="C59" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D59" s="6">
-        <v>1</v>
-      </c>
-      <c r="E59" s="6">
+      <c r="D59" s="5">
+        <v>1</v>
+      </c>
+      <c r="E59" s="5">
         <v>1</v>
       </c>
       <c r="F59" t="s">
@@ -8995,10 +9040,10 @@
       <c r="C60" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D60" s="6">
-        <v>1</v>
-      </c>
-      <c r="E60" s="6">
+      <c r="D60" s="5">
+        <v>1</v>
+      </c>
+      <c r="E60" s="5">
         <v>1</v>
       </c>
       <c r="F60" t="s">
@@ -9030,10 +9075,10 @@
       <c r="C61" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D61" s="6">
-        <v>1</v>
-      </c>
-      <c r="E61" s="6">
+      <c r="D61" s="5">
+        <v>1</v>
+      </c>
+      <c r="E61" s="5">
         <v>1</v>
       </c>
       <c r="F61" t="s">
@@ -9065,10 +9110,10 @@
       <c r="C62" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D62" s="6">
-        <v>1</v>
-      </c>
-      <c r="E62" s="6">
+      <c r="D62" s="5">
+        <v>1</v>
+      </c>
+      <c r="E62" s="5">
         <v>1</v>
       </c>
       <c r="F62" t="s">
@@ -9100,10 +9145,10 @@
       <c r="C63" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D63" s="6">
-        <v>1</v>
-      </c>
-      <c r="E63" s="6">
+      <c r="D63" s="5">
+        <v>1</v>
+      </c>
+      <c r="E63" s="5">
         <v>1</v>
       </c>
       <c r="F63" t="s">
@@ -9135,10 +9180,10 @@
       <c r="C64" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D64" s="6">
-        <v>1</v>
-      </c>
-      <c r="E64" s="6">
+      <c r="D64" s="5">
+        <v>1</v>
+      </c>
+      <c r="E64" s="5">
         <v>1</v>
       </c>
       <c r="F64" t="s">
@@ -9170,10 +9215,10 @@
       <c r="C65" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D65" s="6">
-        <v>1</v>
-      </c>
-      <c r="E65" s="6">
+      <c r="D65" s="5">
+        <v>1</v>
+      </c>
+      <c r="E65" s="5">
         <v>1</v>
       </c>
       <c r="F65" t="s">
@@ -9205,10 +9250,10 @@
       <c r="C66" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D66" s="6">
-        <v>1</v>
-      </c>
-      <c r="E66" s="6">
+      <c r="D66" s="5">
+        <v>1</v>
+      </c>
+      <c r="E66" s="5">
         <v>1</v>
       </c>
       <c r="F66" t="s">
@@ -9240,10 +9285,10 @@
       <c r="C67" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D67" s="6">
-        <v>1</v>
-      </c>
-      <c r="E67" s="6">
+      <c r="D67" s="5">
+        <v>1</v>
+      </c>
+      <c r="E67" s="5">
         <v>1</v>
       </c>
       <c r="F67" t="s">
@@ -9275,10 +9320,10 @@
       <c r="C68" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D68" s="6">
-        <v>1</v>
-      </c>
-      <c r="E68" s="6">
+      <c r="D68" s="5">
+        <v>1</v>
+      </c>
+      <c r="E68" s="5">
         <v>1</v>
       </c>
       <c r="F68" t="s">
@@ -9310,10 +9355,10 @@
       <c r="C69" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D69" s="6">
-        <v>1</v>
-      </c>
-      <c r="E69" s="6">
+      <c r="D69" s="5">
+        <v>1</v>
+      </c>
+      <c r="E69" s="5">
         <v>1</v>
       </c>
       <c r="F69" t="s">
@@ -9345,10 +9390,10 @@
       <c r="C70" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D70" s="6">
-        <v>1</v>
-      </c>
-      <c r="E70" s="6">
+      <c r="D70" s="5">
+        <v>1</v>
+      </c>
+      <c r="E70" s="5">
         <v>1</v>
       </c>
       <c r="F70" t="s">
@@ -9380,10 +9425,10 @@
       <c r="C71" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D71" s="6">
-        <v>1</v>
-      </c>
-      <c r="E71" s="6">
+      <c r="D71" s="5">
+        <v>1</v>
+      </c>
+      <c r="E71" s="5">
         <v>1</v>
       </c>
       <c r="F71" t="s">
@@ -9415,10 +9460,10 @@
       <c r="C72" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D72" s="6">
-        <v>1</v>
-      </c>
-      <c r="E72" s="6">
+      <c r="D72" s="5">
+        <v>1</v>
+      </c>
+      <c r="E72" s="5">
         <v>1</v>
       </c>
       <c r="F72" t="s">
@@ -9450,10 +9495,10 @@
       <c r="C73" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D73" s="6">
-        <v>1</v>
-      </c>
-      <c r="E73" s="6">
+      <c r="D73" s="5">
+        <v>1</v>
+      </c>
+      <c r="E73" s="5">
         <v>1</v>
       </c>
       <c r="F73" t="s">
@@ -9485,10 +9530,10 @@
       <c r="C74" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D74" s="6">
-        <v>1</v>
-      </c>
-      <c r="E74" s="6">
+      <c r="D74" s="5">
+        <v>1</v>
+      </c>
+      <c r="E74" s="5">
         <v>1</v>
       </c>
       <c r="F74" t="s">
@@ -9520,10 +9565,10 @@
       <c r="C75" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D75" s="6">
-        <v>1</v>
-      </c>
-      <c r="E75" s="6">
+      <c r="D75" s="5">
+        <v>1</v>
+      </c>
+      <c r="E75" s="5">
         <v>1</v>
       </c>
       <c r="F75" t="s">
@@ -9555,10 +9600,10 @@
       <c r="C76" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D76" s="6">
-        <v>1</v>
-      </c>
-      <c r="E76" s="6">
+      <c r="D76" s="5">
+        <v>1</v>
+      </c>
+      <c r="E76" s="5">
         <v>1</v>
       </c>
       <c r="F76" t="s">
@@ -9590,10 +9635,10 @@
       <c r="C77" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D77" s="6">
-        <v>1</v>
-      </c>
-      <c r="E77" s="6">
+      <c r="D77" s="5">
+        <v>1</v>
+      </c>
+      <c r="E77" s="5">
         <v>1</v>
       </c>
       <c r="F77" t="s">
@@ -9625,10 +9670,10 @@
       <c r="C78" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D78" s="6">
-        <v>1</v>
-      </c>
-      <c r="E78" s="6">
+      <c r="D78" s="5">
+        <v>1</v>
+      </c>
+      <c r="E78" s="5">
         <v>1</v>
       </c>
       <c r="F78" t="s">
@@ -9660,10 +9705,10 @@
       <c r="C79" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D79" s="6">
-        <v>1</v>
-      </c>
-      <c r="E79" s="6">
+      <c r="D79" s="5">
+        <v>1</v>
+      </c>
+      <c r="E79" s="5">
         <v>1</v>
       </c>
       <c r="F79" t="s">
@@ -9695,10 +9740,10 @@
       <c r="C80" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D80" s="6">
-        <v>1</v>
-      </c>
-      <c r="E80" s="6">
+      <c r="D80" s="5">
+        <v>1</v>
+      </c>
+      <c r="E80" s="5">
         <v>1</v>
       </c>
       <c r="F80" t="s">
@@ -9730,10 +9775,10 @@
       <c r="C81" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D81" s="6">
-        <v>1</v>
-      </c>
-      <c r="E81" s="6">
+      <c r="D81" s="5">
+        <v>1</v>
+      </c>
+      <c r="E81" s="5">
         <v>1</v>
       </c>
       <c r="F81" t="s">
@@ -9765,10 +9810,10 @@
       <c r="C82" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D82" s="6">
-        <v>1</v>
-      </c>
-      <c r="E82" s="6">
+      <c r="D82" s="5">
+        <v>1</v>
+      </c>
+      <c r="E82" s="5">
         <v>1</v>
       </c>
       <c r="F82" t="s">
@@ -9800,10 +9845,10 @@
       <c r="C83" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D83" s="6">
-        <v>1</v>
-      </c>
-      <c r="E83" s="6">
+      <c r="D83" s="5">
+        <v>1</v>
+      </c>
+      <c r="E83" s="5">
         <v>1</v>
       </c>
       <c r="F83" t="s">
@@ -9835,10 +9880,10 @@
       <c r="C84" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D84" s="6">
-        <v>1</v>
-      </c>
-      <c r="E84" s="6">
+      <c r="D84" s="5">
+        <v>1</v>
+      </c>
+      <c r="E84" s="5">
         <v>1</v>
       </c>
       <c r="F84" t="s">
@@ -9870,10 +9915,10 @@
       <c r="C85" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D85" s="6">
-        <v>1</v>
-      </c>
-      <c r="E85" s="6">
+      <c r="D85" s="5">
+        <v>1</v>
+      </c>
+      <c r="E85" s="5">
         <v>1</v>
       </c>
       <c r="F85" t="s">
@@ -9905,10 +9950,10 @@
       <c r="C86" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D86" s="6">
-        <v>1</v>
-      </c>
-      <c r="E86" s="6">
+      <c r="D86" s="5">
+        <v>1</v>
+      </c>
+      <c r="E86" s="5">
         <v>1</v>
       </c>
       <c r="F86" t="s">
@@ -9940,10 +9985,10 @@
       <c r="C87" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D87" s="6">
-        <v>1</v>
-      </c>
-      <c r="E87" s="6">
+      <c r="D87" s="5">
+        <v>1</v>
+      </c>
+      <c r="E87" s="5">
         <v>1</v>
       </c>
       <c r="F87" t="s">
@@ -9975,10 +10020,10 @@
       <c r="C88" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D88" s="6">
-        <v>1</v>
-      </c>
-      <c r="E88" s="6">
+      <c r="D88" s="5">
+        <v>1</v>
+      </c>
+      <c r="E88" s="5">
         <v>1</v>
       </c>
       <c r="F88" t="s">
@@ -10010,10 +10055,10 @@
       <c r="C89" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D89" s="6">
-        <v>1</v>
-      </c>
-      <c r="E89" s="6">
+      <c r="D89" s="5">
+        <v>1</v>
+      </c>
+      <c r="E89" s="5">
         <v>1</v>
       </c>
       <c r="F89" t="s">
@@ -10045,10 +10090,10 @@
       <c r="C90" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D90" s="6">
-        <v>1</v>
-      </c>
-      <c r="E90" s="6">
+      <c r="D90" s="5">
+        <v>1</v>
+      </c>
+      <c r="E90" s="5">
         <v>1</v>
       </c>
       <c r="F90" t="s">
@@ -10080,10 +10125,10 @@
       <c r="C91" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D91" s="6">
-        <v>1</v>
-      </c>
-      <c r="E91" s="6">
+      <c r="D91" s="5">
+        <v>1</v>
+      </c>
+      <c r="E91" s="5">
         <v>1</v>
       </c>
       <c r="F91" t="s">
@@ -10115,10 +10160,10 @@
       <c r="C92" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D92" s="6">
-        <v>1</v>
-      </c>
-      <c r="E92" s="6">
+      <c r="D92" s="5">
+        <v>1</v>
+      </c>
+      <c r="E92" s="5">
         <v>1</v>
       </c>
       <c r="F92" t="s">
@@ -10150,10 +10195,10 @@
       <c r="C93" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D93" s="6">
-        <v>1</v>
-      </c>
-      <c r="E93" s="6">
+      <c r="D93" s="5">
+        <v>1</v>
+      </c>
+      <c r="E93" s="5">
         <v>1</v>
       </c>
       <c r="F93" t="s">
@@ -10185,10 +10230,10 @@
       <c r="C94" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D94" s="6">
-        <v>1</v>
-      </c>
-      <c r="E94" s="6">
+      <c r="D94" s="5">
+        <v>1</v>
+      </c>
+      <c r="E94" s="5">
         <v>1</v>
       </c>
       <c r="F94" t="s">
@@ -10220,10 +10265,10 @@
       <c r="C95" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D95" s="6">
-        <v>1</v>
-      </c>
-      <c r="E95" s="6">
+      <c r="D95" s="5">
+        <v>1</v>
+      </c>
+      <c r="E95" s="5">
         <v>1</v>
       </c>
       <c r="F95" t="s">
@@ -10255,10 +10300,10 @@
       <c r="C96" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D96" s="6">
-        <v>1</v>
-      </c>
-      <c r="E96" s="6">
+      <c r="D96" s="5">
+        <v>1</v>
+      </c>
+      <c r="E96" s="5">
         <v>1</v>
       </c>
       <c r="F96" t="s">
@@ -10290,10 +10335,10 @@
       <c r="C97" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D97" s="6">
-        <v>1</v>
-      </c>
-      <c r="E97" s="6">
+      <c r="D97" s="5">
+        <v>1</v>
+      </c>
+      <c r="E97" s="5">
         <v>1</v>
       </c>
       <c r="F97" t="s">
@@ -10325,10 +10370,10 @@
       <c r="C98" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D98" s="6">
-        <v>1</v>
-      </c>
-      <c r="E98" s="6">
+      <c r="D98" s="5">
+        <v>1</v>
+      </c>
+      <c r="E98" s="5">
         <v>1</v>
       </c>
       <c r="F98" t="s">
@@ -10360,10 +10405,10 @@
       <c r="C99" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D99" s="6">
-        <v>1</v>
-      </c>
-      <c r="E99" s="6">
+      <c r="D99" s="5">
+        <v>1</v>
+      </c>
+      <c r="E99" s="5">
         <v>1</v>
       </c>
       <c r="F99" t="s">
@@ -10395,10 +10440,10 @@
       <c r="C100" s="4" t="s">
         <v>2022</v>
       </c>
-      <c r="D100" s="6">
-        <v>1</v>
-      </c>
-      <c r="E100" s="6">
+      <c r="D100" s="5">
+        <v>1</v>
+      </c>
+      <c r="E100" s="5">
         <v>1</v>
       </c>
       <c r="F100" t="s">
@@ -10430,10 +10475,10 @@
       <c r="C101" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D101" s="6">
-        <v>1</v>
-      </c>
-      <c r="E101" s="6">
+      <c r="D101" s="5">
+        <v>1</v>
+      </c>
+      <c r="E101" s="5">
         <v>1</v>
       </c>
       <c r="F101" t="s">
@@ -10465,10 +10510,10 @@
       <c r="C102" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D102" s="6">
-        <v>1</v>
-      </c>
-      <c r="E102" s="6">
+      <c r="D102" s="5">
+        <v>1</v>
+      </c>
+      <c r="E102" s="5">
         <v>1</v>
       </c>
       <c r="F102" t="s">
@@ -10500,10 +10545,10 @@
       <c r="C103" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D103" s="6">
-        <v>1</v>
-      </c>
-      <c r="E103" s="6">
+      <c r="D103" s="5">
+        <v>1</v>
+      </c>
+      <c r="E103" s="5">
         <v>1</v>
       </c>
       <c r="F103" t="s">
@@ -10535,10 +10580,10 @@
       <c r="C104" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D104" s="6">
-        <v>1</v>
-      </c>
-      <c r="E104" s="6">
+      <c r="D104" s="5">
+        <v>1</v>
+      </c>
+      <c r="E104" s="5">
         <v>1</v>
       </c>
       <c r="F104" t="s">
@@ -10570,10 +10615,10 @@
       <c r="C105" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D105" s="6">
-        <v>1</v>
-      </c>
-      <c r="E105" s="6">
+      <c r="D105" s="5">
+        <v>1</v>
+      </c>
+      <c r="E105" s="5">
         <v>1</v>
       </c>
       <c r="F105" t="s">
@@ -10605,10 +10650,10 @@
       <c r="C106" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D106" s="6">
-        <v>1</v>
-      </c>
-      <c r="E106" s="6">
+      <c r="D106" s="5">
+        <v>1</v>
+      </c>
+      <c r="E106" s="5">
         <v>1</v>
       </c>
       <c r="F106" t="s">
@@ -10640,10 +10685,10 @@
       <c r="C107" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D107" s="6">
-        <v>1</v>
-      </c>
-      <c r="E107" s="6">
+      <c r="D107" s="5">
+        <v>1</v>
+      </c>
+      <c r="E107" s="5">
         <v>1</v>
       </c>
       <c r="F107" t="s">
@@ -10675,10 +10720,10 @@
       <c r="C108" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D108" s="6">
-        <v>1</v>
-      </c>
-      <c r="E108" s="6">
+      <c r="D108" s="5">
+        <v>1</v>
+      </c>
+      <c r="E108" s="5">
         <v>1</v>
       </c>
       <c r="F108" t="s">
@@ -10710,10 +10755,10 @@
       <c r="C109" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D109" s="6">
-        <v>1</v>
-      </c>
-      <c r="E109" s="6">
+      <c r="D109" s="5">
+        <v>1</v>
+      </c>
+      <c r="E109" s="5">
         <v>1</v>
       </c>
       <c r="F109" t="s">
@@ -10745,10 +10790,10 @@
       <c r="C110" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D110" s="6">
-        <v>1</v>
-      </c>
-      <c r="E110" s="6">
+      <c r="D110" s="5">
+        <v>1</v>
+      </c>
+      <c r="E110" s="5">
         <v>1</v>
       </c>
       <c r="F110" t="s">
@@ -10780,10 +10825,10 @@
       <c r="C111" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D111" s="6">
-        <v>1</v>
-      </c>
-      <c r="E111" s="6">
+      <c r="D111" s="5">
+        <v>1</v>
+      </c>
+      <c r="E111" s="5">
         <v>1</v>
       </c>
       <c r="F111" t="s">
@@ -10815,10 +10860,10 @@
       <c r="C112" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D112" s="6">
-        <v>1</v>
-      </c>
-      <c r="E112" s="6">
+      <c r="D112" s="5">
+        <v>1</v>
+      </c>
+      <c r="E112" s="5">
         <v>1</v>
       </c>
       <c r="F112" t="s">
@@ -10850,10 +10895,10 @@
       <c r="C113" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D113" s="6">
-        <v>1</v>
-      </c>
-      <c r="E113" s="6">
+      <c r="D113" s="5">
+        <v>1</v>
+      </c>
+      <c r="E113" s="5">
         <v>1</v>
       </c>
       <c r="F113" t="s">
@@ -10885,10 +10930,10 @@
       <c r="C114" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D114" s="6">
-        <v>1</v>
-      </c>
-      <c r="E114" s="6">
+      <c r="D114" s="5">
+        <v>1</v>
+      </c>
+      <c r="E114" s="5">
         <v>1</v>
       </c>
       <c r="F114" t="s">
@@ -10920,10 +10965,10 @@
       <c r="C115" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D115" s="6">
-        <v>1</v>
-      </c>
-      <c r="E115" s="6">
+      <c r="D115" s="5">
+        <v>1</v>
+      </c>
+      <c r="E115" s="5">
         <v>1</v>
       </c>
       <c r="F115" t="s">
@@ -10955,10 +11000,10 @@
       <c r="C116" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D116" s="6">
-        <v>1</v>
-      </c>
-      <c r="E116" s="6">
+      <c r="D116" s="5">
+        <v>1</v>
+      </c>
+      <c r="E116" s="5">
         <v>1</v>
       </c>
       <c r="F116" t="s">
@@ -10999,10 +11044,10 @@
       <c r="C118" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D118" s="6">
-        <v>1</v>
-      </c>
-      <c r="E118" s="6">
+      <c r="D118" s="5">
+        <v>1</v>
+      </c>
+      <c r="E118" s="5">
         <v>1</v>
       </c>
       <c r="F118" t="s">
@@ -11034,10 +11079,10 @@
       <c r="C119" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D119" s="6">
-        <v>1</v>
-      </c>
-      <c r="E119" s="6">
+      <c r="D119" s="5">
+        <v>1</v>
+      </c>
+      <c r="E119" s="5">
         <v>1</v>
       </c>
       <c r="F119" t="s">
@@ -11069,10 +11114,10 @@
       <c r="C120" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D120" s="6">
-        <v>1</v>
-      </c>
-      <c r="E120" s="6">
+      <c r="D120" s="5">
+        <v>1</v>
+      </c>
+      <c r="E120" s="5">
         <v>1</v>
       </c>
       <c r="F120" t="s">
@@ -11104,10 +11149,10 @@
       <c r="C121" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D121" s="6">
-        <v>1</v>
-      </c>
-      <c r="E121" s="6">
+      <c r="D121" s="5">
+        <v>1</v>
+      </c>
+      <c r="E121" s="5">
         <v>1</v>
       </c>
       <c r="F121" t="s">
@@ -11139,10 +11184,10 @@
       <c r="C122" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D122" s="6">
-        <v>1</v>
-      </c>
-      <c r="E122" s="6">
+      <c r="D122" s="5">
+        <v>1</v>
+      </c>
+      <c r="E122" s="5">
         <v>1</v>
       </c>
       <c r="F122" t="s">
@@ -11174,10 +11219,10 @@
       <c r="C123" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D123" s="6">
-        <v>1</v>
-      </c>
-      <c r="E123" s="6">
+      <c r="D123" s="5">
+        <v>1</v>
+      </c>
+      <c r="E123" s="5">
         <v>1</v>
       </c>
       <c r="F123" t="s">
@@ -11209,10 +11254,10 @@
       <c r="C124" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D124" s="6">
-        <v>1</v>
-      </c>
-      <c r="E124" s="6">
+      <c r="D124" s="5">
+        <v>1</v>
+      </c>
+      <c r="E124" s="5">
         <v>1</v>
       </c>
       <c r="F124" t="s">
@@ -11244,10 +11289,10 @@
       <c r="C125" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D125" s="6">
-        <v>1</v>
-      </c>
-      <c r="E125" s="6">
+      <c r="D125" s="5">
+        <v>1</v>
+      </c>
+      <c r="E125" s="5">
         <v>1</v>
       </c>
       <c r="F125" t="s">
@@ -11279,10 +11324,10 @@
       <c r="C126" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D126" s="6">
-        <v>1</v>
-      </c>
-      <c r="E126" s="6">
+      <c r="D126" s="5">
+        <v>1</v>
+      </c>
+      <c r="E126" s="5">
         <v>1</v>
       </c>
       <c r="F126" t="s">
@@ -11314,10 +11359,10 @@
       <c r="C127" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D127" s="6">
-        <v>1</v>
-      </c>
-      <c r="E127" s="6">
+      <c r="D127" s="5">
+        <v>1</v>
+      </c>
+      <c r="E127" s="5">
         <v>1</v>
       </c>
       <c r="F127" t="s">
@@ -11349,10 +11394,10 @@
       <c r="C128" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D128" s="6">
-        <v>1</v>
-      </c>
-      <c r="E128" s="6">
+      <c r="D128" s="5">
+        <v>1</v>
+      </c>
+      <c r="E128" s="5">
         <v>1</v>
       </c>
       <c r="F128" t="s">
@@ -11384,10 +11429,10 @@
       <c r="C129" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D129" s="6">
-        <v>1</v>
-      </c>
-      <c r="E129" s="6">
+      <c r="D129" s="5">
+        <v>1</v>
+      </c>
+      <c r="E129" s="5">
         <v>1</v>
       </c>
       <c r="F129" t="s">
@@ -11419,10 +11464,10 @@
       <c r="C130" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D130" s="6">
-        <v>1</v>
-      </c>
-      <c r="E130" s="6">
+      <c r="D130" s="5">
+        <v>1</v>
+      </c>
+      <c r="E130" s="5">
         <v>1</v>
       </c>
       <c r="F130" t="s">
@@ -11454,10 +11499,10 @@
       <c r="C131" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D131" s="6">
-        <v>1</v>
-      </c>
-      <c r="E131" s="6">
+      <c r="D131" s="5">
+        <v>1</v>
+      </c>
+      <c r="E131" s="5">
         <v>1</v>
       </c>
       <c r="F131" t="s">
@@ -11489,10 +11534,10 @@
       <c r="C132" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D132" s="6">
-        <v>1</v>
-      </c>
-      <c r="E132" s="6">
+      <c r="D132" s="5">
+        <v>1</v>
+      </c>
+      <c r="E132" s="5">
         <v>1</v>
       </c>
       <c r="F132" t="s">
@@ -11524,10 +11569,10 @@
       <c r="C133" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D133" s="6">
-        <v>1</v>
-      </c>
-      <c r="E133" s="6">
+      <c r="D133" s="5">
+        <v>1</v>
+      </c>
+      <c r="E133" s="5">
         <v>1</v>
       </c>
       <c r="F133" t="s">
@@ -11559,10 +11604,10 @@
       <c r="C134" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D134" s="6">
-        <v>1</v>
-      </c>
-      <c r="E134" s="6">
+      <c r="D134" s="5">
+        <v>1</v>
+      </c>
+      <c r="E134" s="5">
         <v>1</v>
       </c>
       <c r="F134" t="s">
@@ -11594,10 +11639,10 @@
       <c r="C135" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D135" s="6">
-        <v>1</v>
-      </c>
-      <c r="E135" s="6">
+      <c r="D135" s="5">
+        <v>1</v>
+      </c>
+      <c r="E135" s="5">
         <v>1</v>
       </c>
       <c r="F135" t="s">
@@ -11629,10 +11674,10 @@
       <c r="C136" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D136" s="6">
-        <v>1</v>
-      </c>
-      <c r="E136" s="6">
+      <c r="D136" s="5">
+        <v>1</v>
+      </c>
+      <c r="E136" s="5">
         <v>1</v>
       </c>
       <c r="F136" t="s">
@@ -11664,10 +11709,10 @@
       <c r="C137" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D137" s="6">
-        <v>1</v>
-      </c>
-      <c r="E137" s="6">
+      <c r="D137" s="5">
+        <v>1</v>
+      </c>
+      <c r="E137" s="5">
         <v>1</v>
       </c>
       <c r="F137" t="s">
@@ -11699,10 +11744,10 @@
       <c r="C138" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D138" s="6">
-        <v>1</v>
-      </c>
-      <c r="E138" s="6">
+      <c r="D138" s="5">
+        <v>1</v>
+      </c>
+      <c r="E138" s="5">
         <v>1</v>
       </c>
       <c r="F138" t="s">
@@ -11734,10 +11779,10 @@
       <c r="C139" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D139" s="6">
-        <v>1</v>
-      </c>
-      <c r="E139" s="6">
+      <c r="D139" s="5">
+        <v>1</v>
+      </c>
+      <c r="E139" s="5">
         <v>1</v>
       </c>
       <c r="F139" t="s">
@@ -11769,10 +11814,10 @@
       <c r="C140" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D140" s="6">
-        <v>1</v>
-      </c>
-      <c r="E140" s="6">
+      <c r="D140" s="5">
+        <v>1</v>
+      </c>
+      <c r="E140" s="5">
         <v>1</v>
       </c>
       <c r="F140" t="s">
@@ -11804,10 +11849,10 @@
       <c r="C141" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D141" s="6">
-        <v>1</v>
-      </c>
-      <c r="E141" s="6">
+      <c r="D141" s="5">
+        <v>1</v>
+      </c>
+      <c r="E141" s="5">
         <v>1</v>
       </c>
       <c r="F141" t="s">
@@ -11839,10 +11884,10 @@
       <c r="C142" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D142" s="6">
-        <v>1</v>
-      </c>
-      <c r="E142" s="6">
+      <c r="D142" s="5">
+        <v>1</v>
+      </c>
+      <c r="E142" s="5">
         <v>1</v>
       </c>
       <c r="F142" t="s">
@@ -11874,10 +11919,10 @@
       <c r="C143" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D143" s="6">
-        <v>1</v>
-      </c>
-      <c r="E143" s="6">
+      <c r="D143" s="5">
+        <v>1</v>
+      </c>
+      <c r="E143" s="5">
         <v>1</v>
       </c>
       <c r="F143" t="s">
@@ -11909,10 +11954,10 @@
       <c r="C144" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D144" s="6">
-        <v>1</v>
-      </c>
-      <c r="E144" s="6">
+      <c r="D144" s="5">
+        <v>1</v>
+      </c>
+      <c r="E144" s="5">
         <v>1</v>
       </c>
       <c r="F144" t="s">
@@ -11944,10 +11989,10 @@
       <c r="C145" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D145" s="6">
-        <v>1</v>
-      </c>
-      <c r="E145" s="6">
+      <c r="D145" s="5">
+        <v>1</v>
+      </c>
+      <c r="E145" s="5">
         <v>1</v>
       </c>
       <c r="F145" t="s">
@@ -11979,10 +12024,10 @@
       <c r="C146" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D146" s="6">
-        <v>1</v>
-      </c>
-      <c r="E146" s="6">
+      <c r="D146" s="5">
+        <v>1</v>
+      </c>
+      <c r="E146" s="5">
         <v>1</v>
       </c>
       <c r="F146" t="s">
@@ -12014,10 +12059,10 @@
       <c r="C147" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D147" s="6">
-        <v>1</v>
-      </c>
-      <c r="E147" s="6">
+      <c r="D147" s="5">
+        <v>1</v>
+      </c>
+      <c r="E147" s="5">
         <v>1</v>
       </c>
       <c r="F147" t="s">
@@ -12049,10 +12094,10 @@
       <c r="C148" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D148" s="6">
-        <v>1</v>
-      </c>
-      <c r="E148" s="6">
+      <c r="D148" s="5">
+        <v>1</v>
+      </c>
+      <c r="E148" s="5">
         <v>1</v>
       </c>
       <c r="F148" t="s">
@@ -12084,10 +12129,10 @@
       <c r="C149" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D149" s="6">
-        <v>1</v>
-      </c>
-      <c r="E149" s="6">
+      <c r="D149" s="5">
+        <v>1</v>
+      </c>
+      <c r="E149" s="5">
         <v>1</v>
       </c>
       <c r="F149" t="s">
@@ -12119,10 +12164,10 @@
       <c r="C150" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D150" s="6">
-        <v>1</v>
-      </c>
-      <c r="E150" s="6">
+      <c r="D150" s="5">
+        <v>1</v>
+      </c>
+      <c r="E150" s="5">
         <v>1</v>
       </c>
       <c r="F150" t="s">
@@ -12154,10 +12199,10 @@
       <c r="C151" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="D151" s="6">
-        <v>1</v>
-      </c>
-      <c r="E151" s="6">
+      <c r="D151" s="5">
+        <v>1</v>
+      </c>
+      <c r="E151" s="5">
         <v>1</v>
       </c>
       <c r="F151" t="s">
@@ -12189,10 +12234,10 @@
       <c r="C152" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D152" s="6">
-        <v>1</v>
-      </c>
-      <c r="E152" s="6">
+      <c r="D152" s="5">
+        <v>1</v>
+      </c>
+      <c r="E152" s="5">
         <v>1</v>
       </c>
       <c r="F152" t="s">
@@ -12224,10 +12269,10 @@
       <c r="C153" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D153" s="6">
-        <v>1</v>
-      </c>
-      <c r="E153" s="6">
+      <c r="D153" s="5">
+        <v>1</v>
+      </c>
+      <c r="E153" s="5">
         <v>1</v>
       </c>
       <c r="F153" t="s">
@@ -12259,10 +12304,10 @@
       <c r="C154" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D154" s="6">
-        <v>1</v>
-      </c>
-      <c r="E154" s="6">
+      <c r="D154" s="5">
+        <v>1</v>
+      </c>
+      <c r="E154" s="5">
         <v>1</v>
       </c>
       <c r="F154" t="s">
@@ -12294,10 +12339,10 @@
       <c r="C155" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D155" s="6">
-        <v>1</v>
-      </c>
-      <c r="E155" s="6">
+      <c r="D155" s="5">
+        <v>1</v>
+      </c>
+      <c r="E155" s="5">
         <v>1</v>
       </c>
       <c r="F155" t="s">
@@ -12329,10 +12374,10 @@
       <c r="C156" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D156" s="6">
-        <v>1</v>
-      </c>
-      <c r="E156" s="6">
+      <c r="D156" s="5">
+        <v>1</v>
+      </c>
+      <c r="E156" s="5">
         <v>1</v>
       </c>
       <c r="F156" t="s">
@@ -12364,10 +12409,10 @@
       <c r="C157" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D157" s="6">
-        <v>1</v>
-      </c>
-      <c r="E157" s="6">
+      <c r="D157" s="5">
+        <v>1</v>
+      </c>
+      <c r="E157" s="5">
         <v>1</v>
       </c>
       <c r="F157" t="s">
@@ -12399,10 +12444,10 @@
       <c r="C158" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D158" s="6">
-        <v>1</v>
-      </c>
-      <c r="E158" s="6">
+      <c r="D158" s="5">
+        <v>1</v>
+      </c>
+      <c r="E158" s="5">
         <v>1</v>
       </c>
       <c r="F158" t="s">
@@ -12434,10 +12479,10 @@
       <c r="C159" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D159" s="6">
-        <v>1</v>
-      </c>
-      <c r="E159" s="6">
+      <c r="D159" s="5">
+        <v>1</v>
+      </c>
+      <c r="E159" s="5">
         <v>1</v>
       </c>
       <c r="F159" t="s">
@@ -12469,10 +12514,10 @@
       <c r="C160" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D160" s="6">
-        <v>1</v>
-      </c>
-      <c r="E160" s="6">
+      <c r="D160" s="5">
+        <v>1</v>
+      </c>
+      <c r="E160" s="5">
         <v>1</v>
       </c>
       <c r="F160" t="s">
@@ -12504,10 +12549,10 @@
       <c r="C161" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D161" s="6">
-        <v>1</v>
-      </c>
-      <c r="E161" s="6">
+      <c r="D161" s="5">
+        <v>1</v>
+      </c>
+      <c r="E161" s="5">
         <v>1</v>
       </c>
       <c r="F161" t="s">
@@ -12539,10 +12584,10 @@
       <c r="C162" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D162" s="6">
-        <v>1</v>
-      </c>
-      <c r="E162" s="6">
+      <c r="D162" s="5">
+        <v>1</v>
+      </c>
+      <c r="E162" s="5">
         <v>1</v>
       </c>
       <c r="F162" t="s">
@@ -12574,10 +12619,10 @@
       <c r="C163" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D163" s="6">
-        <v>1</v>
-      </c>
-      <c r="E163" s="6">
+      <c r="D163" s="5">
+        <v>1</v>
+      </c>
+      <c r="E163" s="5">
         <v>1</v>
       </c>
       <c r="F163" t="s">
@@ -12609,10 +12654,10 @@
       <c r="C164" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D164" s="6">
-        <v>1</v>
-      </c>
-      <c r="E164" s="6">
+      <c r="D164" s="5">
+        <v>1</v>
+      </c>
+      <c r="E164" s="5">
         <v>1</v>
       </c>
       <c r="F164" t="s">
@@ -12644,10 +12689,10 @@
       <c r="C165" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D165" s="6">
-        <v>1</v>
-      </c>
-      <c r="E165" s="6">
+      <c r="D165" s="5">
+        <v>1</v>
+      </c>
+      <c r="E165" s="5">
         <v>1</v>
       </c>
       <c r="F165" t="s">
@@ -12679,10 +12724,10 @@
       <c r="C166" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D166" s="6">
-        <v>1</v>
-      </c>
-      <c r="E166" s="6">
+      <c r="D166" s="5">
+        <v>1</v>
+      </c>
+      <c r="E166" s="5">
         <v>1</v>
       </c>
       <c r="F166" t="s">
@@ -12714,10 +12759,10 @@
       <c r="C167" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D167" s="6">
-        <v>1</v>
-      </c>
-      <c r="E167" s="6">
+      <c r="D167" s="5">
+        <v>1</v>
+      </c>
+      <c r="E167" s="5">
         <v>1</v>
       </c>
       <c r="F167" t="s">
@@ -12749,10 +12794,10 @@
       <c r="C168" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D168" s="6">
-        <v>1</v>
-      </c>
-      <c r="E168" s="6">
+      <c r="D168" s="5">
+        <v>1</v>
+      </c>
+      <c r="E168" s="5">
         <v>1</v>
       </c>
       <c r="F168" t="s">
@@ -12784,10 +12829,10 @@
       <c r="C169" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D169" s="6">
-        <v>1</v>
-      </c>
-      <c r="E169" s="6">
+      <c r="D169" s="5">
+        <v>1</v>
+      </c>
+      <c r="E169" s="5">
         <v>1</v>
       </c>
       <c r="F169" t="s">
@@ -12819,10 +12864,10 @@
       <c r="C170" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D170" s="6">
-        <v>1</v>
-      </c>
-      <c r="E170" s="6">
+      <c r="D170" s="5">
+        <v>1</v>
+      </c>
+      <c r="E170" s="5">
         <v>1</v>
       </c>
       <c r="F170" t="s">
@@ -12854,10 +12899,10 @@
       <c r="C171" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D171" s="6">
-        <v>1</v>
-      </c>
-      <c r="E171" s="6">
+      <c r="D171" s="5">
+        <v>1</v>
+      </c>
+      <c r="E171" s="5">
         <v>1</v>
       </c>
       <c r="F171" t="s">
@@ -12889,10 +12934,10 @@
       <c r="C172" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D172" s="6">
-        <v>1</v>
-      </c>
-      <c r="E172" s="6">
+      <c r="D172" s="5">
+        <v>1</v>
+      </c>
+      <c r="E172" s="5">
         <v>1</v>
       </c>
       <c r="F172" t="s">
@@ -12924,10 +12969,10 @@
       <c r="C173" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D173" s="6">
-        <v>1</v>
-      </c>
-      <c r="E173" s="6">
+      <c r="D173" s="5">
+        <v>1</v>
+      </c>
+      <c r="E173" s="5">
         <v>1</v>
       </c>
       <c r="F173" t="s">
@@ -12959,10 +13004,10 @@
       <c r="C174" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D174" s="6">
-        <v>1</v>
-      </c>
-      <c r="E174" s="6">
+      <c r="D174" s="5">
+        <v>1</v>
+      </c>
+      <c r="E174" s="5">
         <v>1</v>
       </c>
       <c r="F174" t="s">
@@ -12994,10 +13039,10 @@
       <c r="C175" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D175" s="6">
-        <v>1</v>
-      </c>
-      <c r="E175" s="6">
+      <c r="D175" s="5">
+        <v>1</v>
+      </c>
+      <c r="E175" s="5">
         <v>1</v>
       </c>
       <c r="F175" t="s">
@@ -13029,10 +13074,10 @@
       <c r="C176" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D176" s="6">
-        <v>1</v>
-      </c>
-      <c r="E176" s="6">
+      <c r="D176" s="5">
+        <v>1</v>
+      </c>
+      <c r="E176" s="5">
         <v>1</v>
       </c>
       <c r="F176" t="s">
@@ -13064,10 +13109,10 @@
       <c r="C177" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D177" s="6">
-        <v>1</v>
-      </c>
-      <c r="E177" s="6">
+      <c r="D177" s="5">
+        <v>1</v>
+      </c>
+      <c r="E177" s="5">
         <v>1</v>
       </c>
       <c r="F177" t="s">
@@ -13099,10 +13144,10 @@
       <c r="C178" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D178" s="6">
-        <v>1</v>
-      </c>
-      <c r="E178" s="6">
+      <c r="D178" s="5">
+        <v>1</v>
+      </c>
+      <c r="E178" s="5">
         <v>1</v>
       </c>
       <c r="F178" t="s">
@@ -13134,10 +13179,10 @@
       <c r="C179" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D179" s="6">
-        <v>1</v>
-      </c>
-      <c r="E179" s="6">
+      <c r="D179" s="5">
+        <v>1</v>
+      </c>
+      <c r="E179" s="5">
         <v>1</v>
       </c>
       <c r="F179" t="s">
@@ -13169,10 +13214,10 @@
       <c r="C180" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D180" s="6">
-        <v>1</v>
-      </c>
-      <c r="E180" s="6">
+      <c r="D180" s="5">
+        <v>1</v>
+      </c>
+      <c r="E180" s="5">
         <v>1</v>
       </c>
       <c r="F180" t="s">
@@ -13204,10 +13249,10 @@
       <c r="C181" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D181" s="6">
-        <v>1</v>
-      </c>
-      <c r="E181" s="6">
+      <c r="D181" s="5">
+        <v>1</v>
+      </c>
+      <c r="E181" s="5">
         <v>1</v>
       </c>
       <c r="F181" t="s">
@@ -13239,10 +13284,10 @@
       <c r="C182" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D182" s="6">
-        <v>1</v>
-      </c>
-      <c r="E182" s="6">
+      <c r="D182" s="5">
+        <v>1</v>
+      </c>
+      <c r="E182" s="5">
         <v>1</v>
       </c>
       <c r="F182" t="s">
@@ -13274,10 +13319,10 @@
       <c r="C183" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D183" s="6">
-        <v>1</v>
-      </c>
-      <c r="E183" s="6">
+      <c r="D183" s="5">
+        <v>1</v>
+      </c>
+      <c r="E183" s="5">
         <v>1</v>
       </c>
       <c r="F183" t="s">
@@ -13309,10 +13354,10 @@
       <c r="C184" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D184" s="6">
-        <v>1</v>
-      </c>
-      <c r="E184" s="6">
+      <c r="D184" s="5">
+        <v>1</v>
+      </c>
+      <c r="E184" s="5">
         <v>1</v>
       </c>
       <c r="F184" t="s">
@@ -13344,10 +13389,10 @@
       <c r="C185" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D185" s="6">
-        <v>1</v>
-      </c>
-      <c r="E185" s="6">
+      <c r="D185" s="5">
+        <v>1</v>
+      </c>
+      <c r="E185" s="5">
         <v>1</v>
       </c>
       <c r="F185" t="s">
@@ -13379,10 +13424,10 @@
       <c r="C186" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D186" s="6">
-        <v>1</v>
-      </c>
-      <c r="E186" s="6">
+      <c r="D186" s="5">
+        <v>1</v>
+      </c>
+      <c r="E186" s="5">
         <v>1</v>
       </c>
       <c r="F186" t="s">
@@ -13414,10 +13459,10 @@
       <c r="C187" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D187" s="6">
-        <v>1</v>
-      </c>
-      <c r="E187" s="6">
+      <c r="D187" s="5">
+        <v>1</v>
+      </c>
+      <c r="E187" s="5">
         <v>1</v>
       </c>
       <c r="F187" t="s">
@@ -13449,10 +13494,10 @@
       <c r="C188" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D188" s="6">
-        <v>1</v>
-      </c>
-      <c r="E188" s="6">
+      <c r="D188" s="5">
+        <v>1</v>
+      </c>
+      <c r="E188" s="5">
         <v>1</v>
       </c>
       <c r="F188" t="s">
@@ -13484,10 +13529,10 @@
       <c r="C189" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D189" s="6">
-        <v>1</v>
-      </c>
-      <c r="E189" s="6">
+      <c r="D189" s="5">
+        <v>1</v>
+      </c>
+      <c r="E189" s="5">
         <v>1</v>
       </c>
       <c r="F189" t="s">
@@ -13519,10 +13564,10 @@
       <c r="C190" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D190" s="6">
-        <v>1</v>
-      </c>
-      <c r="E190" s="6">
+      <c r="D190" s="5">
+        <v>1</v>
+      </c>
+      <c r="E190" s="5">
         <v>1</v>
       </c>
       <c r="F190" t="s">
@@ -13554,10 +13599,10 @@
       <c r="C191" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D191" s="6">
-        <v>1</v>
-      </c>
-      <c r="E191" s="6">
+      <c r="D191" s="5">
+        <v>1</v>
+      </c>
+      <c r="E191" s="5">
         <v>1</v>
       </c>
       <c r="F191" t="s">
@@ -13589,10 +13634,10 @@
       <c r="C192" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D192" s="6">
-        <v>1</v>
-      </c>
-      <c r="E192" s="6">
+      <c r="D192" s="5">
+        <v>1</v>
+      </c>
+      <c r="E192" s="5">
         <v>1</v>
       </c>
       <c r="F192" t="s">
@@ -13624,10 +13669,10 @@
       <c r="C193" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D193" s="6">
-        <v>1</v>
-      </c>
-      <c r="E193" s="6">
+      <c r="D193" s="5">
+        <v>1</v>
+      </c>
+      <c r="E193" s="5">
         <v>1</v>
       </c>
       <c r="F193" t="s">
@@ -13659,10 +13704,10 @@
       <c r="C194" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D194" s="6">
-        <v>1</v>
-      </c>
-      <c r="E194" s="6">
+      <c r="D194" s="5">
+        <v>1</v>
+      </c>
+      <c r="E194" s="5">
         <v>1</v>
       </c>
       <c r="F194" t="s">
@@ -13694,10 +13739,10 @@
       <c r="C195" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D195" s="6">
-        <v>1</v>
-      </c>
-      <c r="E195" s="6">
+      <c r="D195" s="5">
+        <v>1</v>
+      </c>
+      <c r="E195" s="5">
         <v>1</v>
       </c>
       <c r="F195" t="s">
@@ -13729,10 +13774,10 @@
       <c r="C196" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D196" s="6">
-        <v>1</v>
-      </c>
-      <c r="E196" s="6">
+      <c r="D196" s="5">
+        <v>1</v>
+      </c>
+      <c r="E196" s="5">
         <v>1</v>
       </c>
       <c r="F196" t="s">
@@ -13764,10 +13809,10 @@
       <c r="C197" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D197" s="6">
-        <v>1</v>
-      </c>
-      <c r="E197" s="6">
+      <c r="D197" s="5">
+        <v>1</v>
+      </c>
+      <c r="E197" s="5">
         <v>1</v>
       </c>
       <c r="F197" t="s">
@@ -13799,10 +13844,10 @@
       <c r="C198" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D198" s="6">
-        <v>1</v>
-      </c>
-      <c r="E198" s="6">
+      <c r="D198" s="5">
+        <v>1</v>
+      </c>
+      <c r="E198" s="5">
         <v>1</v>
       </c>
       <c r="F198" t="s">
@@ -13834,10 +13879,10 @@
       <c r="C199" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D199" s="6">
-        <v>1</v>
-      </c>
-      <c r="E199" s="6">
+      <c r="D199" s="5">
+        <v>1</v>
+      </c>
+      <c r="E199" s="5">
         <v>1</v>
       </c>
       <c r="F199" t="s">
@@ -13869,10 +13914,10 @@
       <c r="C200" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D200" s="6">
-        <v>1</v>
-      </c>
-      <c r="E200" s="6">
+      <c r="D200" s="5">
+        <v>1</v>
+      </c>
+      <c r="E200" s="5">
         <v>1</v>
       </c>
       <c r="F200" t="s">
@@ -13904,10 +13949,10 @@
       <c r="C201" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="D201" s="6">
-        <v>1</v>
-      </c>
-      <c r="E201" s="6">
+      <c r="D201" s="5">
+        <v>1</v>
+      </c>
+      <c r="E201" s="5">
         <v>1</v>
       </c>
       <c r="F201" t="s">
@@ -13939,10 +13984,10 @@
       <c r="C202" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D202" s="6">
-        <v>1</v>
-      </c>
-      <c r="E202" s="6">
+      <c r="D202" s="5">
+        <v>1</v>
+      </c>
+      <c r="E202" s="5">
         <v>1</v>
       </c>
       <c r="F202" t="s">
@@ -13974,10 +14019,10 @@
       <c r="C203" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D203" s="6">
-        <v>1</v>
-      </c>
-      <c r="E203" s="6">
+      <c r="D203" s="5">
+        <v>1</v>
+      </c>
+      <c r="E203" s="5">
         <v>1</v>
       </c>
       <c r="F203" t="s">
@@ -14009,10 +14054,10 @@
       <c r="C204" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D204" s="6">
-        <v>1</v>
-      </c>
-      <c r="E204" s="6">
+      <c r="D204" s="5">
+        <v>1</v>
+      </c>
+      <c r="E204" s="5">
         <v>1</v>
       </c>
       <c r="F204" t="s">
@@ -14044,10 +14089,10 @@
       <c r="C205" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D205" s="6">
-        <v>1</v>
-      </c>
-      <c r="E205" s="6">
+      <c r="D205" s="5">
+        <v>1</v>
+      </c>
+      <c r="E205" s="5">
         <v>1</v>
       </c>
       <c r="F205" t="s">
@@ -14079,10 +14124,10 @@
       <c r="C206" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D206" s="6">
-        <v>1</v>
-      </c>
-      <c r="E206" s="6">
+      <c r="D206" s="5">
+        <v>1</v>
+      </c>
+      <c r="E206" s="5">
         <v>1</v>
       </c>
       <c r="F206" t="s">
@@ -14114,10 +14159,10 @@
       <c r="C207" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D207" s="6">
-        <v>1</v>
-      </c>
-      <c r="E207" s="6">
+      <c r="D207" s="5">
+        <v>1</v>
+      </c>
+      <c r="E207" s="5">
         <v>1</v>
       </c>
       <c r="F207" t="s">
@@ -14149,10 +14194,10 @@
       <c r="C208" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D208" s="6">
-        <v>1</v>
-      </c>
-      <c r="E208" s="6">
+      <c r="D208" s="5">
+        <v>1</v>
+      </c>
+      <c r="E208" s="5">
         <v>1</v>
       </c>
       <c r="F208" t="s">
@@ -14184,10 +14229,10 @@
       <c r="C209" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D209" s="6">
-        <v>1</v>
-      </c>
-      <c r="E209" s="6">
+      <c r="D209" s="5">
+        <v>1</v>
+      </c>
+      <c r="E209" s="5">
         <v>1</v>
       </c>
       <c r="F209" t="s">
@@ -14219,10 +14264,10 @@
       <c r="C210" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D210" s="6">
-        <v>1</v>
-      </c>
-      <c r="E210" s="6">
+      <c r="D210" s="5">
+        <v>1</v>
+      </c>
+      <c r="E210" s="5">
         <v>1</v>
       </c>
       <c r="F210" t="s">
@@ -14254,10 +14299,10 @@
       <c r="C211" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D211" s="6">
-        <v>1</v>
-      </c>
-      <c r="E211" s="6">
+      <c r="D211" s="5">
+        <v>1</v>
+      </c>
+      <c r="E211" s="5">
         <v>1</v>
       </c>
       <c r="F211" t="s">
@@ -14289,10 +14334,10 @@
       <c r="C212" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D212" s="6">
-        <v>1</v>
-      </c>
-      <c r="E212" s="6">
+      <c r="D212" s="5">
+        <v>1</v>
+      </c>
+      <c r="E212" s="5">
         <v>1</v>
       </c>
       <c r="F212" t="s">
@@ -14324,10 +14369,10 @@
       <c r="C213" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D213" s="6">
-        <v>1</v>
-      </c>
-      <c r="E213" s="6">
+      <c r="D213" s="5">
+        <v>1</v>
+      </c>
+      <c r="E213" s="5">
         <v>1</v>
       </c>
       <c r="F213" t="s">
@@ -14359,10 +14404,10 @@
       <c r="C214" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D214" s="6">
-        <v>1</v>
-      </c>
-      <c r="E214" s="6">
+      <c r="D214" s="5">
+        <v>1</v>
+      </c>
+      <c r="E214" s="5">
         <v>1</v>
       </c>
       <c r="F214" t="s">
@@ -14394,10 +14439,10 @@
       <c r="C215" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D215" s="6">
-        <v>1</v>
-      </c>
-      <c r="E215" s="6">
+      <c r="D215" s="5">
+        <v>1</v>
+      </c>
+      <c r="E215" s="5">
         <v>1</v>
       </c>
       <c r="F215" t="s">
@@ -14429,10 +14474,10 @@
       <c r="C216" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D216" s="6">
-        <v>1</v>
-      </c>
-      <c r="E216" s="6">
+      <c r="D216" s="5">
+        <v>1</v>
+      </c>
+      <c r="E216" s="5">
         <v>1</v>
       </c>
       <c r="F216" t="s">
@@ -14464,10 +14509,10 @@
       <c r="C217" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D217" s="6">
-        <v>1</v>
-      </c>
-      <c r="E217" s="6">
+      <c r="D217" s="5">
+        <v>1</v>
+      </c>
+      <c r="E217" s="5">
         <v>1</v>
       </c>
       <c r="F217" t="s">
@@ -14499,10 +14544,10 @@
       <c r="C218" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D218" s="6">
-        <v>1</v>
-      </c>
-      <c r="E218" s="6">
+      <c r="D218" s="5">
+        <v>1</v>
+      </c>
+      <c r="E218" s="5">
         <v>1</v>
       </c>
       <c r="F218" t="s">
@@ -14534,10 +14579,10 @@
       <c r="C219" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D219" s="6">
-        <v>1</v>
-      </c>
-      <c r="E219" s="6">
+      <c r="D219" s="5">
+        <v>1</v>
+      </c>
+      <c r="E219" s="5">
         <v>1</v>
       </c>
       <c r="F219" t="s">
@@ -14569,10 +14614,10 @@
       <c r="C220" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D220" s="6">
-        <v>1</v>
-      </c>
-      <c r="E220" s="6">
+      <c r="D220" s="5">
+        <v>1</v>
+      </c>
+      <c r="E220" s="5">
         <v>1</v>
       </c>
       <c r="F220" t="s">
@@ -14604,10 +14649,10 @@
       <c r="C221" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D221" s="6">
-        <v>1</v>
-      </c>
-      <c r="E221" s="6">
+      <c r="D221" s="5">
+        <v>1</v>
+      </c>
+      <c r="E221" s="5">
         <v>1</v>
       </c>
       <c r="F221" t="s">
@@ -14639,10 +14684,10 @@
       <c r="C222" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D222" s="6">
-        <v>1</v>
-      </c>
-      <c r="E222" s="6">
+      <c r="D222" s="5">
+        <v>1</v>
+      </c>
+      <c r="E222" s="5">
         <v>1</v>
       </c>
       <c r="F222" t="s">
@@ -14674,10 +14719,10 @@
       <c r="C223" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D223" s="6">
-        <v>1</v>
-      </c>
-      <c r="E223" s="6">
+      <c r="D223" s="5">
+        <v>1</v>
+      </c>
+      <c r="E223" s="5">
         <v>1</v>
       </c>
       <c r="F223" t="s">
@@ -14709,10 +14754,10 @@
       <c r="C224" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D224" s="6">
-        <v>1</v>
-      </c>
-      <c r="E224" s="6">
+      <c r="D224" s="5">
+        <v>1</v>
+      </c>
+      <c r="E224" s="5">
         <v>1</v>
       </c>
       <c r="F224" t="s">
@@ -14744,10 +14789,10 @@
       <c r="C225" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D225" s="6">
-        <v>1</v>
-      </c>
-      <c r="E225" s="6">
+      <c r="D225" s="5">
+        <v>1</v>
+      </c>
+      <c r="E225" s="5">
         <v>1</v>
       </c>
       <c r="F225" t="s">
@@ -14779,10 +14824,10 @@
       <c r="C226" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D226" s="6">
-        <v>1</v>
-      </c>
-      <c r="E226" s="6">
+      <c r="D226" s="5">
+        <v>1</v>
+      </c>
+      <c r="E226" s="5">
         <v>1</v>
       </c>
       <c r="F226" t="s">
@@ -14814,10 +14859,10 @@
       <c r="C227" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D227" s="6">
-        <v>1</v>
-      </c>
-      <c r="E227" s="6">
+      <c r="D227" s="5">
+        <v>1</v>
+      </c>
+      <c r="E227" s="5">
         <v>1</v>
       </c>
       <c r="F227" t="s">
@@ -14849,10 +14894,10 @@
       <c r="C228" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D228" s="6">
-        <v>1</v>
-      </c>
-      <c r="E228" s="6">
+      <c r="D228" s="5">
+        <v>1</v>
+      </c>
+      <c r="E228" s="5">
         <v>1</v>
       </c>
       <c r="F228" t="s">
@@ -14884,10 +14929,10 @@
       <c r="C229" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D229" s="6">
-        <v>1</v>
-      </c>
-      <c r="E229" s="6">
+      <c r="D229" s="5">
+        <v>1</v>
+      </c>
+      <c r="E229" s="5">
         <v>1</v>
       </c>
       <c r="F229" t="s">
@@ -14919,10 +14964,10 @@
       <c r="C230" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D230" s="6">
-        <v>1</v>
-      </c>
-      <c r="E230" s="6">
+      <c r="D230" s="5">
+        <v>1</v>
+      </c>
+      <c r="E230" s="5">
         <v>1</v>
       </c>
       <c r="F230" t="s">
@@ -14954,10 +14999,10 @@
       <c r="C231" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D231" s="6">
-        <v>1</v>
-      </c>
-      <c r="E231" s="6">
+      <c r="D231" s="5">
+        <v>1</v>
+      </c>
+      <c r="E231" s="5">
         <v>1</v>
       </c>
       <c r="F231" t="s">
@@ -14989,10 +15034,10 @@
       <c r="C232" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D232" s="6">
-        <v>1</v>
-      </c>
-      <c r="E232" s="6">
+      <c r="D232" s="5">
+        <v>1</v>
+      </c>
+      <c r="E232" s="5">
         <v>1</v>
       </c>
       <c r="F232" t="s">
@@ -15024,10 +15069,10 @@
       <c r="C233" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D233" s="6">
-        <v>1</v>
-      </c>
-      <c r="E233" s="6">
+      <c r="D233" s="5">
+        <v>1</v>
+      </c>
+      <c r="E233" s="5">
         <v>1</v>
       </c>
       <c r="F233" t="s">
@@ -15059,10 +15104,10 @@
       <c r="C234" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D234" s="6">
-        <v>1</v>
-      </c>
-      <c r="E234" s="6">
+      <c r="D234" s="5">
+        <v>1</v>
+      </c>
+      <c r="E234" s="5">
         <v>1</v>
       </c>
       <c r="F234" t="s">
@@ -15094,10 +15139,10 @@
       <c r="C235" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D235" s="6">
-        <v>1</v>
-      </c>
-      <c r="E235" s="6">
+      <c r="D235" s="5">
+        <v>1</v>
+      </c>
+      <c r="E235" s="5">
         <v>1</v>
       </c>
       <c r="F235" t="s">
@@ -15129,10 +15174,10 @@
       <c r="C236" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D236" s="6">
-        <v>1</v>
-      </c>
-      <c r="E236" s="6">
+      <c r="D236" s="5">
+        <v>1</v>
+      </c>
+      <c r="E236" s="5">
         <v>1</v>
       </c>
       <c r="F236" t="s">
@@ -15164,10 +15209,10 @@
       <c r="C237" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D237" s="6">
-        <v>1</v>
-      </c>
-      <c r="E237" s="6">
+      <c r="D237" s="5">
+        <v>1</v>
+      </c>
+      <c r="E237" s="5">
         <v>1</v>
       </c>
       <c r="F237" t="s">
@@ -15199,10 +15244,10 @@
       <c r="C238" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D238" s="6">
-        <v>1</v>
-      </c>
-      <c r="E238" s="6">
+      <c r="D238" s="5">
+        <v>1</v>
+      </c>
+      <c r="E238" s="5">
         <v>1</v>
       </c>
       <c r="F238" t="s">
@@ -15234,10 +15279,10 @@
       <c r="C239" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D239" s="6">
-        <v>1</v>
-      </c>
-      <c r="E239" s="6">
+      <c r="D239" s="5">
+        <v>1</v>
+      </c>
+      <c r="E239" s="5">
         <v>1</v>
       </c>
       <c r="F239" t="s">
@@ -15269,10 +15314,10 @@
       <c r="C240" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D240" s="6">
-        <v>1</v>
-      </c>
-      <c r="E240" s="6">
+      <c r="D240" s="5">
+        <v>1</v>
+      </c>
+      <c r="E240" s="5">
         <v>1</v>
       </c>
       <c r="F240" t="s">
@@ -15304,10 +15349,10 @@
       <c r="C241" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D241" s="6">
-        <v>1</v>
-      </c>
-      <c r="E241" s="6">
+      <c r="D241" s="5">
+        <v>1</v>
+      </c>
+      <c r="E241" s="5">
         <v>1</v>
       </c>
       <c r="F241" t="s">
@@ -15339,10 +15384,10 @@
       <c r="C242" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D242" s="6">
-        <v>1</v>
-      </c>
-      <c r="E242" s="6">
+      <c r="D242" s="5">
+        <v>1</v>
+      </c>
+      <c r="E242" s="5">
         <v>1</v>
       </c>
       <c r="F242" t="s">
@@ -15374,10 +15419,10 @@
       <c r="C243" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D243" s="6">
-        <v>1</v>
-      </c>
-      <c r="E243" s="6">
+      <c r="D243" s="5">
+        <v>1</v>
+      </c>
+      <c r="E243" s="5">
         <v>1</v>
       </c>
       <c r="F243" t="s">
@@ -15409,10 +15454,10 @@
       <c r="C244" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D244" s="6">
-        <v>1</v>
-      </c>
-      <c r="E244" s="6">
+      <c r="D244" s="5">
+        <v>1</v>
+      </c>
+      <c r="E244" s="5">
         <v>1</v>
       </c>
       <c r="F244" t="s">
@@ -15444,10 +15489,10 @@
       <c r="C245" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D245" s="6">
-        <v>1</v>
-      </c>
-      <c r="E245" s="6">
+      <c r="D245" s="5">
+        <v>1</v>
+      </c>
+      <c r="E245" s="5">
         <v>1</v>
       </c>
       <c r="F245" t="s">
@@ -15479,10 +15524,10 @@
       <c r="C246" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D246" s="6">
-        <v>1</v>
-      </c>
-      <c r="E246" s="6">
+      <c r="D246" s="5">
+        <v>1</v>
+      </c>
+      <c r="E246" s="5">
         <v>1</v>
       </c>
       <c r="F246" t="s">
@@ -15514,10 +15559,10 @@
       <c r="C247" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D247" s="6">
-        <v>1</v>
-      </c>
-      <c r="E247" s="6">
+      <c r="D247" s="5">
+        <v>1</v>
+      </c>
+      <c r="E247" s="5">
         <v>1</v>
       </c>
       <c r="F247" t="s">
@@ -15549,10 +15594,10 @@
       <c r="C248" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D248" s="6">
-        <v>1</v>
-      </c>
-      <c r="E248" s="6">
+      <c r="D248" s="5">
+        <v>1</v>
+      </c>
+      <c r="E248" s="5">
         <v>1</v>
       </c>
       <c r="F248" t="s">
@@ -15584,10 +15629,10 @@
       <c r="C249" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D249" s="6">
-        <v>1</v>
-      </c>
-      <c r="E249" s="6">
+      <c r="D249" s="5">
+        <v>1</v>
+      </c>
+      <c r="E249" s="5">
         <v>1</v>
       </c>
       <c r="F249" t="s">
@@ -15619,10 +15664,10 @@
       <c r="C250" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D250" s="6">
-        <v>1</v>
-      </c>
-      <c r="E250" s="6">
+      <c r="D250" s="5">
+        <v>1</v>
+      </c>
+      <c r="E250" s="5">
         <v>1</v>
       </c>
       <c r="F250" t="s">
@@ -15654,10 +15699,10 @@
       <c r="C251" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="D251" s="6">
-        <v>1</v>
-      </c>
-      <c r="E251" s="6">
+      <c r="D251" s="5">
+        <v>1</v>
+      </c>
+      <c r="E251" s="5">
         <v>1</v>
       </c>
       <c r="F251" t="s">
@@ -15689,10 +15734,10 @@
       <c r="C252" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D252" s="6">
-        <v>1</v>
-      </c>
-      <c r="E252" s="6">
+      <c r="D252" s="5">
+        <v>1</v>
+      </c>
+      <c r="E252" s="5">
         <v>1</v>
       </c>
       <c r="F252" t="s">
@@ -15724,10 +15769,10 @@
       <c r="C253" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D253" s="6">
-        <v>1</v>
-      </c>
-      <c r="E253" s="6">
+      <c r="D253" s="5">
+        <v>1</v>
+      </c>
+      <c r="E253" s="5">
         <v>1</v>
       </c>
       <c r="F253" t="s">
@@ -15759,10 +15804,10 @@
       <c r="C254" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D254" s="6">
-        <v>1</v>
-      </c>
-      <c r="E254" s="6">
+      <c r="D254" s="5">
+        <v>1</v>
+      </c>
+      <c r="E254" s="5">
         <v>1</v>
       </c>
       <c r="F254" t="s">
@@ -15794,10 +15839,10 @@
       <c r="C255" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D255" s="6">
-        <v>1</v>
-      </c>
-      <c r="E255" s="6">
+      <c r="D255" s="5">
+        <v>1</v>
+      </c>
+      <c r="E255" s="5">
         <v>1</v>
       </c>
       <c r="F255" t="s">
@@ -15829,10 +15874,10 @@
       <c r="C256" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D256" s="6">
-        <v>1</v>
-      </c>
-      <c r="E256" s="6">
+      <c r="D256" s="5">
+        <v>1</v>
+      </c>
+      <c r="E256" s="5">
         <v>1</v>
       </c>
       <c r="F256" t="s">
@@ -15864,10 +15909,10 @@
       <c r="C257" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D257" s="6">
-        <v>1</v>
-      </c>
-      <c r="E257" s="6">
+      <c r="D257" s="5">
+        <v>1</v>
+      </c>
+      <c r="E257" s="5">
         <v>1</v>
       </c>
       <c r="F257" t="s">
@@ -15899,10 +15944,10 @@
       <c r="C258" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D258" s="6">
-        <v>1</v>
-      </c>
-      <c r="E258" s="6">
+      <c r="D258" s="5">
+        <v>1</v>
+      </c>
+      <c r="E258" s="5">
         <v>1</v>
       </c>
       <c r="F258" t="s">
@@ -15934,10 +15979,10 @@
       <c r="C259" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D259" s="6">
-        <v>1</v>
-      </c>
-      <c r="E259" s="6">
+      <c r="D259" s="5">
+        <v>1</v>
+      </c>
+      <c r="E259" s="5">
         <v>1</v>
       </c>
       <c r="F259" t="s">
@@ -15969,10 +16014,10 @@
       <c r="C260" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D260" s="6">
-        <v>1</v>
-      </c>
-      <c r="E260" s="6">
+      <c r="D260" s="5">
+        <v>1</v>
+      </c>
+      <c r="E260" s="5">
         <v>1</v>
       </c>
       <c r="F260" t="s">
@@ -16004,10 +16049,10 @@
       <c r="C261" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D261" s="6">
-        <v>1</v>
-      </c>
-      <c r="E261" s="6">
+      <c r="D261" s="5">
+        <v>1</v>
+      </c>
+      <c r="E261" s="5">
         <v>1</v>
       </c>
       <c r="F261" t="s">
@@ -16039,10 +16084,10 @@
       <c r="C262" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D262" s="6">
-        <v>1</v>
-      </c>
-      <c r="E262" s="6">
+      <c r="D262" s="5">
+        <v>1</v>
+      </c>
+      <c r="E262" s="5">
         <v>1</v>
       </c>
       <c r="F262" t="s">
@@ -16074,10 +16119,10 @@
       <c r="C263" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D263" s="6">
-        <v>1</v>
-      </c>
-      <c r="E263" s="6">
+      <c r="D263" s="5">
+        <v>1</v>
+      </c>
+      <c r="E263" s="5">
         <v>1</v>
       </c>
       <c r="F263" t="s">
@@ -16109,10 +16154,10 @@
       <c r="C264" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D264" s="6">
-        <v>1</v>
-      </c>
-      <c r="E264" s="6">
+      <c r="D264" s="5">
+        <v>1</v>
+      </c>
+      <c r="E264" s="5">
         <v>1</v>
       </c>
       <c r="F264" t="s">
@@ -16144,10 +16189,10 @@
       <c r="C265" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D265" s="6">
-        <v>1</v>
-      </c>
-      <c r="E265" s="6">
+      <c r="D265" s="5">
+        <v>1</v>
+      </c>
+      <c r="E265" s="5">
         <v>1</v>
       </c>
       <c r="F265" t="s">
@@ -16179,10 +16224,10 @@
       <c r="C266" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D266" s="6">
-        <v>1</v>
-      </c>
-      <c r="E266" s="6">
+      <c r="D266" s="5">
+        <v>1</v>
+      </c>
+      <c r="E266" s="5">
         <v>1</v>
       </c>
       <c r="F266" t="s">
@@ -16214,10 +16259,10 @@
       <c r="C267" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D267" s="6">
-        <v>1</v>
-      </c>
-      <c r="E267" s="6">
+      <c r="D267" s="5">
+        <v>1</v>
+      </c>
+      <c r="E267" s="5">
         <v>1</v>
       </c>
       <c r="F267" t="s">
@@ -16249,10 +16294,10 @@
       <c r="C268" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D268" s="6">
-        <v>1</v>
-      </c>
-      <c r="E268" s="6">
+      <c r="D268" s="5">
+        <v>1</v>
+      </c>
+      <c r="E268" s="5">
         <v>1</v>
       </c>
       <c r="F268" t="s">
@@ -16284,10 +16329,10 @@
       <c r="C269" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D269" s="6">
-        <v>1</v>
-      </c>
-      <c r="E269" s="6">
+      <c r="D269" s="5">
+        <v>1</v>
+      </c>
+      <c r="E269" s="5">
         <v>1</v>
       </c>
       <c r="F269" t="s">
@@ -16319,10 +16364,10 @@
       <c r="C270" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D270" s="6">
-        <v>1</v>
-      </c>
-      <c r="E270" s="6">
+      <c r="D270" s="5">
+        <v>1</v>
+      </c>
+      <c r="E270" s="5">
         <v>1</v>
       </c>
       <c r="F270" t="s">
@@ -16354,10 +16399,10 @@
       <c r="C271" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D271" s="6">
-        <v>1</v>
-      </c>
-      <c r="E271" s="6">
+      <c r="D271" s="5">
+        <v>1</v>
+      </c>
+      <c r="E271" s="5">
         <v>1</v>
       </c>
       <c r="F271" t="s">
@@ -16389,10 +16434,10 @@
       <c r="C272" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D272" s="6">
-        <v>1</v>
-      </c>
-      <c r="E272" s="6">
+      <c r="D272" s="5">
+        <v>1</v>
+      </c>
+      <c r="E272" s="5">
         <v>1</v>
       </c>
       <c r="F272" t="s">
@@ -16424,10 +16469,10 @@
       <c r="C273" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D273" s="6">
-        <v>1</v>
-      </c>
-      <c r="E273" s="6">
+      <c r="D273" s="5">
+        <v>1</v>
+      </c>
+      <c r="E273" s="5">
         <v>1</v>
       </c>
       <c r="F273" t="s">
@@ -16459,10 +16504,10 @@
       <c r="C274" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D274" s="6">
-        <v>1</v>
-      </c>
-      <c r="E274" s="6">
+      <c r="D274" s="5">
+        <v>1</v>
+      </c>
+      <c r="E274" s="5">
         <v>1</v>
       </c>
       <c r="F274" t="s">
@@ -16494,10 +16539,10 @@
       <c r="C275" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D275" s="6">
-        <v>1</v>
-      </c>
-      <c r="E275" s="6">
+      <c r="D275" s="5">
+        <v>1</v>
+      </c>
+      <c r="E275" s="5">
         <v>1</v>
       </c>
       <c r="F275" t="s">
@@ -16529,10 +16574,10 @@
       <c r="C276" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D276" s="6">
-        <v>1</v>
-      </c>
-      <c r="E276" s="6">
+      <c r="D276" s="5">
+        <v>1</v>
+      </c>
+      <c r="E276" s="5">
         <v>1</v>
       </c>
       <c r="F276" t="s">
@@ -16564,10 +16609,10 @@
       <c r="C277" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D277" s="6">
-        <v>1</v>
-      </c>
-      <c r="E277" s="6">
+      <c r="D277" s="5">
+        <v>1</v>
+      </c>
+      <c r="E277" s="5">
         <v>1</v>
       </c>
       <c r="F277" t="s">
@@ -16599,10 +16644,10 @@
       <c r="C278" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D278" s="6">
-        <v>1</v>
-      </c>
-      <c r="E278" s="6">
+      <c r="D278" s="5">
+        <v>1</v>
+      </c>
+      <c r="E278" s="5">
         <v>1</v>
       </c>
       <c r="F278" t="s">
@@ -16634,10 +16679,10 @@
       <c r="C279" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D279" s="6">
-        <v>1</v>
-      </c>
-      <c r="E279" s="6">
+      <c r="D279" s="5">
+        <v>1</v>
+      </c>
+      <c r="E279" s="5">
         <v>1</v>
       </c>
       <c r="F279" t="s">
@@ -16669,10 +16714,10 @@
       <c r="C280" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D280" s="6">
-        <v>1</v>
-      </c>
-      <c r="E280" s="6">
+      <c r="D280" s="5">
+        <v>1</v>
+      </c>
+      <c r="E280" s="5">
         <v>1</v>
       </c>
       <c r="F280" t="s">
@@ -16704,10 +16749,10 @@
       <c r="C281" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D281" s="6">
-        <v>1</v>
-      </c>
-      <c r="E281" s="6">
+      <c r="D281" s="5">
+        <v>1</v>
+      </c>
+      <c r="E281" s="5">
         <v>1</v>
       </c>
       <c r="F281" t="s">
@@ -16739,10 +16784,10 @@
       <c r="C282" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D282" s="6">
-        <v>1</v>
-      </c>
-      <c r="E282" s="6">
+      <c r="D282" s="5">
+        <v>1</v>
+      </c>
+      <c r="E282" s="5">
         <v>1</v>
       </c>
       <c r="F282" t="s">
@@ -16774,10 +16819,10 @@
       <c r="C283" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D283" s="6">
-        <v>1</v>
-      </c>
-      <c r="E283" s="6">
+      <c r="D283" s="5">
+        <v>1</v>
+      </c>
+      <c r="E283" s="5">
         <v>1</v>
       </c>
       <c r="F283" t="s">
@@ -16809,10 +16854,10 @@
       <c r="C284" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D284" s="6">
-        <v>1</v>
-      </c>
-      <c r="E284" s="6">
+      <c r="D284" s="5">
+        <v>1</v>
+      </c>
+      <c r="E284" s="5">
         <v>1</v>
       </c>
       <c r="F284" t="s">
@@ -16844,10 +16889,10 @@
       <c r="C285" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D285" s="6">
-        <v>1</v>
-      </c>
-      <c r="E285" s="6">
+      <c r="D285" s="5">
+        <v>1</v>
+      </c>
+      <c r="E285" s="5">
         <v>1</v>
       </c>
       <c r="F285" t="s">
@@ -16879,10 +16924,10 @@
       <c r="C286" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D286" s="6">
-        <v>1</v>
-      </c>
-      <c r="E286" s="6">
+      <c r="D286" s="5">
+        <v>1</v>
+      </c>
+      <c r="E286" s="5">
         <v>1</v>
       </c>
       <c r="F286" t="s">
@@ -16914,10 +16959,10 @@
       <c r="C287" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D287" s="6">
-        <v>1</v>
-      </c>
-      <c r="E287" s="6">
+      <c r="D287" s="5">
+        <v>1</v>
+      </c>
+      <c r="E287" s="5">
         <v>1</v>
       </c>
       <c r="F287" t="s">
@@ -16949,10 +16994,10 @@
       <c r="C288" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D288" s="6">
-        <v>1</v>
-      </c>
-      <c r="E288" s="6">
+      <c r="D288" s="5">
+        <v>1</v>
+      </c>
+      <c r="E288" s="5">
         <v>1</v>
       </c>
       <c r="F288" t="s">
@@ -16984,10 +17029,10 @@
       <c r="C289" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D289" s="6">
-        <v>1</v>
-      </c>
-      <c r="E289" s="6">
+      <c r="D289" s="5">
+        <v>1</v>
+      </c>
+      <c r="E289" s="5">
         <v>1</v>
       </c>
       <c r="F289" t="s">
@@ -17019,10 +17064,10 @@
       <c r="C290" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D290" s="6">
-        <v>1</v>
-      </c>
-      <c r="E290" s="6">
+      <c r="D290" s="5">
+        <v>1</v>
+      </c>
+      <c r="E290" s="5">
         <v>1</v>
       </c>
       <c r="F290" t="s">
@@ -17054,10 +17099,10 @@
       <c r="C291" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D291" s="6">
-        <v>1</v>
-      </c>
-      <c r="E291" s="6">
+      <c r="D291" s="5">
+        <v>1</v>
+      </c>
+      <c r="E291" s="5">
         <v>1</v>
       </c>
       <c r="F291" t="s">
@@ -17089,10 +17134,10 @@
       <c r="C292" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D292" s="6">
-        <v>1</v>
-      </c>
-      <c r="E292" s="6">
+      <c r="D292" s="5">
+        <v>1</v>
+      </c>
+      <c r="E292" s="5">
         <v>1</v>
       </c>
       <c r="F292" t="s">
@@ -17124,10 +17169,10 @@
       <c r="C293" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D293" s="6">
-        <v>1</v>
-      </c>
-      <c r="E293" s="6">
+      <c r="D293" s="5">
+        <v>1</v>
+      </c>
+      <c r="E293" s="5">
         <v>1</v>
       </c>
       <c r="F293" t="s">
@@ -17159,10 +17204,10 @@
       <c r="C294" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D294" s="6">
-        <v>1</v>
-      </c>
-      <c r="E294" s="6">
+      <c r="D294" s="5">
+        <v>1</v>
+      </c>
+      <c r="E294" s="5">
         <v>1</v>
       </c>
       <c r="F294" t="s">
@@ -17194,10 +17239,10 @@
       <c r="C295" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D295" s="6">
-        <v>1</v>
-      </c>
-      <c r="E295" s="6">
+      <c r="D295" s="5">
+        <v>1</v>
+      </c>
+      <c r="E295" s="5">
         <v>1</v>
       </c>
       <c r="F295" t="s">
@@ -17229,10 +17274,10 @@
       <c r="C296" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D296" s="6">
-        <v>1</v>
-      </c>
-      <c r="E296" s="6">
+      <c r="D296" s="5">
+        <v>1</v>
+      </c>
+      <c r="E296" s="5">
         <v>1</v>
       </c>
       <c r="F296" t="s">
@@ -17264,10 +17309,10 @@
       <c r="C297" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D297" s="6">
-        <v>1</v>
-      </c>
-      <c r="E297" s="6">
+      <c r="D297" s="5">
+        <v>1</v>
+      </c>
+      <c r="E297" s="5">
         <v>1</v>
       </c>
       <c r="F297" t="s">
@@ -17299,10 +17344,10 @@
       <c r="C298" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D298" s="6">
-        <v>1</v>
-      </c>
-      <c r="E298" s="6">
+      <c r="D298" s="5">
+        <v>1</v>
+      </c>
+      <c r="E298" s="5">
         <v>1</v>
       </c>
       <c r="F298" t="s">
@@ -17334,10 +17379,10 @@
       <c r="C299" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D299" s="6">
-        <v>1</v>
-      </c>
-      <c r="E299" s="6">
+      <c r="D299" s="5">
+        <v>1</v>
+      </c>
+      <c r="E299" s="5">
         <v>1</v>
       </c>
       <c r="F299" t="s">
@@ -17369,10 +17414,10 @@
       <c r="C300" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D300" s="6">
-        <v>1</v>
-      </c>
-      <c r="E300" s="6">
+      <c r="D300" s="5">
+        <v>1</v>
+      </c>
+      <c r="E300" s="5">
         <v>1</v>
       </c>
       <c r="F300" t="s">
@@ -17404,10 +17449,10 @@
       <c r="C301" s="4" t="s">
         <v>2040</v>
       </c>
-      <c r="D301" s="6">
-        <v>1</v>
-      </c>
-      <c r="E301" s="6">
+      <c r="D301" s="5">
+        <v>1</v>
+      </c>
+      <c r="E301" s="5">
         <v>1</v>
       </c>
       <c r="F301" t="s">
@@ -17439,10 +17484,10 @@
       <c r="C302" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D302" s="6">
-        <v>1</v>
-      </c>
-      <c r="E302" s="6">
+      <c r="D302" s="5">
+        <v>1</v>
+      </c>
+      <c r="E302" s="5">
         <v>1</v>
       </c>
       <c r="F302" t="s">
@@ -17474,10 +17519,10 @@
       <c r="C303" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D303" s="6">
-        <v>1</v>
-      </c>
-      <c r="E303" s="6">
+      <c r="D303" s="5">
+        <v>1</v>
+      </c>
+      <c r="E303" s="5">
         <v>1</v>
       </c>
       <c r="F303" t="s">
@@ -17509,10 +17554,10 @@
       <c r="C304" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D304" s="6">
-        <v>1</v>
-      </c>
-      <c r="E304" s="6">
+      <c r="D304" s="5">
+        <v>1</v>
+      </c>
+      <c r="E304" s="5">
         <v>1</v>
       </c>
       <c r="F304" t="s">
@@ -17544,10 +17589,10 @@
       <c r="C305" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D305" s="6">
-        <v>1</v>
-      </c>
-      <c r="E305" s="6">
+      <c r="D305" s="5">
+        <v>1</v>
+      </c>
+      <c r="E305" s="5">
         <v>1</v>
       </c>
       <c r="F305" t="s">
@@ -17579,10 +17624,10 @@
       <c r="C306" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D306" s="6">
-        <v>1</v>
-      </c>
-      <c r="E306" s="6">
+      <c r="D306" s="5">
+        <v>1</v>
+      </c>
+      <c r="E306" s="5">
         <v>1</v>
       </c>
       <c r="F306" t="s">
@@ -17614,10 +17659,10 @@
       <c r="C307" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D307" s="6">
-        <v>1</v>
-      </c>
-      <c r="E307" s="6">
+      <c r="D307" s="5">
+        <v>1</v>
+      </c>
+      <c r="E307" s="5">
         <v>1</v>
       </c>
       <c r="F307" t="s">
@@ -17649,10 +17694,10 @@
       <c r="C308" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D308" s="6">
-        <v>1</v>
-      </c>
-      <c r="E308" s="6">
+      <c r="D308" s="5">
+        <v>1</v>
+      </c>
+      <c r="E308" s="5">
         <v>1</v>
       </c>
       <c r="F308" t="s">
@@ -17684,10 +17729,10 @@
       <c r="C309" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D309" s="6">
-        <v>1</v>
-      </c>
-      <c r="E309" s="6">
+      <c r="D309" s="5">
+        <v>1</v>
+      </c>
+      <c r="E309" s="5">
         <v>1</v>
       </c>
       <c r="F309" t="s">
@@ -17719,10 +17764,10 @@
       <c r="C310" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D310" s="6">
-        <v>1</v>
-      </c>
-      <c r="E310" s="6">
+      <c r="D310" s="5">
+        <v>1</v>
+      </c>
+      <c r="E310" s="5">
         <v>1</v>
       </c>
       <c r="F310" t="s">
@@ -17754,10 +17799,10 @@
       <c r="C311" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D311" s="6">
-        <v>1</v>
-      </c>
-      <c r="E311" s="6">
+      <c r="D311" s="5">
+        <v>1</v>
+      </c>
+      <c r="E311" s="5">
         <v>1</v>
       </c>
       <c r="F311" t="s">
@@ -17789,10 +17834,10 @@
       <c r="C312" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D312" s="6">
-        <v>1</v>
-      </c>
-      <c r="E312" s="6">
+      <c r="D312" s="5">
+        <v>1</v>
+      </c>
+      <c r="E312" s="5">
         <v>1</v>
       </c>
       <c r="F312" t="s">
@@ -17824,10 +17869,10 @@
       <c r="C313" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D313" s="6">
-        <v>1</v>
-      </c>
-      <c r="E313" s="6">
+      <c r="D313" s="5">
+        <v>1</v>
+      </c>
+      <c r="E313" s="5">
         <v>1</v>
       </c>
       <c r="F313" t="s">
@@ -17859,10 +17904,10 @@
       <c r="C314" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D314" s="6">
-        <v>1</v>
-      </c>
-      <c r="E314" s="6">
+      <c r="D314" s="5">
+        <v>1</v>
+      </c>
+      <c r="E314" s="5">
         <v>1</v>
       </c>
       <c r="F314" t="s">
@@ -17894,10 +17939,10 @@
       <c r="C315" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D315" s="6">
-        <v>1</v>
-      </c>
-      <c r="E315" s="6">
+      <c r="D315" s="5">
+        <v>1</v>
+      </c>
+      <c r="E315" s="5">
         <v>1</v>
       </c>
       <c r="F315" t="s">
@@ -17929,10 +17974,10 @@
       <c r="C316" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D316" s="6">
-        <v>1</v>
-      </c>
-      <c r="E316" s="6">
+      <c r="D316" s="5">
+        <v>1</v>
+      </c>
+      <c r="E316" s="5">
         <v>1</v>
       </c>
       <c r="F316" t="s">
@@ -17964,10 +18009,10 @@
       <c r="C317" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D317" s="6">
-        <v>1</v>
-      </c>
-      <c r="E317" s="6">
+      <c r="D317" s="5">
+        <v>1</v>
+      </c>
+      <c r="E317" s="5">
         <v>1</v>
       </c>
       <c r="F317" t="s">
@@ -17999,10 +18044,10 @@
       <c r="C318" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D318" s="6">
-        <v>1</v>
-      </c>
-      <c r="E318" s="6">
+      <c r="D318" s="5">
+        <v>1</v>
+      </c>
+      <c r="E318" s="5">
         <v>1</v>
       </c>
       <c r="F318" t="s">
@@ -18034,10 +18079,10 @@
       <c r="C319" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D319" s="6">
-        <v>1</v>
-      </c>
-      <c r="E319" s="6">
+      <c r="D319" s="5">
+        <v>1</v>
+      </c>
+      <c r="E319" s="5">
         <v>1</v>
       </c>
       <c r="F319" t="s">
@@ -18069,10 +18114,10 @@
       <c r="C320" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D320" s="6">
-        <v>1</v>
-      </c>
-      <c r="E320" s="6">
+      <c r="D320" s="5">
+        <v>1</v>
+      </c>
+      <c r="E320" s="5">
         <v>1</v>
       </c>
       <c r="F320" t="s">
@@ -18104,10 +18149,10 @@
       <c r="C321" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D321" s="6">
-        <v>1</v>
-      </c>
-      <c r="E321" s="6">
+      <c r="D321" s="5">
+        <v>1</v>
+      </c>
+      <c r="E321" s="5">
         <v>1</v>
       </c>
       <c r="F321" t="s">
@@ -18139,10 +18184,10 @@
       <c r="C322" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D322" s="6">
-        <v>1</v>
-      </c>
-      <c r="E322" s="6">
+      <c r="D322" s="5">
+        <v>1</v>
+      </c>
+      <c r="E322" s="5">
         <v>1</v>
       </c>
       <c r="F322" t="s">
@@ -18174,10 +18219,10 @@
       <c r="C323" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D323" s="6">
-        <v>1</v>
-      </c>
-      <c r="E323" s="6">
+      <c r="D323" s="5">
+        <v>1</v>
+      </c>
+      <c r="E323" s="5">
         <v>1</v>
       </c>
       <c r="F323" t="s">
@@ -18209,10 +18254,10 @@
       <c r="C324" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D324" s="6">
-        <v>1</v>
-      </c>
-      <c r="E324" s="6">
+      <c r="D324" s="5">
+        <v>1</v>
+      </c>
+      <c r="E324" s="5">
         <v>1</v>
       </c>
       <c r="F324" t="s">
@@ -18244,10 +18289,10 @@
       <c r="C325" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D325" s="6">
-        <v>1</v>
-      </c>
-      <c r="E325" s="6">
+      <c r="D325" s="5">
+        <v>1</v>
+      </c>
+      <c r="E325" s="5">
         <v>1</v>
       </c>
       <c r="F325" t="s">
@@ -18279,10 +18324,10 @@
       <c r="C326" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D326" s="6">
-        <v>1</v>
-      </c>
-      <c r="E326" s="6">
+      <c r="D326" s="5">
+        <v>1</v>
+      </c>
+      <c r="E326" s="5">
         <v>1</v>
       </c>
       <c r="F326" t="s">
@@ -18314,10 +18359,10 @@
       <c r="C327" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D327" s="6">
-        <v>1</v>
-      </c>
-      <c r="E327" s="6">
+      <c r="D327" s="5">
+        <v>1</v>
+      </c>
+      <c r="E327" s="5">
         <v>1</v>
       </c>
       <c r="F327" t="s">
@@ -18349,10 +18394,10 @@
       <c r="C328" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D328" s="6">
-        <v>1</v>
-      </c>
-      <c r="E328" s="6">
+      <c r="D328" s="5">
+        <v>1</v>
+      </c>
+      <c r="E328" s="5">
         <v>1</v>
       </c>
       <c r="F328" t="s">
@@ -18384,10 +18429,10 @@
       <c r="C329" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D329" s="6">
-        <v>1</v>
-      </c>
-      <c r="E329" s="6">
+      <c r="D329" s="5">
+        <v>1</v>
+      </c>
+      <c r="E329" s="5">
         <v>1</v>
       </c>
       <c r="F329" t="s">
@@ -18419,10 +18464,10 @@
       <c r="C330" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D330" s="6">
-        <v>1</v>
-      </c>
-      <c r="E330" s="6">
+      <c r="D330" s="5">
+        <v>1</v>
+      </c>
+      <c r="E330" s="5">
         <v>1</v>
       </c>
       <c r="F330" t="s">
@@ -18454,10 +18499,10 @@
       <c r="C331" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D331" s="6">
-        <v>1</v>
-      </c>
-      <c r="E331" s="6">
+      <c r="D331" s="5">
+        <v>1</v>
+      </c>
+      <c r="E331" s="5">
         <v>1</v>
       </c>
       <c r="F331" t="s">
@@ -18489,10 +18534,10 @@
       <c r="C332" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D332" s="6">
-        <v>1</v>
-      </c>
-      <c r="E332" s="6">
+      <c r="D332" s="5">
+        <v>1</v>
+      </c>
+      <c r="E332" s="5">
         <v>1</v>
       </c>
       <c r="F332" t="s">
@@ -18524,10 +18569,10 @@
       <c r="C333" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D333" s="6">
-        <v>1</v>
-      </c>
-      <c r="E333" s="6">
+      <c r="D333" s="5">
+        <v>1</v>
+      </c>
+      <c r="E333" s="5">
         <v>1</v>
       </c>
       <c r="F333" t="s">
@@ -18559,10 +18604,10 @@
       <c r="C334" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D334" s="6">
-        <v>1</v>
-      </c>
-      <c r="E334" s="6">
+      <c r="D334" s="5">
+        <v>1</v>
+      </c>
+      <c r="E334" s="5">
         <v>1</v>
       </c>
       <c r="F334" t="s">
@@ -18594,10 +18639,10 @@
       <c r="C335" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D335" s="6">
-        <v>1</v>
-      </c>
-      <c r="E335" s="6">
+      <c r="D335" s="5">
+        <v>1</v>
+      </c>
+      <c r="E335" s="5">
         <v>1</v>
       </c>
       <c r="F335" t="s">
@@ -18629,10 +18674,10 @@
       <c r="C336" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D336" s="6">
-        <v>1</v>
-      </c>
-      <c r="E336" s="6">
+      <c r="D336" s="5">
+        <v>1</v>
+      </c>
+      <c r="E336" s="5">
         <v>1</v>
       </c>
       <c r="F336" t="s">
@@ -18664,10 +18709,10 @@
       <c r="C337" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D337" s="6">
-        <v>1</v>
-      </c>
-      <c r="E337" s="6">
+      <c r="D337" s="5">
+        <v>1</v>
+      </c>
+      <c r="E337" s="5">
         <v>1</v>
       </c>
       <c r="F337" t="s">
@@ -18699,10 +18744,10 @@
       <c r="C338" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D338" s="6">
-        <v>1</v>
-      </c>
-      <c r="E338" s="6">
+      <c r="D338" s="5">
+        <v>1</v>
+      </c>
+      <c r="E338" s="5">
         <v>1</v>
       </c>
       <c r="F338" t="s">
@@ -18734,10 +18779,10 @@
       <c r="C339" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D339" s="6">
-        <v>1</v>
-      </c>
-      <c r="E339" s="6">
+      <c r="D339" s="5">
+        <v>1</v>
+      </c>
+      <c r="E339" s="5">
         <v>1</v>
       </c>
       <c r="F339" t="s">
@@ -18769,10 +18814,10 @@
       <c r="C340" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D340" s="6">
-        <v>1</v>
-      </c>
-      <c r="E340" s="6">
+      <c r="D340" s="5">
+        <v>1</v>
+      </c>
+      <c r="E340" s="5">
         <v>1</v>
       </c>
       <c r="F340" t="s">
@@ -18804,10 +18849,10 @@
       <c r="C341" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D341" s="6">
-        <v>1</v>
-      </c>
-      <c r="E341" s="6">
+      <c r="D341" s="5">
+        <v>1</v>
+      </c>
+      <c r="E341" s="5">
         <v>1</v>
       </c>
       <c r="F341" t="s">
@@ -18839,10 +18884,10 @@
       <c r="C342" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D342" s="6">
-        <v>1</v>
-      </c>
-      <c r="E342" s="6">
+      <c r="D342" s="5">
+        <v>1</v>
+      </c>
+      <c r="E342" s="5">
         <v>1</v>
       </c>
       <c r="F342" t="s">
@@ -18874,10 +18919,10 @@
       <c r="C343" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D343" s="6">
-        <v>1</v>
-      </c>
-      <c r="E343" s="6">
+      <c r="D343" s="5">
+        <v>1</v>
+      </c>
+      <c r="E343" s="5">
         <v>1</v>
       </c>
       <c r="F343" t="s">
@@ -18909,10 +18954,10 @@
       <c r="C344" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D344" s="6">
-        <v>1</v>
-      </c>
-      <c r="E344" s="6">
+      <c r="D344" s="5">
+        <v>1</v>
+      </c>
+      <c r="E344" s="5">
         <v>1</v>
       </c>
       <c r="F344" t="s">
@@ -18944,10 +18989,10 @@
       <c r="C345" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D345" s="6">
-        <v>1</v>
-      </c>
-      <c r="E345" s="6">
+      <c r="D345" s="5">
+        <v>1</v>
+      </c>
+      <c r="E345" s="5">
         <v>1</v>
       </c>
       <c r="F345" t="s">
@@ -18979,10 +19024,10 @@
       <c r="C346" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D346" s="6">
-        <v>1</v>
-      </c>
-      <c r="E346" s="6">
+      <c r="D346" s="5">
+        <v>1</v>
+      </c>
+      <c r="E346" s="5">
         <v>1</v>
       </c>
       <c r="F346" t="s">
@@ -19014,10 +19059,10 @@
       <c r="C347" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D347" s="6">
-        <v>1</v>
-      </c>
-      <c r="E347" s="6">
+      <c r="D347" s="5">
+        <v>1</v>
+      </c>
+      <c r="E347" s="5">
         <v>1</v>
       </c>
       <c r="F347" t="s">
@@ -19049,10 +19094,10 @@
       <c r="C348" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D348" s="6">
-        <v>1</v>
-      </c>
-      <c r="E348" s="6">
+      <c r="D348" s="5">
+        <v>1</v>
+      </c>
+      <c r="E348" s="5">
         <v>1</v>
       </c>
       <c r="F348" t="s">
@@ -19084,10 +19129,10 @@
       <c r="C349" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D349" s="6">
-        <v>1</v>
-      </c>
-      <c r="E349" s="6">
+      <c r="D349" s="5">
+        <v>1</v>
+      </c>
+      <c r="E349" s="5">
         <v>1</v>
       </c>
       <c r="F349" t="s">
@@ -19119,10 +19164,10 @@
       <c r="C350" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D350" s="6">
-        <v>1</v>
-      </c>
-      <c r="E350" s="6">
+      <c r="D350" s="5">
+        <v>1</v>
+      </c>
+      <c r="E350" s="5">
         <v>1</v>
       </c>
       <c r="F350" t="s">
@@ -19154,10 +19199,10 @@
       <c r="C351" s="4" t="s">
         <v>2041</v>
       </c>
-      <c r="D351" s="6">
-        <v>1</v>
-      </c>
-      <c r="E351" s="6">
+      <c r="D351" s="5">
+        <v>1</v>
+      </c>
+      <c r="E351" s="5">
         <v>1</v>
       </c>
       <c r="F351" t="s">
@@ -19189,10 +19234,10 @@
       <c r="C352" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D352" s="6">
-        <v>1</v>
-      </c>
-      <c r="E352" s="6">
+      <c r="D352" s="5">
+        <v>1</v>
+      </c>
+      <c r="E352" s="5">
         <v>1</v>
       </c>
       <c r="F352" t="s">
@@ -19224,10 +19269,10 @@
       <c r="C353" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D353" s="6">
-        <v>1</v>
-      </c>
-      <c r="E353" s="6">
+      <c r="D353" s="5">
+        <v>1</v>
+      </c>
+      <c r="E353" s="5">
         <v>1</v>
       </c>
       <c r="F353" t="s">
@@ -19259,10 +19304,10 @@
       <c r="C354" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D354" s="6">
-        <v>1</v>
-      </c>
-      <c r="E354" s="6">
+      <c r="D354" s="5">
+        <v>1</v>
+      </c>
+      <c r="E354" s="5">
         <v>1</v>
       </c>
       <c r="F354" t="s">
@@ -19294,10 +19339,10 @@
       <c r="C355" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D355" s="6">
-        <v>1</v>
-      </c>
-      <c r="E355" s="6">
+      <c r="D355" s="5">
+        <v>1</v>
+      </c>
+      <c r="E355" s="5">
         <v>1</v>
       </c>
       <c r="F355" t="s">
@@ -19329,10 +19374,10 @@
       <c r="C356" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D356" s="6">
-        <v>1</v>
-      </c>
-      <c r="E356" s="6">
+      <c r="D356" s="5">
+        <v>1</v>
+      </c>
+      <c r="E356" s="5">
         <v>1</v>
       </c>
       <c r="F356" t="s">
@@ -19364,10 +19409,10 @@
       <c r="C357" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D357" s="6">
-        <v>1</v>
-      </c>
-      <c r="E357" s="6">
+      <c r="D357" s="5">
+        <v>1</v>
+      </c>
+      <c r="E357" s="5">
         <v>1</v>
       </c>
       <c r="F357" t="s">
@@ -19399,10 +19444,10 @@
       <c r="C358" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D358" s="6">
-        <v>1</v>
-      </c>
-      <c r="E358" s="6">
+      <c r="D358" s="5">
+        <v>1</v>
+      </c>
+      <c r="E358" s="5">
         <v>1</v>
       </c>
       <c r="F358" t="s">
@@ -19434,10 +19479,10 @@
       <c r="C359" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D359" s="6">
-        <v>1</v>
-      </c>
-      <c r="E359" s="6">
+      <c r="D359" s="5">
+        <v>1</v>
+      </c>
+      <c r="E359" s="5">
         <v>1</v>
       </c>
       <c r="F359" t="s">
@@ -19469,10 +19514,10 @@
       <c r="C360" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D360" s="6">
-        <v>1</v>
-      </c>
-      <c r="E360" s="6">
+      <c r="D360" s="5">
+        <v>1</v>
+      </c>
+      <c r="E360" s="5">
         <v>1</v>
       </c>
       <c r="F360" t="s">
@@ -19504,10 +19549,10 @@
       <c r="C361" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D361" s="6">
-        <v>1</v>
-      </c>
-      <c r="E361" s="6">
+      <c r="D361" s="5">
+        <v>1</v>
+      </c>
+      <c r="E361" s="5">
         <v>1</v>
       </c>
       <c r="F361" t="s">
@@ -19539,10 +19584,10 @@
       <c r="C362" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D362" s="6">
-        <v>1</v>
-      </c>
-      <c r="E362" s="6">
+      <c r="D362" s="5">
+        <v>1</v>
+      </c>
+      <c r="E362" s="5">
         <v>1</v>
       </c>
       <c r="F362" t="s">
@@ -19574,10 +19619,10 @@
       <c r="C363" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D363" s="6">
-        <v>1</v>
-      </c>
-      <c r="E363" s="6">
+      <c r="D363" s="5">
+        <v>1</v>
+      </c>
+      <c r="E363" s="5">
         <v>1</v>
       </c>
       <c r="F363" t="s">
@@ -19609,10 +19654,10 @@
       <c r="C364" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D364" s="6">
-        <v>1</v>
-      </c>
-      <c r="E364" s="6">
+      <c r="D364" s="5">
+        <v>1</v>
+      </c>
+      <c r="E364" s="5">
         <v>1</v>
       </c>
       <c r="F364" t="s">
@@ -19644,10 +19689,10 @@
       <c r="C365" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D365" s="6">
-        <v>1</v>
-      </c>
-      <c r="E365" s="6">
+      <c r="D365" s="5">
+        <v>1</v>
+      </c>
+      <c r="E365" s="5">
         <v>1</v>
       </c>
       <c r="F365" t="s">
@@ -19679,10 +19724,10 @@
       <c r="C366" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D366" s="6">
-        <v>1</v>
-      </c>
-      <c r="E366" s="6">
+      <c r="D366" s="5">
+        <v>1</v>
+      </c>
+      <c r="E366" s="5">
         <v>1</v>
       </c>
       <c r="F366" t="s">
@@ -19714,10 +19759,10 @@
       <c r="C367" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D367" s="6">
-        <v>1</v>
-      </c>
-      <c r="E367" s="6">
+      <c r="D367" s="5">
+        <v>1</v>
+      </c>
+      <c r="E367" s="5">
         <v>1</v>
       </c>
       <c r="F367" t="s">
@@ -19749,10 +19794,10 @@
       <c r="C368" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D368" s="6">
-        <v>1</v>
-      </c>
-      <c r="E368" s="6">
+      <c r="D368" s="5">
+        <v>1</v>
+      </c>
+      <c r="E368" s="5">
         <v>1</v>
       </c>
       <c r="F368" t="s">
@@ -19784,10 +19829,10 @@
       <c r="C369" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D369" s="6">
-        <v>1</v>
-      </c>
-      <c r="E369" s="6">
+      <c r="D369" s="5">
+        <v>1</v>
+      </c>
+      <c r="E369" s="5">
         <v>1</v>
       </c>
       <c r="F369" t="s">
@@ -19819,10 +19864,10 @@
       <c r="C370" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D370" s="6">
-        <v>1</v>
-      </c>
-      <c r="E370" s="6">
+      <c r="D370" s="5">
+        <v>1</v>
+      </c>
+      <c r="E370" s="5">
         <v>1</v>
       </c>
       <c r="F370" t="s">
@@ -19854,10 +19899,10 @@
       <c r="C371" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D371" s="6">
-        <v>1</v>
-      </c>
-      <c r="E371" s="6">
+      <c r="D371" s="5">
+        <v>1</v>
+      </c>
+      <c r="E371" s="5">
         <v>1</v>
       </c>
       <c r="F371" t="s">
@@ -19889,10 +19934,10 @@
       <c r="C372" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D372" s="6">
-        <v>1</v>
-      </c>
-      <c r="E372" s="6">
+      <c r="D372" s="5">
+        <v>1</v>
+      </c>
+      <c r="E372" s="5">
         <v>1</v>
       </c>
       <c r="F372" t="s">
@@ -19924,10 +19969,10 @@
       <c r="C373" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D373" s="6">
-        <v>1</v>
-      </c>
-      <c r="E373" s="6">
+      <c r="D373" s="5">
+        <v>1</v>
+      </c>
+      <c r="E373" s="5">
         <v>1</v>
       </c>
       <c r="F373" t="s">
@@ -19959,10 +20004,10 @@
       <c r="C374" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D374" s="6">
-        <v>1</v>
-      </c>
-      <c r="E374" s="6">
+      <c r="D374" s="5">
+        <v>1</v>
+      </c>
+      <c r="E374" s="5">
         <v>1</v>
       </c>
       <c r="F374" t="s">
@@ -19994,10 +20039,10 @@
       <c r="C375" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D375" s="6">
-        <v>1</v>
-      </c>
-      <c r="E375" s="6">
+      <c r="D375" s="5">
+        <v>1</v>
+      </c>
+      <c r="E375" s="5">
         <v>1</v>
       </c>
       <c r="F375" t="s">
@@ -20029,10 +20074,10 @@
       <c r="C376" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D376" s="6">
-        <v>1</v>
-      </c>
-      <c r="E376" s="6">
+      <c r="D376" s="5">
+        <v>1</v>
+      </c>
+      <c r="E376" s="5">
         <v>1</v>
       </c>
       <c r="F376" t="s">
@@ -20064,10 +20109,10 @@
       <c r="C377" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D377" s="6">
-        <v>1</v>
-      </c>
-      <c r="E377" s="6">
+      <c r="D377" s="5">
+        <v>1</v>
+      </c>
+      <c r="E377" s="5">
         <v>1</v>
       </c>
       <c r="F377" t="s">
@@ -20099,10 +20144,10 @@
       <c r="C378" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D378" s="6">
-        <v>1</v>
-      </c>
-      <c r="E378" s="6">
+      <c r="D378" s="5">
+        <v>1</v>
+      </c>
+      <c r="E378" s="5">
         <v>1</v>
       </c>
       <c r="F378" t="s">
@@ -20134,10 +20179,10 @@
       <c r="C379" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D379" s="6">
-        <v>1</v>
-      </c>
-      <c r="E379" s="6">
+      <c r="D379" s="5">
+        <v>1</v>
+      </c>
+      <c r="E379" s="5">
         <v>1</v>
       </c>
       <c r="F379" t="s">
@@ -20169,10 +20214,10 @@
       <c r="C380" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D380" s="6">
-        <v>1</v>
-      </c>
-      <c r="E380" s="6">
+      <c r="D380" s="5">
+        <v>1</v>
+      </c>
+      <c r="E380" s="5">
         <v>1</v>
       </c>
       <c r="F380" t="s">
@@ -20204,10 +20249,10 @@
       <c r="C381" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D381" s="6">
-        <v>1</v>
-      </c>
-      <c r="E381" s="6">
+      <c r="D381" s="5">
+        <v>1</v>
+      </c>
+      <c r="E381" s="5">
         <v>1</v>
       </c>
       <c r="F381" t="s">
@@ -20239,10 +20284,10 @@
       <c r="C382" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D382" s="6">
-        <v>1</v>
-      </c>
-      <c r="E382" s="6">
+      <c r="D382" s="5">
+        <v>1</v>
+      </c>
+      <c r="E382" s="5">
         <v>1</v>
       </c>
       <c r="F382" t="s">
@@ -20274,10 +20319,10 @@
       <c r="C383" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D383" s="6">
-        <v>1</v>
-      </c>
-      <c r="E383" s="6">
+      <c r="D383" s="5">
+        <v>1</v>
+      </c>
+      <c r="E383" s="5">
         <v>1</v>
       </c>
       <c r="F383" t="s">
@@ -20309,10 +20354,10 @@
       <c r="C384" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D384" s="6">
-        <v>1</v>
-      </c>
-      <c r="E384" s="6">
+      <c r="D384" s="5">
+        <v>1</v>
+      </c>
+      <c r="E384" s="5">
         <v>1</v>
       </c>
       <c r="F384" t="s">
@@ -20344,10 +20389,10 @@
       <c r="C385" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D385" s="6">
-        <v>1</v>
-      </c>
-      <c r="E385" s="6">
+      <c r="D385" s="5">
+        <v>1</v>
+      </c>
+      <c r="E385" s="5">
         <v>1</v>
       </c>
       <c r="F385" t="s">
@@ -20379,10 +20424,10 @@
       <c r="C386" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D386" s="6">
-        <v>1</v>
-      </c>
-      <c r="E386" s="6">
+      <c r="D386" s="5">
+        <v>1</v>
+      </c>
+      <c r="E386" s="5">
         <v>1</v>
       </c>
       <c r="F386" t="s">
@@ -20414,10 +20459,10 @@
       <c r="C387" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D387" s="6">
-        <v>1</v>
-      </c>
-      <c r="E387" s="6">
+      <c r="D387" s="5">
+        <v>1</v>
+      </c>
+      <c r="E387" s="5">
         <v>1</v>
       </c>
       <c r="F387" t="s">
@@ -20449,10 +20494,10 @@
       <c r="C388" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D388" s="6">
-        <v>1</v>
-      </c>
-      <c r="E388" s="6">
+      <c r="D388" s="5">
+        <v>1</v>
+      </c>
+      <c r="E388" s="5">
         <v>1</v>
       </c>
       <c r="F388" t="s">
@@ -20484,10 +20529,10 @@
       <c r="C389" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D389" s="6">
-        <v>1</v>
-      </c>
-      <c r="E389" s="6">
+      <c r="D389" s="5">
+        <v>1</v>
+      </c>
+      <c r="E389" s="5">
         <v>1</v>
       </c>
       <c r="F389" t="s">
@@ -20519,10 +20564,10 @@
       <c r="C390" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D390" s="6">
-        <v>1</v>
-      </c>
-      <c r="E390" s="6">
+      <c r="D390" s="5">
+        <v>1</v>
+      </c>
+      <c r="E390" s="5">
         <v>1</v>
       </c>
       <c r="F390" t="s">
@@ -20554,10 +20599,10 @@
       <c r="C391" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D391" s="6">
-        <v>1</v>
-      </c>
-      <c r="E391" s="6">
+      <c r="D391" s="5">
+        <v>1</v>
+      </c>
+      <c r="E391" s="5">
         <v>1</v>
       </c>
       <c r="F391" t="s">
@@ -20589,10 +20634,10 @@
       <c r="C392" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D392" s="6">
-        <v>1</v>
-      </c>
-      <c r="E392" s="6">
+      <c r="D392" s="5">
+        <v>1</v>
+      </c>
+      <c r="E392" s="5">
         <v>1</v>
       </c>
       <c r="F392" t="s">
@@ -20624,10 +20669,10 @@
       <c r="C393" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D393" s="6">
-        <v>1</v>
-      </c>
-      <c r="E393" s="6">
+      <c r="D393" s="5">
+        <v>1</v>
+      </c>
+      <c r="E393" s="5">
         <v>1</v>
       </c>
       <c r="F393" t="s">
@@ -20659,10 +20704,10 @@
       <c r="C394" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D394" s="6">
-        <v>1</v>
-      </c>
-      <c r="E394" s="6">
+      <c r="D394" s="5">
+        <v>1</v>
+      </c>
+      <c r="E394" s="5">
         <v>1</v>
       </c>
       <c r="F394" t="s">
@@ -20694,10 +20739,10 @@
       <c r="C395" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D395" s="6">
-        <v>1</v>
-      </c>
-      <c r="E395" s="6">
+      <c r="D395" s="5">
+        <v>1</v>
+      </c>
+      <c r="E395" s="5">
         <v>1</v>
       </c>
       <c r="F395" t="s">
@@ -20729,10 +20774,10 @@
       <c r="C396" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D396" s="6">
-        <v>1</v>
-      </c>
-      <c r="E396" s="6">
+      <c r="D396" s="5">
+        <v>1</v>
+      </c>
+      <c r="E396" s="5">
         <v>1</v>
       </c>
       <c r="F396" t="s">
@@ -20764,10 +20809,10 @@
       <c r="C397" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D397" s="6">
-        <v>1</v>
-      </c>
-      <c r="E397" s="6">
+      <c r="D397" s="5">
+        <v>1</v>
+      </c>
+      <c r="E397" s="5">
         <v>1</v>
       </c>
       <c r="F397" t="s">
@@ -20799,10 +20844,10 @@
       <c r="C398" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D398" s="6">
-        <v>1</v>
-      </c>
-      <c r="E398" s="6">
+      <c r="D398" s="5">
+        <v>1</v>
+      </c>
+      <c r="E398" s="5">
         <v>1</v>
       </c>
       <c r="F398" t="s">
@@ -20834,10 +20879,10 @@
       <c r="C399" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D399" s="6">
-        <v>1</v>
-      </c>
-      <c r="E399" s="6">
+      <c r="D399" s="5">
+        <v>1</v>
+      </c>
+      <c r="E399" s="5">
         <v>1</v>
       </c>
       <c r="F399" t="s">
@@ -20869,10 +20914,10 @@
       <c r="C400" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D400" s="6">
-        <v>1</v>
-      </c>
-      <c r="E400" s="6">
+      <c r="D400" s="5">
+        <v>1</v>
+      </c>
+      <c r="E400" s="5">
         <v>1</v>
       </c>
       <c r="F400" t="s">
@@ -20904,10 +20949,10 @@
       <c r="C401" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="D401" s="6">
-        <v>1</v>
-      </c>
-      <c r="E401" s="6">
+      <c r="D401" s="5">
+        <v>1</v>
+      </c>
+      <c r="E401" s="5">
         <v>1</v>
       </c>
       <c r="F401" t="s">
@@ -20939,10 +20984,10 @@
       <c r="C402" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D402" s="6">
-        <v>1</v>
-      </c>
-      <c r="E402" s="6">
+      <c r="D402" s="5">
+        <v>1</v>
+      </c>
+      <c r="E402" s="5">
         <v>1</v>
       </c>
       <c r="F402" t="s">
@@ -20974,10 +21019,10 @@
       <c r="C403" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D403" s="6">
-        <v>1</v>
-      </c>
-      <c r="E403" s="6">
+      <c r="D403" s="5">
+        <v>1</v>
+      </c>
+      <c r="E403" s="5">
         <v>1</v>
       </c>
       <c r="F403" t="s">
@@ -21009,10 +21054,10 @@
       <c r="C404" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D404" s="6">
-        <v>1</v>
-      </c>
-      <c r="E404" s="6">
+      <c r="D404" s="5">
+        <v>1</v>
+      </c>
+      <c r="E404" s="5">
         <v>1</v>
       </c>
       <c r="F404" t="s">
@@ -21044,10 +21089,10 @@
       <c r="C405" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D405" s="6">
-        <v>1</v>
-      </c>
-      <c r="E405" s="6">
+      <c r="D405" s="5">
+        <v>1</v>
+      </c>
+      <c r="E405" s="5">
         <v>1</v>
       </c>
       <c r="F405" t="s">
@@ -21079,10 +21124,10 @@
       <c r="C406" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D406" s="6">
-        <v>1</v>
-      </c>
-      <c r="E406" s="6">
+      <c r="D406" s="5">
+        <v>1</v>
+      </c>
+      <c r="E406" s="5">
         <v>1</v>
       </c>
       <c r="F406" t="s">
@@ -21114,10 +21159,10 @@
       <c r="C407" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D407" s="6">
-        <v>1</v>
-      </c>
-      <c r="E407" s="6">
+      <c r="D407" s="5">
+        <v>1</v>
+      </c>
+      <c r="E407" s="5">
         <v>1</v>
       </c>
       <c r="F407" t="s">
@@ -21149,10 +21194,10 @@
       <c r="C408" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D408" s="6">
-        <v>1</v>
-      </c>
-      <c r="E408" s="6">
+      <c r="D408" s="5">
+        <v>1</v>
+      </c>
+      <c r="E408" s="5">
         <v>1</v>
       </c>
       <c r="F408" t="s">
@@ -21184,10 +21229,10 @@
       <c r="C409" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D409" s="6">
-        <v>1</v>
-      </c>
-      <c r="E409" s="6">
+      <c r="D409" s="5">
+        <v>1</v>
+      </c>
+      <c r="E409" s="5">
         <v>1</v>
       </c>
       <c r="F409" t="s">
@@ -21219,10 +21264,10 @@
       <c r="C410" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D410" s="6">
-        <v>1</v>
-      </c>
-      <c r="E410" s="6">
+      <c r="D410" s="5">
+        <v>1</v>
+      </c>
+      <c r="E410" s="5">
         <v>1</v>
       </c>
       <c r="F410" t="s">
@@ -21254,10 +21299,10 @@
       <c r="C411" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D411" s="6">
-        <v>1</v>
-      </c>
-      <c r="E411" s="6">
+      <c r="D411" s="5">
+        <v>1</v>
+      </c>
+      <c r="E411" s="5">
         <v>1</v>
       </c>
       <c r="F411" t="s">
@@ -21289,10 +21334,10 @@
       <c r="C412" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D412" s="6">
-        <v>1</v>
-      </c>
-      <c r="E412" s="6">
+      <c r="D412" s="5">
+        <v>1</v>
+      </c>
+      <c r="E412" s="5">
         <v>1</v>
       </c>
       <c r="F412" t="s">
@@ -21324,10 +21369,10 @@
       <c r="C413" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D413" s="6">
-        <v>1</v>
-      </c>
-      <c r="E413" s="6">
+      <c r="D413" s="5">
+        <v>1</v>
+      </c>
+      <c r="E413" s="5">
         <v>1</v>
       </c>
       <c r="F413" t="s">
@@ -21359,10 +21404,10 @@
       <c r="C414" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D414" s="6">
-        <v>1</v>
-      </c>
-      <c r="E414" s="6">
+      <c r="D414" s="5">
+        <v>1</v>
+      </c>
+      <c r="E414" s="5">
         <v>1</v>
       </c>
       <c r="F414" t="s">
@@ -21394,10 +21439,10 @@
       <c r="C415" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D415" s="6">
-        <v>1</v>
-      </c>
-      <c r="E415" s="6">
+      <c r="D415" s="5">
+        <v>1</v>
+      </c>
+      <c r="E415" s="5">
         <v>1</v>
       </c>
       <c r="F415" t="s">
@@ -21429,10 +21474,10 @@
       <c r="C416" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D416" s="6">
-        <v>1</v>
-      </c>
-      <c r="E416" s="6">
+      <c r="D416" s="5">
+        <v>1</v>
+      </c>
+      <c r="E416" s="5">
         <v>1</v>
       </c>
       <c r="F416" t="s">
@@ -21464,10 +21509,10 @@
       <c r="C417" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D417" s="6">
-        <v>1</v>
-      </c>
-      <c r="E417" s="6">
+      <c r="D417" s="5">
+        <v>1</v>
+      </c>
+      <c r="E417" s="5">
         <v>1</v>
       </c>
       <c r="F417" t="s">
@@ -21499,10 +21544,10 @@
       <c r="C418" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D418" s="6">
-        <v>1</v>
-      </c>
-      <c r="E418" s="6">
+      <c r="D418" s="5">
+        <v>1</v>
+      </c>
+      <c r="E418" s="5">
         <v>1</v>
       </c>
       <c r="F418" t="s">
@@ -21534,10 +21579,10 @@
       <c r="C419" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D419" s="6">
-        <v>1</v>
-      </c>
-      <c r="E419" s="6">
+      <c r="D419" s="5">
+        <v>1</v>
+      </c>
+      <c r="E419" s="5">
         <v>1</v>
       </c>
       <c r="F419" t="s">
@@ -21569,10 +21614,10 @@
       <c r="C420" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D420" s="6">
-        <v>1</v>
-      </c>
-      <c r="E420" s="6">
+      <c r="D420" s="5">
+        <v>1</v>
+      </c>
+      <c r="E420" s="5">
         <v>1</v>
       </c>
       <c r="F420" t="s">
@@ -21604,10 +21649,10 @@
       <c r="C421" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D421" s="6">
-        <v>1</v>
-      </c>
-      <c r="E421" s="6">
+      <c r="D421" s="5">
+        <v>1</v>
+      </c>
+      <c r="E421" s="5">
         <v>1</v>
       </c>
       <c r="F421" t="s">
@@ -21639,10 +21684,10 @@
       <c r="C422" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D422" s="6">
-        <v>1</v>
-      </c>
-      <c r="E422" s="6">
+      <c r="D422" s="5">
+        <v>1</v>
+      </c>
+      <c r="E422" s="5">
         <v>1</v>
       </c>
       <c r="F422" t="s">
@@ -21674,10 +21719,10 @@
       <c r="C423" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D423" s="6">
-        <v>1</v>
-      </c>
-      <c r="E423" s="6">
+      <c r="D423" s="5">
+        <v>1</v>
+      </c>
+      <c r="E423" s="5">
         <v>1</v>
       </c>
       <c r="F423" t="s">
@@ -21709,10 +21754,10 @@
       <c r="C424" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D424" s="6">
-        <v>1</v>
-      </c>
-      <c r="E424" s="6">
+      <c r="D424" s="5">
+        <v>1</v>
+      </c>
+      <c r="E424" s="5">
         <v>1</v>
       </c>
       <c r="F424" t="s">
@@ -21744,10 +21789,10 @@
       <c r="C425" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D425" s="6">
-        <v>1</v>
-      </c>
-      <c r="E425" s="6">
+      <c r="D425" s="5">
+        <v>1</v>
+      </c>
+      <c r="E425" s="5">
         <v>1</v>
       </c>
       <c r="F425" t="s">
@@ -21779,10 +21824,10 @@
       <c r="C426" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D426" s="6">
-        <v>1</v>
-      </c>
-      <c r="E426" s="6">
+      <c r="D426" s="5">
+        <v>1</v>
+      </c>
+      <c r="E426" s="5">
         <v>1</v>
       </c>
       <c r="F426" t="s">
@@ -21814,10 +21859,10 @@
       <c r="C427" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D427" s="6">
-        <v>1</v>
-      </c>
-      <c r="E427" s="6">
+      <c r="D427" s="5">
+        <v>1</v>
+      </c>
+      <c r="E427" s="5">
         <v>1</v>
       </c>
       <c r="F427" t="s">
@@ -21849,10 +21894,10 @@
       <c r="C428" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D428" s="6">
-        <v>1</v>
-      </c>
-      <c r="E428" s="6">
+      <c r="D428" s="5">
+        <v>1</v>
+      </c>
+      <c r="E428" s="5">
         <v>1</v>
       </c>
       <c r="F428" t="s">
@@ -21884,10 +21929,10 @@
       <c r="C429" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D429" s="6">
-        <v>1</v>
-      </c>
-      <c r="E429" s="6">
+      <c r="D429" s="5">
+        <v>1</v>
+      </c>
+      <c r="E429" s="5">
         <v>1</v>
       </c>
       <c r="F429" t="s">
@@ -21919,10 +21964,10 @@
       <c r="C430" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D430" s="6">
-        <v>1</v>
-      </c>
-      <c r="E430" s="6">
+      <c r="D430" s="5">
+        <v>1</v>
+      </c>
+      <c r="E430" s="5">
         <v>1</v>
       </c>
       <c r="F430" t="s">
@@ -21954,10 +21999,10 @@
       <c r="C431" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D431" s="6">
-        <v>1</v>
-      </c>
-      <c r="E431" s="6">
+      <c r="D431" s="5">
+        <v>1</v>
+      </c>
+      <c r="E431" s="5">
         <v>1</v>
       </c>
       <c r="F431" t="s">
@@ -21989,10 +22034,10 @@
       <c r="C432" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D432" s="6">
-        <v>1</v>
-      </c>
-      <c r="E432" s="6">
+      <c r="D432" s="5">
+        <v>1</v>
+      </c>
+      <c r="E432" s="5">
         <v>1</v>
       </c>
       <c r="F432" t="s">
@@ -22024,10 +22069,10 @@
       <c r="C433" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D433" s="6">
-        <v>1</v>
-      </c>
-      <c r="E433" s="6">
+      <c r="D433" s="5">
+        <v>1</v>
+      </c>
+      <c r="E433" s="5">
         <v>1</v>
       </c>
       <c r="F433" t="s">
@@ -22059,10 +22104,10 @@
       <c r="C434" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D434" s="6">
-        <v>1</v>
-      </c>
-      <c r="E434" s="6">
+      <c r="D434" s="5">
+        <v>1</v>
+      </c>
+      <c r="E434" s="5">
         <v>1</v>
       </c>
       <c r="F434" t="s">
@@ -22094,10 +22139,10 @@
       <c r="C435" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D435" s="6">
-        <v>1</v>
-      </c>
-      <c r="E435" s="6">
+      <c r="D435" s="5">
+        <v>1</v>
+      </c>
+      <c r="E435" s="5">
         <v>1</v>
       </c>
       <c r="F435" t="s">
@@ -22129,10 +22174,10 @@
       <c r="C436" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D436" s="6">
-        <v>1</v>
-      </c>
-      <c r="E436" s="6">
+      <c r="D436" s="5">
+        <v>1</v>
+      </c>
+      <c r="E436" s="5">
         <v>1</v>
       </c>
       <c r="F436" t="s">
@@ -22164,10 +22209,10 @@
       <c r="C437" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D437" s="6">
-        <v>1</v>
-      </c>
-      <c r="E437" s="6">
+      <c r="D437" s="5">
+        <v>1</v>
+      </c>
+      <c r="E437" s="5">
         <v>1</v>
       </c>
       <c r="F437" t="s">
@@ -22199,10 +22244,10 @@
       <c r="C438" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D438" s="6">
-        <v>1</v>
-      </c>
-      <c r="E438" s="6">
+      <c r="D438" s="5">
+        <v>1</v>
+      </c>
+      <c r="E438" s="5">
         <v>1</v>
       </c>
       <c r="F438" t="s">
@@ -22234,10 +22279,10 @@
       <c r="C439" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D439" s="6">
-        <v>1</v>
-      </c>
-      <c r="E439" s="6">
+      <c r="D439" s="5">
+        <v>1</v>
+      </c>
+      <c r="E439" s="5">
         <v>1</v>
       </c>
       <c r="F439" t="s">
@@ -22269,10 +22314,10 @@
       <c r="C440" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D440" s="6">
-        <v>1</v>
-      </c>
-      <c r="E440" s="6">
+      <c r="D440" s="5">
+        <v>1</v>
+      </c>
+      <c r="E440" s="5">
         <v>1</v>
       </c>
       <c r="F440" t="s">
@@ -22304,10 +22349,10 @@
       <c r="C441" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D441" s="6">
-        <v>1</v>
-      </c>
-      <c r="E441" s="6">
+      <c r="D441" s="5">
+        <v>1</v>
+      </c>
+      <c r="E441" s="5">
         <v>1</v>
       </c>
       <c r="F441" t="s">
@@ -22339,10 +22384,10 @@
       <c r="C442" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D442" s="6">
-        <v>1</v>
-      </c>
-      <c r="E442" s="6">
+      <c r="D442" s="5">
+        <v>1</v>
+      </c>
+      <c r="E442" s="5">
         <v>1</v>
       </c>
       <c r="F442" t="s">
@@ -22374,10 +22419,10 @@
       <c r="C443" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D443" s="6">
-        <v>1</v>
-      </c>
-      <c r="E443" s="6">
+      <c r="D443" s="5">
+        <v>1</v>
+      </c>
+      <c r="E443" s="5">
         <v>1</v>
       </c>
       <c r="F443" t="s">
@@ -22409,10 +22454,10 @@
       <c r="C444" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D444" s="6">
-        <v>1</v>
-      </c>
-      <c r="E444" s="6">
+      <c r="D444" s="5">
+        <v>1</v>
+      </c>
+      <c r="E444" s="5">
         <v>1</v>
       </c>
       <c r="F444" t="s">
@@ -22444,10 +22489,10 @@
       <c r="C445" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D445" s="6">
-        <v>1</v>
-      </c>
-      <c r="E445" s="6">
+      <c r="D445" s="5">
+        <v>1</v>
+      </c>
+      <c r="E445" s="5">
         <v>1</v>
       </c>
       <c r="F445" t="s">
@@ -22479,10 +22524,10 @@
       <c r="C446" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D446" s="6">
-        <v>1</v>
-      </c>
-      <c r="E446" s="6">
+      <c r="D446" s="5">
+        <v>1</v>
+      </c>
+      <c r="E446" s="5">
         <v>1</v>
       </c>
       <c r="F446" t="s">
@@ -22514,10 +22559,10 @@
       <c r="C447" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D447" s="6">
-        <v>1</v>
-      </c>
-      <c r="E447" s="6">
+      <c r="D447" s="5">
+        <v>1</v>
+      </c>
+      <c r="E447" s="5">
         <v>1</v>
       </c>
       <c r="F447" t="s">
@@ -22549,10 +22594,10 @@
       <c r="C448" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D448" s="6">
-        <v>1</v>
-      </c>
-      <c r="E448" s="6">
+      <c r="D448" s="5">
+        <v>1</v>
+      </c>
+      <c r="E448" s="5">
         <v>1</v>
       </c>
       <c r="F448" t="s">
@@ -22584,10 +22629,10 @@
       <c r="C449" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D449" s="6">
-        <v>1</v>
-      </c>
-      <c r="E449" s="6">
+      <c r="D449" s="5">
+        <v>1</v>
+      </c>
+      <c r="E449" s="5">
         <v>1</v>
       </c>
       <c r="F449" t="s">
@@ -22619,10 +22664,10 @@
       <c r="C450" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D450" s="6">
-        <v>1</v>
-      </c>
-      <c r="E450" s="6">
+      <c r="D450" s="5">
+        <v>1</v>
+      </c>
+      <c r="E450" s="5">
         <v>1</v>
       </c>
       <c r="F450" t="s">
@@ -22654,10 +22699,10 @@
       <c r="C451" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="D451" s="6">
-        <v>1</v>
-      </c>
-      <c r="E451" s="6">
+      <c r="D451" s="5">
+        <v>1</v>
+      </c>
+      <c r="E451" s="5">
         <v>1</v>
       </c>
       <c r="F451" t="s">
@@ -22689,10 +22734,10 @@
       <c r="C452" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D452" s="6">
-        <v>1</v>
-      </c>
-      <c r="E452" s="6">
+      <c r="D452" s="5">
+        <v>1</v>
+      </c>
+      <c r="E452" s="5">
         <v>1</v>
       </c>
       <c r="F452" t="s">
@@ -22724,10 +22769,10 @@
       <c r="C453" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D453" s="6">
-        <v>1</v>
-      </c>
-      <c r="E453" s="6">
+      <c r="D453" s="5">
+        <v>1</v>
+      </c>
+      <c r="E453" s="5">
         <v>1</v>
       </c>
       <c r="F453" t="s">
@@ -22759,10 +22804,10 @@
       <c r="C454" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D454" s="6">
-        <v>1</v>
-      </c>
-      <c r="E454" s="6">
+      <c r="D454" s="5">
+        <v>1</v>
+      </c>
+      <c r="E454" s="5">
         <v>1</v>
       </c>
       <c r="F454" t="s">
@@ -22794,10 +22839,10 @@
       <c r="C455" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D455" s="6">
-        <v>1</v>
-      </c>
-      <c r="E455" s="6">
+      <c r="D455" s="5">
+        <v>1</v>
+      </c>
+      <c r="E455" s="5">
         <v>1</v>
       </c>
       <c r="F455" t="s">
@@ -22829,10 +22874,10 @@
       <c r="C456" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D456" s="6">
-        <v>1</v>
-      </c>
-      <c r="E456" s="6">
+      <c r="D456" s="5">
+        <v>1</v>
+      </c>
+      <c r="E456" s="5">
         <v>1</v>
       </c>
       <c r="F456" t="s">
@@ -22864,10 +22909,10 @@
       <c r="C457" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D457" s="6">
-        <v>1</v>
-      </c>
-      <c r="E457" s="6">
+      <c r="D457" s="5">
+        <v>1</v>
+      </c>
+      <c r="E457" s="5">
         <v>1</v>
       </c>
       <c r="F457" t="s">
@@ -22899,10 +22944,10 @@
       <c r="C458" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D458" s="6">
-        <v>1</v>
-      </c>
-      <c r="E458" s="6">
+      <c r="D458" s="5">
+        <v>1</v>
+      </c>
+      <c r="E458" s="5">
         <v>1</v>
       </c>
       <c r="F458" t="s">
@@ -22934,10 +22979,10 @@
       <c r="C459" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D459" s="6">
-        <v>1</v>
-      </c>
-      <c r="E459" s="6">
+      <c r="D459" s="5">
+        <v>1</v>
+      </c>
+      <c r="E459" s="5">
         <v>1</v>
       </c>
       <c r="F459" t="s">
@@ -22969,10 +23014,10 @@
       <c r="C460" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D460" s="6">
-        <v>1</v>
-      </c>
-      <c r="E460" s="6">
+      <c r="D460" s="5">
+        <v>1</v>
+      </c>
+      <c r="E460" s="5">
         <v>1</v>
       </c>
       <c r="F460" t="s">
@@ -23004,10 +23049,10 @@
       <c r="C461" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D461" s="6">
-        <v>1</v>
-      </c>
-      <c r="E461" s="6">
+      <c r="D461" s="5">
+        <v>1</v>
+      </c>
+      <c r="E461" s="5">
         <v>1</v>
       </c>
       <c r="F461" t="s">
@@ -23039,10 +23084,10 @@
       <c r="C462" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D462" s="6">
-        <v>1</v>
-      </c>
-      <c r="E462" s="6">
+      <c r="D462" s="5">
+        <v>1</v>
+      </c>
+      <c r="E462" s="5">
         <v>1</v>
       </c>
       <c r="F462" t="s">
@@ -23074,10 +23119,10 @@
       <c r="C463" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D463" s="6">
-        <v>1</v>
-      </c>
-      <c r="E463" s="6">
+      <c r="D463" s="5">
+        <v>1</v>
+      </c>
+      <c r="E463" s="5">
         <v>1</v>
       </c>
       <c r="F463" t="s">
@@ -23109,10 +23154,10 @@
       <c r="C464" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D464" s="6">
-        <v>1</v>
-      </c>
-      <c r="E464" s="6">
+      <c r="D464" s="5">
+        <v>1</v>
+      </c>
+      <c r="E464" s="5">
         <v>1</v>
       </c>
       <c r="F464" t="s">
@@ -23144,10 +23189,10 @@
       <c r="C465" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D465" s="6">
-        <v>1</v>
-      </c>
-      <c r="E465" s="6">
+      <c r="D465" s="5">
+        <v>1</v>
+      </c>
+      <c r="E465" s="5">
         <v>1</v>
       </c>
       <c r="F465" t="s">
@@ -23179,10 +23224,10 @@
       <c r="C466" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D466" s="6">
-        <v>1</v>
-      </c>
-      <c r="E466" s="6">
+      <c r="D466" s="5">
+        <v>1</v>
+      </c>
+      <c r="E466" s="5">
         <v>1</v>
       </c>
       <c r="F466" t="s">
@@ -23214,10 +23259,10 @@
       <c r="C467" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D467" s="6">
-        <v>1</v>
-      </c>
-      <c r="E467" s="6">
+      <c r="D467" s="5">
+        <v>1</v>
+      </c>
+      <c r="E467" s="5">
         <v>1</v>
       </c>
       <c r="F467" t="s">
@@ -23249,10 +23294,10 @@
       <c r="C468" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D468" s="6">
-        <v>1</v>
-      </c>
-      <c r="E468" s="6">
+      <c r="D468" s="5">
+        <v>1</v>
+      </c>
+      <c r="E468" s="5">
         <v>1</v>
       </c>
       <c r="F468" t="s">
@@ -23284,10 +23329,10 @@
       <c r="C469" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D469" s="6">
-        <v>1</v>
-      </c>
-      <c r="E469" s="6">
+      <c r="D469" s="5">
+        <v>1</v>
+      </c>
+      <c r="E469" s="5">
         <v>1</v>
       </c>
       <c r="F469" t="s">
@@ -23319,10 +23364,10 @@
       <c r="C470" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D470" s="6">
-        <v>1</v>
-      </c>
-      <c r="E470" s="6">
+      <c r="D470" s="5">
+        <v>1</v>
+      </c>
+      <c r="E470" s="5">
         <v>1</v>
       </c>
       <c r="F470" t="s">
@@ -23354,10 +23399,10 @@
       <c r="C471" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D471" s="6">
-        <v>1</v>
-      </c>
-      <c r="E471" s="6">
+      <c r="D471" s="5">
+        <v>1</v>
+      </c>
+      <c r="E471" s="5">
         <v>1</v>
       </c>
       <c r="F471" t="s">
@@ -23389,10 +23434,10 @@
       <c r="C472" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D472" s="6">
-        <v>1</v>
-      </c>
-      <c r="E472" s="6">
+      <c r="D472" s="5">
+        <v>1</v>
+      </c>
+      <c r="E472" s="5">
         <v>1</v>
       </c>
       <c r="F472" t="s">
@@ -23424,10 +23469,10 @@
       <c r="C473" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D473" s="6">
-        <v>1</v>
-      </c>
-      <c r="E473" s="6">
+      <c r="D473" s="5">
+        <v>1</v>
+      </c>
+      <c r="E473" s="5">
         <v>1</v>
       </c>
       <c r="F473" t="s">
@@ -23459,10 +23504,10 @@
       <c r="C474" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D474" s="6">
-        <v>1</v>
-      </c>
-      <c r="E474" s="6">
+      <c r="D474" s="5">
+        <v>1</v>
+      </c>
+      <c r="E474" s="5">
         <v>1</v>
       </c>
       <c r="F474" t="s">
@@ -23494,10 +23539,10 @@
       <c r="C475" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D475" s="6">
-        <v>1</v>
-      </c>
-      <c r="E475" s="6">
+      <c r="D475" s="5">
+        <v>1</v>
+      </c>
+      <c r="E475" s="5">
         <v>1</v>
       </c>
       <c r="F475" t="s">
@@ -23529,10 +23574,10 @@
       <c r="C476" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D476" s="6">
-        <v>1</v>
-      </c>
-      <c r="E476" s="6">
+      <c r="D476" s="5">
+        <v>1</v>
+      </c>
+      <c r="E476" s="5">
         <v>1</v>
       </c>
       <c r="F476" t="s">
@@ -23564,10 +23609,10 @@
       <c r="C477" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D477" s="6">
-        <v>1</v>
-      </c>
-      <c r="E477" s="6">
+      <c r="D477" s="5">
+        <v>1</v>
+      </c>
+      <c r="E477" s="5">
         <v>1</v>
       </c>
       <c r="F477" t="s">
@@ -23599,10 +23644,10 @@
       <c r="C478" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D478" s="6">
-        <v>1</v>
-      </c>
-      <c r="E478" s="6">
+      <c r="D478" s="5">
+        <v>1</v>
+      </c>
+      <c r="E478" s="5">
         <v>1</v>
       </c>
       <c r="F478" t="s">
@@ -23634,10 +23679,10 @@
       <c r="C479" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D479" s="6">
-        <v>1</v>
-      </c>
-      <c r="E479" s="6">
+      <c r="D479" s="5">
+        <v>1</v>
+      </c>
+      <c r="E479" s="5">
         <v>1</v>
       </c>
       <c r="F479" t="s">
@@ -23669,10 +23714,10 @@
       <c r="C480" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D480" s="6">
-        <v>1</v>
-      </c>
-      <c r="E480" s="6">
+      <c r="D480" s="5">
+        <v>1</v>
+      </c>
+      <c r="E480" s="5">
         <v>1</v>
       </c>
       <c r="F480" t="s">
@@ -23704,10 +23749,10 @@
       <c r="C481" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D481" s="6">
-        <v>1</v>
-      </c>
-      <c r="E481" s="6">
+      <c r="D481" s="5">
+        <v>1</v>
+      </c>
+      <c r="E481" s="5">
         <v>1</v>
       </c>
       <c r="F481" t="s">
@@ -23739,10 +23784,10 @@
       <c r="C482" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D482" s="6">
-        <v>1</v>
-      </c>
-      <c r="E482" s="6">
+      <c r="D482" s="5">
+        <v>1</v>
+      </c>
+      <c r="E482" s="5">
         <v>1</v>
       </c>
       <c r="F482" t="s">
@@ -23774,10 +23819,10 @@
       <c r="C483" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D483" s="6">
-        <v>1</v>
-      </c>
-      <c r="E483" s="6">
+      <c r="D483" s="5">
+        <v>1</v>
+      </c>
+      <c r="E483" s="5">
         <v>1</v>
       </c>
       <c r="F483" t="s">
@@ -23809,10 +23854,10 @@
       <c r="C484" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D484" s="6">
-        <v>1</v>
-      </c>
-      <c r="E484" s="6">
+      <c r="D484" s="5">
+        <v>1</v>
+      </c>
+      <c r="E484" s="5">
         <v>1</v>
       </c>
       <c r="F484" t="s">
@@ -23844,10 +23889,10 @@
       <c r="C485" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D485" s="6">
-        <v>1</v>
-      </c>
-      <c r="E485" s="6">
+      <c r="D485" s="5">
+        <v>1</v>
+      </c>
+      <c r="E485" s="5">
         <v>1</v>
       </c>
       <c r="F485" t="s">
@@ -23879,10 +23924,10 @@
       <c r="C486" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D486" s="6">
-        <v>1</v>
-      </c>
-      <c r="E486" s="6">
+      <c r="D486" s="5">
+        <v>1</v>
+      </c>
+      <c r="E486" s="5">
         <v>1</v>
       </c>
       <c r="F486" s="2" t="s">
@@ -23914,10 +23959,10 @@
       <c r="C487" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D487" s="6">
-        <v>1</v>
-      </c>
-      <c r="E487" s="6">
+      <c r="D487" s="5">
+        <v>1</v>
+      </c>
+      <c r="E487" s="5">
         <v>1</v>
       </c>
       <c r="F487" s="2" t="s">
@@ -23949,10 +23994,10 @@
       <c r="C488" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D488" s="6">
-        <v>1</v>
-      </c>
-      <c r="E488" s="6">
+      <c r="D488" s="5">
+        <v>1</v>
+      </c>
+      <c r="E488" s="5">
         <v>1</v>
       </c>
       <c r="F488" s="2" t="s">
@@ -23984,10 +24029,10 @@
       <c r="C489" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D489" s="6">
-        <v>1</v>
-      </c>
-      <c r="E489" s="6">
+      <c r="D489" s="5">
+        <v>1</v>
+      </c>
+      <c r="E489" s="5">
         <v>1</v>
       </c>
       <c r="F489" s="2" t="s">
@@ -24019,10 +24064,10 @@
       <c r="C490" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D490" s="6">
-        <v>1</v>
-      </c>
-      <c r="E490" s="6">
+      <c r="D490" s="5">
+        <v>1</v>
+      </c>
+      <c r="E490" s="5">
         <v>1</v>
       </c>
       <c r="F490" s="2" t="s">
@@ -24054,10 +24099,10 @@
       <c r="C491" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D491" s="6">
-        <v>1</v>
-      </c>
-      <c r="E491" s="6">
+      <c r="D491" s="5">
+        <v>1</v>
+      </c>
+      <c r="E491" s="5">
         <v>1</v>
       </c>
       <c r="F491" s="2" t="s">
@@ -24089,10 +24134,10 @@
       <c r="C492" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D492" s="6">
-        <v>1</v>
-      </c>
-      <c r="E492" s="6">
+      <c r="D492" s="5">
+        <v>1</v>
+      </c>
+      <c r="E492" s="5">
         <v>1</v>
       </c>
       <c r="F492" s="2" t="s">
@@ -24124,10 +24169,10 @@
       <c r="C493" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D493" s="6">
-        <v>1</v>
-      </c>
-      <c r="E493" s="6">
+      <c r="D493" s="5">
+        <v>1</v>
+      </c>
+      <c r="E493" s="5">
         <v>1</v>
       </c>
       <c r="F493" s="2" t="s">
@@ -24159,10 +24204,10 @@
       <c r="C494" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D494" s="6">
-        <v>1</v>
-      </c>
-      <c r="E494" s="6">
+      <c r="D494" s="5">
+        <v>1</v>
+      </c>
+      <c r="E494" s="5">
         <v>1</v>
       </c>
       <c r="F494" s="2" t="s">
@@ -24194,10 +24239,10 @@
       <c r="C495" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D495" s="6">
-        <v>1</v>
-      </c>
-      <c r="E495" s="6">
+      <c r="D495" s="5">
+        <v>1</v>
+      </c>
+      <c r="E495" s="5">
         <v>1</v>
       </c>
       <c r="F495" s="2" t="s">
@@ -24229,10 +24274,10 @@
       <c r="C496" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D496" s="6">
-        <v>1</v>
-      </c>
-      <c r="E496" s="6">
+      <c r="D496" s="5">
+        <v>1</v>
+      </c>
+      <c r="E496" s="5">
         <v>1</v>
       </c>
       <c r="F496" t="s">
@@ -24264,10 +24309,10 @@
       <c r="C497" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D497" s="6">
-        <v>1</v>
-      </c>
-      <c r="E497" s="6">
+      <c r="D497" s="5">
+        <v>1</v>
+      </c>
+      <c r="E497" s="5">
         <v>1</v>
       </c>
       <c r="F497" t="s">
@@ -24299,10 +24344,10 @@
       <c r="C498" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D498" s="6">
-        <v>1</v>
-      </c>
-      <c r="E498" s="6">
+      <c r="D498" s="5">
+        <v>1</v>
+      </c>
+      <c r="E498" s="5">
         <v>1</v>
       </c>
       <c r="F498" t="s">
@@ -24334,10 +24379,10 @@
       <c r="C499" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D499" s="6">
-        <v>1</v>
-      </c>
-      <c r="E499" s="6">
+      <c r="D499" s="5">
+        <v>1</v>
+      </c>
+      <c r="E499" s="5">
         <v>1</v>
       </c>
       <c r="F499" t="s">
@@ -24369,10 +24414,10 @@
       <c r="C500" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D500" s="6">
-        <v>1</v>
-      </c>
-      <c r="E500" s="6">
+      <c r="D500" s="5">
+        <v>1</v>
+      </c>
+      <c r="E500" s="5">
         <v>1</v>
       </c>
       <c r="F500" t="s">
@@ -24404,10 +24449,10 @@
       <c r="C501" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="D501" s="6">
-        <v>1</v>
-      </c>
-      <c r="E501" s="6">
+      <c r="D501" s="5">
+        <v>1</v>
+      </c>
+      <c r="E501" s="5">
         <v>1</v>
       </c>
       <c r="F501" t="s">
@@ -24439,10 +24484,10 @@
       <c r="C502" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D502" s="6">
-        <v>1</v>
-      </c>
-      <c r="E502" s="6">
+      <c r="D502" s="5">
+        <v>1</v>
+      </c>
+      <c r="E502" s="5">
         <v>1</v>
       </c>
       <c r="F502" t="s">
@@ -24474,10 +24519,10 @@
       <c r="C503" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D503" s="6">
-        <v>1</v>
-      </c>
-      <c r="E503" s="6">
+      <c r="D503" s="5">
+        <v>1</v>
+      </c>
+      <c r="E503" s="5">
         <v>1</v>
       </c>
       <c r="F503" t="s">
@@ -24509,10 +24554,10 @@
       <c r="C504" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D504" s="6">
-        <v>1</v>
-      </c>
-      <c r="E504" s="6">
+      <c r="D504" s="5">
+        <v>1</v>
+      </c>
+      <c r="E504" s="5">
         <v>1</v>
       </c>
       <c r="F504" t="s">
@@ -24544,10 +24589,10 @@
       <c r="C505" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D505" s="6">
-        <v>1</v>
-      </c>
-      <c r="E505" s="6">
+      <c r="D505" s="5">
+        <v>1</v>
+      </c>
+      <c r="E505" s="5">
         <v>1</v>
       </c>
       <c r="F505" t="s">
@@ -24579,10 +24624,10 @@
       <c r="C506" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D506" s="6">
-        <v>1</v>
-      </c>
-      <c r="E506" s="6">
+      <c r="D506" s="5">
+        <v>1</v>
+      </c>
+      <c r="E506" s="5">
         <v>1</v>
       </c>
       <c r="F506" t="s">
@@ -24614,10 +24659,10 @@
       <c r="C507" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D507" s="6">
-        <v>1</v>
-      </c>
-      <c r="E507" s="6">
+      <c r="D507" s="5">
+        <v>1</v>
+      </c>
+      <c r="E507" s="5">
         <v>1</v>
       </c>
       <c r="F507" t="s">
@@ -24649,10 +24694,10 @@
       <c r="C508" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D508" s="6">
-        <v>1</v>
-      </c>
-      <c r="E508" s="6">
+      <c r="D508" s="5">
+        <v>1</v>
+      </c>
+      <c r="E508" s="5">
         <v>1</v>
       </c>
       <c r="F508" t="s">
@@ -24684,10 +24729,10 @@
       <c r="C509" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D509" s="6">
-        <v>1</v>
-      </c>
-      <c r="E509" s="6">
+      <c r="D509" s="5">
+        <v>1</v>
+      </c>
+      <c r="E509" s="5">
         <v>1</v>
       </c>
       <c r="F509" t="s">
@@ -24719,10 +24764,10 @@
       <c r="C510" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D510" s="6">
-        <v>1</v>
-      </c>
-      <c r="E510" s="6">
+      <c r="D510" s="5">
+        <v>1</v>
+      </c>
+      <c r="E510" s="5">
         <v>1</v>
       </c>
       <c r="F510" t="s">
@@ -24754,10 +24799,10 @@
       <c r="C511" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D511" s="6">
-        <v>1</v>
-      </c>
-      <c r="E511" s="6">
+      <c r="D511" s="5">
+        <v>1</v>
+      </c>
+      <c r="E511" s="5">
         <v>1</v>
       </c>
       <c r="F511" t="s">
@@ -24789,10 +24834,10 @@
       <c r="C512" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D512" s="6">
-        <v>1</v>
-      </c>
-      <c r="E512" s="6">
+      <c r="D512" s="5">
+        <v>1</v>
+      </c>
+      <c r="E512" s="5">
         <v>1</v>
       </c>
       <c r="F512" t="s">
@@ -24824,10 +24869,10 @@
       <c r="C513" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D513" s="6">
-        <v>1</v>
-      </c>
-      <c r="E513" s="6">
+      <c r="D513" s="5">
+        <v>1</v>
+      </c>
+      <c r="E513" s="5">
         <v>1</v>
       </c>
       <c r="F513" t="s">
@@ -24859,10 +24904,10 @@
       <c r="C514" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D514" s="6">
-        <v>1</v>
-      </c>
-      <c r="E514" s="6">
+      <c r="D514" s="5">
+        <v>1</v>
+      </c>
+      <c r="E514" s="5">
         <v>1</v>
       </c>
       <c r="F514" t="s">
@@ -24894,10 +24939,10 @@
       <c r="C515" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D515" s="6">
-        <v>1</v>
-      </c>
-      <c r="E515" s="6">
+      <c r="D515" s="5">
+        <v>1</v>
+      </c>
+      <c r="E515" s="5">
         <v>1</v>
       </c>
       <c r="F515" t="s">
@@ -24929,10 +24974,10 @@
       <c r="C516" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D516" s="6">
-        <v>1</v>
-      </c>
-      <c r="E516" s="6">
+      <c r="D516" s="5">
+        <v>1</v>
+      </c>
+      <c r="E516" s="5">
         <v>1</v>
       </c>
       <c r="F516" t="s">
@@ -24964,10 +25009,10 @@
       <c r="C517" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D517" s="6">
-        <v>1</v>
-      </c>
-      <c r="E517" s="6">
+      <c r="D517" s="5">
+        <v>1</v>
+      </c>
+      <c r="E517" s="5">
         <v>1</v>
       </c>
       <c r="F517" t="s">
@@ -24999,10 +25044,10 @@
       <c r="C518" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D518" s="6">
-        <v>1</v>
-      </c>
-      <c r="E518" s="6">
+      <c r="D518" s="5">
+        <v>1</v>
+      </c>
+      <c r="E518" s="5">
         <v>1</v>
       </c>
       <c r="F518" t="s">
@@ -25034,10 +25079,10 @@
       <c r="C519" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D519" s="6">
-        <v>1</v>
-      </c>
-      <c r="E519" s="6">
+      <c r="D519" s="5">
+        <v>1</v>
+      </c>
+      <c r="E519" s="5">
         <v>1</v>
       </c>
       <c r="F519" t="s">
@@ -25069,10 +25114,10 @@
       <c r="C520" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D520" s="6">
-        <v>1</v>
-      </c>
-      <c r="E520" s="6">
+      <c r="D520" s="5">
+        <v>1</v>
+      </c>
+      <c r="E520" s="5">
         <v>1</v>
       </c>
       <c r="F520" t="s">
@@ -25104,10 +25149,10 @@
       <c r="C521" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D521" s="6">
-        <v>1</v>
-      </c>
-      <c r="E521" s="6">
+      <c r="D521" s="5">
+        <v>1</v>
+      </c>
+      <c r="E521" s="5">
         <v>1</v>
       </c>
       <c r="F521" t="s">
@@ -25139,10 +25184,10 @@
       <c r="C522" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D522" s="6">
-        <v>1</v>
-      </c>
-      <c r="E522" s="6">
+      <c r="D522" s="5">
+        <v>1</v>
+      </c>
+      <c r="E522" s="5">
         <v>1</v>
       </c>
       <c r="F522" t="s">
@@ -25174,10 +25219,10 @@
       <c r="C523" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D523" s="6">
-        <v>1</v>
-      </c>
-      <c r="E523" s="6">
+      <c r="D523" s="5">
+        <v>1</v>
+      </c>
+      <c r="E523" s="5">
         <v>1</v>
       </c>
       <c r="F523" t="s">
@@ -25209,10 +25254,10 @@
       <c r="C524" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D524" s="6">
-        <v>1</v>
-      </c>
-      <c r="E524" s="6">
+      <c r="D524" s="5">
+        <v>1</v>
+      </c>
+      <c r="E524" s="5">
         <v>1</v>
       </c>
       <c r="F524" t="s">
@@ -25244,10 +25289,10 @@
       <c r="C525" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D525" s="6">
-        <v>1</v>
-      </c>
-      <c r="E525" s="6">
+      <c r="D525" s="5">
+        <v>1</v>
+      </c>
+      <c r="E525" s="5">
         <v>1</v>
       </c>
       <c r="F525" t="s">
@@ -25279,10 +25324,10 @@
       <c r="C526" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D526" s="6">
-        <v>1</v>
-      </c>
-      <c r="E526" s="6">
+      <c r="D526" s="5">
+        <v>1</v>
+      </c>
+      <c r="E526" s="5">
         <v>1</v>
       </c>
       <c r="F526" t="s">
@@ -25314,10 +25359,10 @@
       <c r="C527" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D527" s="6">
-        <v>1</v>
-      </c>
-      <c r="E527" s="6">
+      <c r="D527" s="5">
+        <v>1</v>
+      </c>
+      <c r="E527" s="5">
         <v>1</v>
       </c>
       <c r="F527" t="s">
@@ -25349,10 +25394,10 @@
       <c r="C528" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D528" s="6">
-        <v>1</v>
-      </c>
-      <c r="E528" s="6">
+      <c r="D528" s="5">
+        <v>1</v>
+      </c>
+      <c r="E528" s="5">
         <v>1</v>
       </c>
       <c r="F528" t="s">
@@ -25384,10 +25429,10 @@
       <c r="C529" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D529" s="6">
-        <v>1</v>
-      </c>
-      <c r="E529" s="6">
+      <c r="D529" s="5">
+        <v>1</v>
+      </c>
+      <c r="E529" s="5">
         <v>1</v>
       </c>
       <c r="F529" t="s">
@@ -25419,10 +25464,10 @@
       <c r="C530" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D530" s="6">
-        <v>1</v>
-      </c>
-      <c r="E530" s="6">
+      <c r="D530" s="5">
+        <v>1</v>
+      </c>
+      <c r="E530" s="5">
         <v>1</v>
       </c>
       <c r="F530" t="s">
@@ -25454,10 +25499,10 @@
       <c r="C531" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D531" s="6">
-        <v>1</v>
-      </c>
-      <c r="E531" s="6">
+      <c r="D531" s="5">
+        <v>1</v>
+      </c>
+      <c r="E531" s="5">
         <v>1</v>
       </c>
       <c r="F531" t="s">
@@ -25489,10 +25534,10 @@
       <c r="C532" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D532" s="6">
-        <v>1</v>
-      </c>
-      <c r="E532" s="6">
+      <c r="D532" s="5">
+        <v>1</v>
+      </c>
+      <c r="E532" s="5">
         <v>1</v>
       </c>
       <c r="F532" t="s">
@@ -25524,10 +25569,10 @@
       <c r="C533" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D533" s="6">
-        <v>1</v>
-      </c>
-      <c r="E533" s="6">
+      <c r="D533" s="5">
+        <v>1</v>
+      </c>
+      <c r="E533" s="5">
         <v>1</v>
       </c>
       <c r="F533" t="s">
@@ -25559,10 +25604,10 @@
       <c r="C534" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D534" s="6">
-        <v>1</v>
-      </c>
-      <c r="E534" s="6">
+      <c r="D534" s="5">
+        <v>1</v>
+      </c>
+      <c r="E534" s="5">
         <v>1</v>
       </c>
       <c r="F534" t="s">
@@ -25594,10 +25639,10 @@
       <c r="C535" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D535" s="6">
-        <v>1</v>
-      </c>
-      <c r="E535" s="6">
+      <c r="D535" s="5">
+        <v>1</v>
+      </c>
+      <c r="E535" s="5">
         <v>1</v>
       </c>
       <c r="F535" t="s">
@@ -25629,10 +25674,10 @@
       <c r="C536" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D536" s="6">
-        <v>1</v>
-      </c>
-      <c r="E536" s="6">
+      <c r="D536" s="5">
+        <v>1</v>
+      </c>
+      <c r="E536" s="5">
         <v>1</v>
       </c>
       <c r="F536" t="s">
@@ -25664,10 +25709,10 @@
       <c r="C537" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D537" s="6">
-        <v>1</v>
-      </c>
-      <c r="E537" s="6">
+      <c r="D537" s="5">
+        <v>1</v>
+      </c>
+      <c r="E537" s="5">
         <v>1</v>
       </c>
       <c r="F537" t="s">
@@ -25699,10 +25744,10 @@
       <c r="C538" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D538" s="6">
-        <v>1</v>
-      </c>
-      <c r="E538" s="6">
+      <c r="D538" s="5">
+        <v>1</v>
+      </c>
+      <c r="E538" s="5">
         <v>1</v>
       </c>
       <c r="F538" t="s">
@@ -25734,10 +25779,10 @@
       <c r="C539" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D539" s="6">
-        <v>1</v>
-      </c>
-      <c r="E539" s="6">
+      <c r="D539" s="5">
+        <v>1</v>
+      </c>
+      <c r="E539" s="5">
         <v>1</v>
       </c>
       <c r="F539" t="s">
@@ -25769,10 +25814,10 @@
       <c r="C540" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D540" s="6">
-        <v>1</v>
-      </c>
-      <c r="E540" s="6">
+      <c r="D540" s="5">
+        <v>1</v>
+      </c>
+      <c r="E540" s="5">
         <v>1</v>
       </c>
       <c r="F540" t="s">
@@ -25804,10 +25849,10 @@
       <c r="C541" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D541" s="6">
-        <v>1</v>
-      </c>
-      <c r="E541" s="6">
+      <c r="D541" s="5">
+        <v>1</v>
+      </c>
+      <c r="E541" s="5">
         <v>1</v>
       </c>
       <c r="F541" t="s">
@@ -25839,10 +25884,10 @@
       <c r="C542" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D542" s="6">
-        <v>1</v>
-      </c>
-      <c r="E542" s="6">
+      <c r="D542" s="5">
+        <v>1</v>
+      </c>
+      <c r="E542" s="5">
         <v>1</v>
       </c>
       <c r="F542" t="s">
@@ -25874,10 +25919,10 @@
       <c r="C543" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D543" s="6">
-        <v>1</v>
-      </c>
-      <c r="E543" s="6">
+      <c r="D543" s="5">
+        <v>1</v>
+      </c>
+      <c r="E543" s="5">
         <v>1</v>
       </c>
       <c r="F543" t="s">
@@ -25909,10 +25954,10 @@
       <c r="C544" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D544" s="6">
-        <v>1</v>
-      </c>
-      <c r="E544" s="6">
+      <c r="D544" s="5">
+        <v>1</v>
+      </c>
+      <c r="E544" s="5">
         <v>1</v>
       </c>
       <c r="F544" t="s">
@@ -25944,10 +25989,10 @@
       <c r="C545" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D545" s="6">
-        <v>1</v>
-      </c>
-      <c r="E545" s="6">
+      <c r="D545" s="5">
+        <v>1</v>
+      </c>
+      <c r="E545" s="5">
         <v>1</v>
       </c>
       <c r="F545" t="s">
@@ -25979,10 +26024,10 @@
       <c r="C546" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D546" s="6">
-        <v>1</v>
-      </c>
-      <c r="E546" s="6">
+      <c r="D546" s="5">
+        <v>1</v>
+      </c>
+      <c r="E546" s="5">
         <v>1</v>
       </c>
       <c r="F546" t="s">
@@ -26014,10 +26059,10 @@
       <c r="C547" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D547" s="6">
-        <v>1</v>
-      </c>
-      <c r="E547" s="6">
+      <c r="D547" s="5">
+        <v>1</v>
+      </c>
+      <c r="E547" s="5">
         <v>1</v>
       </c>
       <c r="F547" t="s">
@@ -26049,10 +26094,10 @@
       <c r="C548" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D548" s="6">
-        <v>1</v>
-      </c>
-      <c r="E548" s="6">
+      <c r="D548" s="5">
+        <v>1</v>
+      </c>
+      <c r="E548" s="5">
         <v>1</v>
       </c>
       <c r="F548" t="s">
@@ -26084,10 +26129,10 @@
       <c r="C549" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D549" s="6">
-        <v>1</v>
-      </c>
-      <c r="E549" s="6">
+      <c r="D549" s="5">
+        <v>1</v>
+      </c>
+      <c r="E549" s="5">
         <v>1</v>
       </c>
       <c r="F549" t="s">
@@ -26119,10 +26164,10 @@
       <c r="C550" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D550" s="6">
-        <v>1</v>
-      </c>
-      <c r="E550" s="6">
+      <c r="D550" s="5">
+        <v>1</v>
+      </c>
+      <c r="E550" s="5">
         <v>1</v>
       </c>
       <c r="F550" t="s">
@@ -26154,10 +26199,10 @@
       <c r="C551" s="4" t="s">
         <v>2045</v>
       </c>
-      <c r="D551" s="6">
-        <v>1</v>
-      </c>
-      <c r="E551" s="6">
+      <c r="D551" s="5">
+        <v>1</v>
+      </c>
+      <c r="E551" s="5">
         <v>1</v>
       </c>
       <c r="F551" t="s">
@@ -26189,10 +26234,10 @@
       <c r="C552" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D552" s="6">
-        <v>1</v>
-      </c>
-      <c r="E552" s="6">
+      <c r="D552" s="5">
+        <v>1</v>
+      </c>
+      <c r="E552" s="5">
         <v>1</v>
       </c>
       <c r="F552" t="s">
@@ -26224,10 +26269,10 @@
       <c r="C553" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D553" s="6">
-        <v>1</v>
-      </c>
-      <c r="E553" s="6">
+      <c r="D553" s="5">
+        <v>1</v>
+      </c>
+      <c r="E553" s="5">
         <v>1</v>
       </c>
       <c r="F553" t="s">
@@ -26259,10 +26304,10 @@
       <c r="C554" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D554" s="6">
-        <v>1</v>
-      </c>
-      <c r="E554" s="6">
+      <c r="D554" s="5">
+        <v>1</v>
+      </c>
+      <c r="E554" s="5">
         <v>1</v>
       </c>
       <c r="F554" t="s">
@@ -26294,10 +26339,10 @@
       <c r="C555" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D555" s="6">
-        <v>1</v>
-      </c>
-      <c r="E555" s="6">
+      <c r="D555" s="5">
+        <v>1</v>
+      </c>
+      <c r="E555" s="5">
         <v>1</v>
       </c>
       <c r="F555" t="s">
@@ -26329,10 +26374,10 @@
       <c r="C556" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D556" s="6">
-        <v>1</v>
-      </c>
-      <c r="E556" s="6">
+      <c r="D556" s="5">
+        <v>1</v>
+      </c>
+      <c r="E556" s="5">
         <v>1</v>
       </c>
       <c r="F556" t="s">
@@ -26364,10 +26409,10 @@
       <c r="C557" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D557" s="6">
-        <v>1</v>
-      </c>
-      <c r="E557" s="6">
+      <c r="D557" s="5">
+        <v>1</v>
+      </c>
+      <c r="E557" s="5">
         <v>1</v>
       </c>
       <c r="F557" t="s">
@@ -26399,10 +26444,10 @@
       <c r="C558" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D558" s="6">
-        <v>1</v>
-      </c>
-      <c r="E558" s="6">
+      <c r="D558" s="5">
+        <v>1</v>
+      </c>
+      <c r="E558" s="5">
         <v>1</v>
       </c>
       <c r="F558" t="s">
@@ -26434,10 +26479,10 @@
       <c r="C559" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D559" s="6">
-        <v>1</v>
-      </c>
-      <c r="E559" s="6">
+      <c r="D559" s="5">
+        <v>1</v>
+      </c>
+      <c r="E559" s="5">
         <v>1</v>
       </c>
       <c r="F559" t="s">
@@ -26469,10 +26514,10 @@
       <c r="C560" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D560" s="6">
-        <v>1</v>
-      </c>
-      <c r="E560" s="6">
+      <c r="D560" s="5">
+        <v>1</v>
+      </c>
+      <c r="E560" s="5">
         <v>1</v>
       </c>
       <c r="F560" t="s">
@@ -26504,10 +26549,10 @@
       <c r="C561" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D561" s="6">
-        <v>1</v>
-      </c>
-      <c r="E561" s="6">
+      <c r="D561" s="5">
+        <v>1</v>
+      </c>
+      <c r="E561" s="5">
         <v>1</v>
       </c>
       <c r="F561" t="s">
@@ -26539,10 +26584,10 @@
       <c r="C562" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D562" s="6">
-        <v>1</v>
-      </c>
-      <c r="E562" s="6">
+      <c r="D562" s="5">
+        <v>1</v>
+      </c>
+      <c r="E562" s="5">
         <v>1</v>
       </c>
       <c r="F562" t="s">
@@ -26574,10 +26619,10 @@
       <c r="C563" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D563" s="6">
-        <v>1</v>
-      </c>
-      <c r="E563" s="6">
+      <c r="D563" s="5">
+        <v>1</v>
+      </c>
+      <c r="E563" s="5">
         <v>1</v>
       </c>
       <c r="F563" t="s">
@@ -26609,10 +26654,10 @@
       <c r="C564" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D564" s="6">
-        <v>1</v>
-      </c>
-      <c r="E564" s="6">
+      <c r="D564" s="5">
+        <v>1</v>
+      </c>
+      <c r="E564" s="5">
         <v>1</v>
       </c>
       <c r="F564" t="s">
@@ -26644,10 +26689,10 @@
       <c r="C565" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D565" s="6">
-        <v>1</v>
-      </c>
-      <c r="E565" s="6">
+      <c r="D565" s="5">
+        <v>1</v>
+      </c>
+      <c r="E565" s="5">
         <v>1</v>
       </c>
       <c r="F565" t="s">
@@ -26679,10 +26724,10 @@
       <c r="C566" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D566" s="6">
-        <v>1</v>
-      </c>
-      <c r="E566" s="6">
+      <c r="D566" s="5">
+        <v>1</v>
+      </c>
+      <c r="E566" s="5">
         <v>1</v>
       </c>
       <c r="F566" t="s">
@@ -26714,10 +26759,10 @@
       <c r="C567" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D567" s="6">
-        <v>1</v>
-      </c>
-      <c r="E567" s="6">
+      <c r="D567" s="5">
+        <v>1</v>
+      </c>
+      <c r="E567" s="5">
         <v>1</v>
       </c>
       <c r="F567" t="s">
@@ -26749,10 +26794,10 @@
       <c r="C568" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D568" s="6">
-        <v>1</v>
-      </c>
-      <c r="E568" s="6">
+      <c r="D568" s="5">
+        <v>1</v>
+      </c>
+      <c r="E568" s="5">
         <v>1</v>
       </c>
       <c r="F568" t="s">
@@ -26784,10 +26829,10 @@
       <c r="C569" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D569" s="6">
-        <v>1</v>
-      </c>
-      <c r="E569" s="6">
+      <c r="D569" s="5">
+        <v>1</v>
+      </c>
+      <c r="E569" s="5">
         <v>1</v>
       </c>
       <c r="F569" t="s">
@@ -26819,10 +26864,10 @@
       <c r="C570" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D570" s="6">
-        <v>1</v>
-      </c>
-      <c r="E570" s="6">
+      <c r="D570" s="5">
+        <v>1</v>
+      </c>
+      <c r="E570" s="5">
         <v>1</v>
       </c>
       <c r="F570" t="s">
@@ -26854,10 +26899,10 @@
       <c r="C571" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D571" s="6">
-        <v>1</v>
-      </c>
-      <c r="E571" s="6">
+      <c r="D571" s="5">
+        <v>1</v>
+      </c>
+      <c r="E571" s="5">
         <v>1</v>
       </c>
       <c r="F571" t="s">
@@ -26889,10 +26934,10 @@
       <c r="C572" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D572" s="6">
-        <v>1</v>
-      </c>
-      <c r="E572" s="6">
+      <c r="D572" s="5">
+        <v>1</v>
+      </c>
+      <c r="E572" s="5">
         <v>1</v>
       </c>
       <c r="F572" t="s">
@@ -26924,10 +26969,10 @@
       <c r="C573" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D573" s="6">
-        <v>1</v>
-      </c>
-      <c r="E573" s="6">
+      <c r="D573" s="5">
+        <v>1</v>
+      </c>
+      <c r="E573" s="5">
         <v>1</v>
       </c>
       <c r="F573" t="s">
@@ -26959,10 +27004,10 @@
       <c r="C574" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D574" s="6">
-        <v>1</v>
-      </c>
-      <c r="E574" s="6">
+      <c r="D574" s="5">
+        <v>1</v>
+      </c>
+      <c r="E574" s="5">
         <v>1</v>
       </c>
       <c r="F574" t="s">
@@ -26994,10 +27039,10 @@
       <c r="C575" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D575" s="6">
-        <v>1</v>
-      </c>
-      <c r="E575" s="6">
+      <c r="D575" s="5">
+        <v>1</v>
+      </c>
+      <c r="E575" s="5">
         <v>1</v>
       </c>
       <c r="F575" t="s">
@@ -27029,10 +27074,10 @@
       <c r="C576" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D576" s="6">
-        <v>1</v>
-      </c>
-      <c r="E576" s="6">
+      <c r="D576" s="5">
+        <v>1</v>
+      </c>
+      <c r="E576" s="5">
         <v>1</v>
       </c>
       <c r="F576" t="s">
@@ -27064,10 +27109,10 @@
       <c r="C577" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D577" s="6">
-        <v>1</v>
-      </c>
-      <c r="E577" s="6">
+      <c r="D577" s="5">
+        <v>1</v>
+      </c>
+      <c r="E577" s="5">
         <v>1</v>
       </c>
       <c r="F577" t="s">
@@ -27099,10 +27144,10 @@
       <c r="C578" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D578" s="6">
-        <v>1</v>
-      </c>
-      <c r="E578" s="6">
+      <c r="D578" s="5">
+        <v>1</v>
+      </c>
+      <c r="E578" s="5">
         <v>1</v>
       </c>
       <c r="F578" t="s">
@@ -27134,10 +27179,10 @@
       <c r="C579" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D579" s="6">
-        <v>1</v>
-      </c>
-      <c r="E579" s="6">
+      <c r="D579" s="5">
+        <v>1</v>
+      </c>
+      <c r="E579" s="5">
         <v>1</v>
       </c>
       <c r="F579" t="s">
@@ -27169,10 +27214,10 @@
       <c r="C580" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D580" s="6">
-        <v>1</v>
-      </c>
-      <c r="E580" s="6">
+      <c r="D580" s="5">
+        <v>1</v>
+      </c>
+      <c r="E580" s="5">
         <v>1</v>
       </c>
       <c r="F580" t="s">
@@ -27204,10 +27249,10 @@
       <c r="C581" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D581" s="6">
-        <v>1</v>
-      </c>
-      <c r="E581" s="6">
+      <c r="D581" s="5">
+        <v>1</v>
+      </c>
+      <c r="E581" s="5">
         <v>1</v>
       </c>
       <c r="F581" t="s">
@@ -27239,10 +27284,10 @@
       <c r="C582" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D582" s="6">
-        <v>1</v>
-      </c>
-      <c r="E582" s="6">
+      <c r="D582" s="5">
+        <v>1</v>
+      </c>
+      <c r="E582" s="5">
         <v>1</v>
       </c>
       <c r="F582" t="s">
@@ -27274,10 +27319,10 @@
       <c r="C583" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D583" s="6">
-        <v>1</v>
-      </c>
-      <c r="E583" s="6">
+      <c r="D583" s="5">
+        <v>1</v>
+      </c>
+      <c r="E583" s="5">
         <v>1</v>
       </c>
       <c r="F583" t="s">
@@ -27309,10 +27354,10 @@
       <c r="C584" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D584" s="6">
-        <v>1</v>
-      </c>
-      <c r="E584" s="6">
+      <c r="D584" s="5">
+        <v>1</v>
+      </c>
+      <c r="E584" s="5">
         <v>1</v>
       </c>
       <c r="F584" t="s">
@@ -27344,10 +27389,10 @@
       <c r="C585" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D585" s="6">
-        <v>1</v>
-      </c>
-      <c r="E585" s="6">
+      <c r="D585" s="5">
+        <v>1</v>
+      </c>
+      <c r="E585" s="5">
         <v>1</v>
       </c>
       <c r="F585" t="s">
@@ -27379,10 +27424,10 @@
       <c r="C586" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D586" s="6">
-        <v>1</v>
-      </c>
-      <c r="E586" s="6">
+      <c r="D586" s="5">
+        <v>1</v>
+      </c>
+      <c r="E586" s="5">
         <v>1</v>
       </c>
       <c r="F586" t="s">
@@ -27414,10 +27459,10 @@
       <c r="C587" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D587" s="6">
-        <v>1</v>
-      </c>
-      <c r="E587" s="6">
+      <c r="D587" s="5">
+        <v>1</v>
+      </c>
+      <c r="E587" s="5">
         <v>1</v>
       </c>
       <c r="F587" t="s">
@@ -27449,10 +27494,10 @@
       <c r="C588" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D588" s="6">
-        <v>1</v>
-      </c>
-      <c r="E588" s="6">
+      <c r="D588" s="5">
+        <v>1</v>
+      </c>
+      <c r="E588" s="5">
         <v>1</v>
       </c>
       <c r="F588" t="s">
@@ -27484,10 +27529,10 @@
       <c r="C589" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D589" s="6">
-        <v>1</v>
-      </c>
-      <c r="E589" s="6">
+      <c r="D589" s="5">
+        <v>1</v>
+      </c>
+      <c r="E589" s="5">
         <v>1</v>
       </c>
       <c r="F589" t="s">
@@ -27519,10 +27564,10 @@
       <c r="C590" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D590" s="6">
-        <v>1</v>
-      </c>
-      <c r="E590" s="6">
+      <c r="D590" s="5">
+        <v>1</v>
+      </c>
+      <c r="E590" s="5">
         <v>1</v>
       </c>
       <c r="F590" t="s">
@@ -27554,10 +27599,10 @@
       <c r="C591" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D591" s="6">
-        <v>1</v>
-      </c>
-      <c r="E591" s="6">
+      <c r="D591" s="5">
+        <v>1</v>
+      </c>
+      <c r="E591" s="5">
         <v>1</v>
       </c>
       <c r="F591" t="s">
@@ -27589,10 +27634,10 @@
       <c r="C592" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D592" s="6">
-        <v>1</v>
-      </c>
-      <c r="E592" s="6">
+      <c r="D592" s="5">
+        <v>1</v>
+      </c>
+      <c r="E592" s="5">
         <v>1</v>
       </c>
       <c r="F592" t="s">
@@ -27624,10 +27669,10 @@
       <c r="C593" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D593" s="6">
-        <v>1</v>
-      </c>
-      <c r="E593" s="6">
+      <c r="D593" s="5">
+        <v>1</v>
+      </c>
+      <c r="E593" s="5">
         <v>1</v>
       </c>
       <c r="F593" t="s">
@@ -27659,10 +27704,10 @@
       <c r="C594" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D594" s="6">
-        <v>1</v>
-      </c>
-      <c r="E594" s="6">
+      <c r="D594" s="5">
+        <v>1</v>
+      </c>
+      <c r="E594" s="5">
         <v>1</v>
       </c>
       <c r="F594" t="s">
@@ -27694,10 +27739,10 @@
       <c r="C595" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D595" s="6">
-        <v>1</v>
-      </c>
-      <c r="E595" s="6">
+      <c r="D595" s="5">
+        <v>1</v>
+      </c>
+      <c r="E595" s="5">
         <v>1</v>
       </c>
       <c r="F595" t="s">
@@ -27729,10 +27774,10 @@
       <c r="C596" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D596" s="6">
-        <v>1</v>
-      </c>
-      <c r="E596" s="6">
+      <c r="D596" s="5">
+        <v>1</v>
+      </c>
+      <c r="E596" s="5">
         <v>1</v>
       </c>
       <c r="F596" t="s">
@@ -27764,10 +27809,10 @@
       <c r="C597" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D597" s="6">
-        <v>1</v>
-      </c>
-      <c r="E597" s="6">
+      <c r="D597" s="5">
+        <v>1</v>
+      </c>
+      <c r="E597" s="5">
         <v>1</v>
       </c>
       <c r="F597" t="s">
@@ -27799,10 +27844,10 @@
       <c r="C598" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D598" s="6">
-        <v>1</v>
-      </c>
-      <c r="E598" s="6">
+      <c r="D598" s="5">
+        <v>1</v>
+      </c>
+      <c r="E598" s="5">
         <v>1</v>
       </c>
       <c r="F598" t="s">
@@ -27834,10 +27879,10 @@
       <c r="C599" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D599" s="6">
-        <v>1</v>
-      </c>
-      <c r="E599" s="6">
+      <c r="D599" s="5">
+        <v>1</v>
+      </c>
+      <c r="E599" s="5">
         <v>1</v>
       </c>
       <c r="F599" t="s">
@@ -27869,10 +27914,10 @@
       <c r="C600" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D600" s="6">
-        <v>1</v>
-      </c>
-      <c r="E600" s="6">
+      <c r="D600" s="5">
+        <v>1</v>
+      </c>
+      <c r="E600" s="5">
         <v>1</v>
       </c>
       <c r="F600" t="s">
@@ -27904,10 +27949,10 @@
       <c r="C601" s="4" t="s">
         <v>2046</v>
       </c>
-      <c r="D601" s="6">
-        <v>1</v>
-      </c>
-      <c r="E601" s="6">
+      <c r="D601" s="5">
+        <v>1</v>
+      </c>
+      <c r="E601" s="5">
         <v>1</v>
       </c>
       <c r="F601" t="s">
@@ -27939,10 +27984,10 @@
       <c r="C602" s="4" t="s">
         <v>2047</v>
       </c>
-      <c r="D602" s="6">
-        <v>1</v>
-      </c>
-      <c r="E602" s="6">
+      <c r="D602" s="5">
+        <v>1</v>
+      </c>
+      <c r="E602" s="5">
         <v>1</v>
       </c>
       <c r="F602" t="s">
@@ -27974,10 +28019,10 @@
       <c r="C603" s="4" t="s">
         <v>2047</v>
       </c>
-      <c r="D603" s="6">
-        <v>1</v>
-      </c>
-      <c r="E603" s="6">
+      <c r="D603" s="5">
+        <v>1</v>
+      </c>
+      <c r="E603" s="5">
         <v>1</v>
       </c>
       <c r="F603" t="s">
@@ -28009,10 +28054,10 @@
       <c r="C604" s="4" t="s">
         <v>2047</v>
       </c>
-      <c r="D604" s="6">
-        <v>1</v>
-      </c>
-      <c r="E604" s="6">
+      <c r="D604" s="5">
+        <v>1</v>
+      </c>
+      <c r="E604" s="5">
         <v>1</v>
       </c>
       <c r="F604" t="s">
@@ -28044,10 +28089,10 @@
       <c r="C605" s="4" t="s">
         <v>2047</v>
       </c>
-      <c r="D605" s="6">
-        <v>1</v>
-      </c>
-      <c r="E605" s="6">
+      <c r="D605" s="5">
+        <v>1</v>
+      </c>
+      <c r="E605" s="5">
         <v>1</v>
       </c>
       <c r="F605" t="s">
@@ -28079,10 +28124,10 @@
       <c r="C606" s="4" t="s">
         <v>2047</v>
       </c>
-      <c r="D606" s="6">
-        <v>1</v>
-      </c>
-      <c r="E606" s="6">
+      <c r="D606" s="5">
+        <v>1</v>
+      </c>
+      <c r="E606" s="5">
         <v>1</v>
       </c>
       <c r="F606" t="s">
@@ -28114,10 +28159,10 @@
       <c r="C607" s="4" t="s">
         <v>2047</v>
       </c>
-      <c r="D607" s="6">
-        <v>1</v>
-      </c>
-      <c r="E607" s="6">
+      <c r="D607" s="5">
+        <v>1</v>
+      </c>
+      <c r="E607" s="5">
         <v>1</v>
       </c>
       <c r="F607" t="s">
@@ -28149,10 +28194,10 @@
       <c r="C608" s="4" t="s">
         <v>2047</v>
       </c>
-      <c r="D608" s="6">
-        <v>1</v>
-      </c>
-      <c r="E608" s="6">
+      <c r="D608" s="5">
+        <v>1</v>
+      </c>
+      <c r="E608" s="5">
         <v>1</v>
       </c>
       <c r="F608" t="s">
@@ -28184,10 +28229,10 @@
       <c r="C609" s="4" t="s">
         <v>2047</v>
       </c>
-      <c r="D609" s="6">
-        <v>1</v>
-      </c>
-      <c r="E609" s="6">
+      <c r="D609" s="5">
+        <v>1</v>
+      </c>
+      <c r="E609" s="5">
         <v>1</v>
       </c>
       <c r="F609" t="s">
@@ -28219,10 +28264,10 @@
       <c r="C610" s="4" t="s">
         <v>2047</v>
       </c>
-      <c r="D610" s="6">
-        <v>1</v>
-      </c>
-      <c r="E610" s="6">
+      <c r="D610" s="5">
+        <v>1</v>
+      </c>
+      <c r="E610" s="5">
         <v>1</v>
       </c>
       <c r="F610" t="s">
@@ -28254,10 +28299,10 @@
       <c r="C611" s="4" t="s">
         <v>2047</v>
       </c>
-      <c r="D611" s="6">
-        <v>1</v>
-      </c>
-      <c r="E611" s="6">
+      <c r="D611" s="5">
+        <v>1</v>
+      </c>
+      <c r="E611" s="5">
         <v>1</v>
       </c>
       <c r="F611" t="s">
@@ -28289,10 +28334,10 @@
       <c r="C612" s="4" t="s">
         <v>2047</v>
       </c>
-      <c r="D612" s="6">
-        <v>1</v>
-      </c>
-      <c r="E612" s="6">
+      <c r="D612" s="5">
+        <v>1</v>
+      </c>
+      <c r="E612" s="5">
         <v>1</v>
       </c>
       <c r="F612" t="s">
@@ -28324,10 +28369,10 @@
       <c r="C613" s="4" t="s">
         <v>2047</v>
       </c>
-      <c r="D613" s="6">
-        <v>1</v>
-      </c>
-      <c r="E613" s="6">
+      <c r="D613" s="5">
+        <v>1</v>
+      </c>
+      <c r="E613" s="5">
         <v>1</v>
       </c>
       <c r="F613" t="s">
@@ -28356,13 +28401,13 @@
       <c r="B614" s="3" t="s">
         <v>2093</v>
       </c>
-      <c r="C614" s="8" t="s">
+      <c r="C614" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="D614" s="6">
-        <v>1</v>
-      </c>
-      <c r="E614" s="6">
+      <c r="D614" s="5">
+        <v>1</v>
+      </c>
+      <c r="E614" s="5">
         <v>1</v>
       </c>
       <c r="F614" t="s">
@@ -28391,13 +28436,13 @@
       <c r="B615" s="3" t="s">
         <v>2095</v>
       </c>
-      <c r="C615" s="8" t="s">
+      <c r="C615" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="D615" s="6">
-        <v>1</v>
-      </c>
-      <c r="E615" s="6">
+      <c r="D615" s="5">
+        <v>1</v>
+      </c>
+      <c r="E615" s="5">
         <v>1</v>
       </c>
       <c r="F615" t="s">
@@ -28426,13 +28471,13 @@
       <c r="B616" s="3" t="s">
         <v>2097</v>
       </c>
-      <c r="C616" s="8" t="s">
+      <c r="C616" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="D616" s="6">
-        <v>1</v>
-      </c>
-      <c r="E616" s="6">
+      <c r="D616" s="5">
+        <v>1</v>
+      </c>
+      <c r="E616" s="5">
         <v>1</v>
       </c>
       <c r="F616" t="s">
@@ -28461,13 +28506,13 @@
       <c r="B617" s="3" t="s">
         <v>2099</v>
       </c>
-      <c r="C617" s="8" t="s">
+      <c r="C617" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="D617" s="6">
-        <v>1</v>
-      </c>
-      <c r="E617" s="6">
+      <c r="D617" s="5">
+        <v>1</v>
+      </c>
+      <c r="E617" s="5">
         <v>1</v>
       </c>
       <c r="F617" t="s">
@@ -28496,13 +28541,13 @@
       <c r="B618" s="3" t="s">
         <v>2101</v>
       </c>
-      <c r="C618" s="8" t="s">
+      <c r="C618" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="D618" s="6">
-        <v>1</v>
-      </c>
-      <c r="E618" s="6">
+      <c r="D618" s="5">
+        <v>1</v>
+      </c>
+      <c r="E618" s="5">
         <v>1</v>
       </c>
       <c r="F618" t="s">
@@ -28531,13 +28576,13 @@
       <c r="B619" s="3" t="s">
         <v>2103</v>
       </c>
-      <c r="C619" s="8" t="s">
+      <c r="C619" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="D619" s="6">
-        <v>1</v>
-      </c>
-      <c r="E619" s="6">
+      <c r="D619" s="5">
+        <v>1</v>
+      </c>
+      <c r="E619" s="5">
         <v>1</v>
       </c>
       <c r="F619" t="s">
@@ -28566,13 +28611,13 @@
       <c r="B620" s="3" t="s">
         <v>2105</v>
       </c>
-      <c r="C620" s="8" t="s">
+      <c r="C620" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="D620" s="6">
-        <v>1</v>
-      </c>
-      <c r="E620" s="6">
+      <c r="D620" s="5">
+        <v>1</v>
+      </c>
+      <c r="E620" s="5">
         <v>1</v>
       </c>
       <c r="F620" t="s">
@@ -28601,13 +28646,13 @@
       <c r="B621" s="3" t="s">
         <v>2107</v>
       </c>
-      <c r="C621" s="8" t="s">
+      <c r="C621" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="D621" s="6">
-        <v>1</v>
-      </c>
-      <c r="E621" s="6">
+      <c r="D621" s="5">
+        <v>1</v>
+      </c>
+      <c r="E621" s="5">
         <v>1</v>
       </c>
       <c r="F621" t="s">
@@ -28636,13 +28681,13 @@
       <c r="B622" s="3" t="s">
         <v>2109</v>
       </c>
-      <c r="C622" s="8" t="s">
+      <c r="C622" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="D622" s="6">
-        <v>1</v>
-      </c>
-      <c r="E622" s="6">
+      <c r="D622" s="5">
+        <v>1</v>
+      </c>
+      <c r="E622" s="5">
         <v>1</v>
       </c>
       <c r="F622" t="s">
@@ -28671,13 +28716,13 @@
       <c r="B623" s="3" t="s">
         <v>2111</v>
       </c>
-      <c r="C623" s="8" t="s">
+      <c r="C623" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="D623" s="6">
-        <v>1</v>
-      </c>
-      <c r="E623" s="6">
+      <c r="D623" s="5">
+        <v>1</v>
+      </c>
+      <c r="E623" s="5">
         <v>1</v>
       </c>
       <c r="F623" t="s">
@@ -28706,13 +28751,13 @@
       <c r="B624" s="3" t="s">
         <v>2113</v>
       </c>
-      <c r="C624" s="8" t="s">
+      <c r="C624" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="D624" s="6">
-        <v>1</v>
-      </c>
-      <c r="E624" s="6">
+      <c r="D624" s="5">
+        <v>1</v>
+      </c>
+      <c r="E624" s="5">
         <v>1</v>
       </c>
       <c r="F624" t="s">
@@ -28741,13 +28786,13 @@
       <c r="B625" s="3" t="s">
         <v>2115</v>
       </c>
-      <c r="C625" s="8" t="s">
+      <c r="C625" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="D625" s="6">
-        <v>1</v>
-      </c>
-      <c r="E625" s="6">
+      <c r="D625" s="5">
+        <v>1</v>
+      </c>
+      <c r="E625" s="5">
         <v>1</v>
       </c>
       <c r="F625" t="s">
@@ -28776,13 +28821,13 @@
       <c r="B626" s="3" t="s">
         <v>1021</v>
       </c>
-      <c r="C626" s="8" t="s">
+      <c r="C626" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="D626" s="6">
-        <v>1</v>
-      </c>
-      <c r="E626" s="6">
+      <c r="D626" s="5">
+        <v>1</v>
+      </c>
+      <c r="E626" s="5">
         <v>1</v>
       </c>
       <c r="F626" t="s">
@@ -28811,13 +28856,13 @@
       <c r="B627" s="3" t="s">
         <v>2118</v>
       </c>
-      <c r="C627" s="8" t="s">
+      <c r="C627" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="D627" s="6">
-        <v>1</v>
-      </c>
-      <c r="E627" s="6">
+      <c r="D627" s="5">
+        <v>1</v>
+      </c>
+      <c r="E627" s="5">
         <v>1</v>
       </c>
       <c r="F627" t="s">
@@ -28846,13 +28891,13 @@
       <c r="B628" s="3" t="s">
         <v>2120</v>
       </c>
-      <c r="C628" s="8" t="s">
+      <c r="C628" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="D628" s="6">
-        <v>1</v>
-      </c>
-      <c r="E628" s="6">
+      <c r="D628" s="5">
+        <v>1</v>
+      </c>
+      <c r="E628" s="5">
         <v>1</v>
       </c>
       <c r="F628" t="s">
@@ -28881,13 +28926,13 @@
       <c r="B629" s="3" t="s">
         <v>2122</v>
       </c>
-      <c r="C629" s="8" t="s">
+      <c r="C629" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="D629" s="6">
-        <v>1</v>
-      </c>
-      <c r="E629" s="6">
+      <c r="D629" s="5">
+        <v>1</v>
+      </c>
+      <c r="E629" s="5">
         <v>1</v>
       </c>
       <c r="F629" t="s">
@@ -28916,13 +28961,13 @@
       <c r="B630" s="3" t="s">
         <v>2124</v>
       </c>
-      <c r="C630" s="8" t="s">
+      <c r="C630" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="D630" s="6">
-        <v>1</v>
-      </c>
-      <c r="E630" s="6">
+      <c r="D630" s="5">
+        <v>1</v>
+      </c>
+      <c r="E630" s="5">
         <v>1</v>
       </c>
       <c r="F630" t="s">
@@ -28951,13 +28996,13 @@
       <c r="B631" s="3" t="s">
         <v>2126</v>
       </c>
-      <c r="C631" s="8" t="s">
+      <c r="C631" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="D631" s="6">
-        <v>1</v>
-      </c>
-      <c r="E631" s="6">
+      <c r="D631" s="5">
+        <v>1</v>
+      </c>
+      <c r="E631" s="5">
         <v>1</v>
       </c>
       <c r="F631" t="s">
@@ -28977,6 +29022,79 @@
       </c>
       <c r="K631" t="s">
         <v>972</v>
+      </c>
+    </row>
+    <row r="632" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A632" s="3" t="s">
+        <v>2161</v>
+      </c>
+      <c r="B632" s="3" t="s">
+        <v>2162</v>
+      </c>
+      <c r="C632" s="7" t="s">
+        <v>2163</v>
+      </c>
+      <c r="D632" s="5">
+        <v>1</v>
+      </c>
+      <c r="E632" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="633" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A633" s="3" t="s">
+        <v>2164</v>
+      </c>
+      <c r="B633" s="3" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="634" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A634" s="3" t="s">
+        <v>2166</v>
+      </c>
+      <c r="B634" s="3" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="635" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A635" s="3" t="s">
+        <v>2168</v>
+      </c>
+      <c r="B635" s="3" t="s">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="636" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A636" s="3" t="s">
+        <v>2170</v>
+      </c>
+      <c r="B636" s="3" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="637" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A637" s="3" t="s">
+        <v>2172</v>
+      </c>
+      <c r="B637" s="3" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="638" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A638" s="3" t="s">
+        <v>2174</v>
+      </c>
+      <c r="B638" s="3" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="639" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A639" s="3" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B639" s="3" t="s">
+        <v>1181</v>
       </c>
     </row>
   </sheetData>
